--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9FD737-01F0-AE46-A99B-E66522A4983E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702C2339-B6B0-AE4B-8412-0C65FDEFDD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="2" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
     <sheet name="Localization" sheetId="8" r:id="rId2"/>
-    <sheet name="Player" sheetId="4" r:id="rId3"/>
-    <sheet name="Item" sheetId="19" r:id="rId4"/>
-    <sheet name="Grade" sheetId="22" r:id="rId5"/>
-    <sheet name="SynergeBiome" sheetId="20" r:id="rId6"/>
-    <sheet name="SynergeElement" sheetId="21" r:id="rId7"/>
+    <sheet name="Spawner" sheetId="23" r:id="rId3"/>
+    <sheet name="Player" sheetId="4" r:id="rId4"/>
+    <sheet name="Item" sheetId="19" r:id="rId5"/>
+    <sheet name="Grade" sheetId="22" r:id="rId6"/>
+    <sheet name="SynergeBiome" sheetId="20" r:id="rId7"/>
+    <sheet name="SynergeElement" sheetId="21" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="100">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,6 +75,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>List&lt;string&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>description</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -351,6 +356,86 @@
   </si>
   <si>
     <t>Snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropPlayerKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropPlayerPercent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Animal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prefabPath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player/Human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player/Dog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player/Eagle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player/Snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Dog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Eagle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spawner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;float&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spawnPlayerKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spawnPercent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player_Eagle,Player_Dog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spawner/SpawnerTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tick</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +621,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -586,6 +671,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -958,10 +1052,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -969,10 +1063,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -980,10 +1074,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -991,10 +1085,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1002,10 +1096,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1013,10 +1107,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1024,10 +1118,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1035,10 +1129,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1046,10 +1140,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1057,10 +1151,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1068,10 +1162,10 @@
         <v>5</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1079,10 +1173,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1090,10 +1184,10 @@
         <v>7</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1101,10 +1195,10 @@
         <v>8</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1112,10 +1206,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1123,10 +1217,10 @@
         <v>2</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E19" s="11"/>
     </row>
@@ -1135,10 +1229,10 @@
         <v>3</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" s="11"/>
     </row>
@@ -1147,10 +1241,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" s="11"/>
     </row>
@@ -1159,10 +1253,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E22" s="11"/>
     </row>
@@ -1171,10 +1265,10 @@
         <v>2</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" s="11"/>
     </row>
@@ -1183,10 +1277,10 @@
         <v>3</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" s="12"/>
     </row>
@@ -1195,16 +1289,22 @@
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="1"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="1"/>
+      <c r="A26" s="1">
+        <v>5</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1"/>
@@ -1413,19 +1513,242 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7454E3B-BCDE-5A49-BB39-4B30666D97F3}">
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="11"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="11"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
+        <v>Spawner_Test</v>
+      </c>
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="9">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="20">
+        <v>100100</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="11"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="11"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="11"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="11"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="11"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="L12" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A933480A-994B-A74A-B07D-EEB09A80B87F}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -1440,21 +1763,27 @@
       <c r="F1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>12</v>
+      <c r="G1" s="5" t="s">
+        <v>0</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+        <v>13</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -1463,45 +1792,53 @@
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
-    </row>
-    <row r="2" spans="1:21">
+      <c r="V1" s="5"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>13</v>
+      <c r="G2" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="14"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
       <c r="U2" s="6"/>
-    </row>
-    <row r="3" spans="1:21">
+      <c r="V2" s="6"/>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Player_Human</v>
@@ -1510,31 +1847,40 @@
         <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>46</v>
+        <v>53</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
+        <v>49</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Player_Dog</v>
@@ -1543,31 +1889,40 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>46</v>
+        <v>53</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21">
+        <v>49</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Player_Eagle</v>
@@ -1576,31 +1931,40 @@
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>46</v>
+        <v>53</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21">
+        <v>49</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
         <v>Player_Snake</v>
@@ -1609,205 +1973,240 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>46</v>
+        <v>53</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21">
+        <v>49</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="M6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="11"/>
+      <c r="G7" s="9"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" spans="1:21">
+      <c r="J7" s="11"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:22">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" spans="1:21">
+      <c r="F8" s="9"/>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:22">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="1:21">
+      <c r="F9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:22">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" spans="1:21">
+      <c r="F10" s="9"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:22">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" spans="1:21">
+      <c r="F11" s="9"/>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:22">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" spans="1:21">
+      <c r="F12" s="9"/>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:22">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:21">
+      <c r="F13" s="9"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:22">
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="3"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" spans="1:21">
+      <c r="F14" s="9"/>
+      <c r="G14" s="3"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:22">
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="4"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" spans="1:21">
+      <c r="F15" s="9"/>
+      <c r="G15" s="4"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:22">
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="4"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" spans="3:9">
+      <c r="F16" s="9"/>
+      <c r="G16" s="4"/>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="3:10">
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="4"/>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" spans="3:9">
+      <c r="F17" s="9"/>
+      <c r="G17" s="4"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="3:10">
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="I18" s="9"/>
-    </row>
-    <row r="19" spans="3:9">
+      <c r="F18" s="9"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="3:10">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" spans="3:9">
+      <c r="F19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="3:10">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
-      <c r="I20" s="9"/>
-    </row>
-    <row r="21" spans="3:9">
+      <c r="F20" s="9"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="3:10">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
-      <c r="I21" s="9"/>
-    </row>
-    <row r="22" spans="3:9">
+      <c r="F21" s="9"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="3:10">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
-      <c r="I22" s="9"/>
-    </row>
-    <row r="23" spans="3:9">
+      <c r="F22" s="9"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="3:10">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
-      <c r="I23" s="9"/>
-    </row>
-    <row r="24" spans="3:9">
+      <c r="F23" s="9"/>
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="3:10">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
-      <c r="I24" s="9"/>
-    </row>
-    <row r="25" spans="3:9">
+      <c r="F24" s="9"/>
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="3:10">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
-      <c r="I25" s="9"/>
-    </row>
-    <row r="26" spans="3:9">
+      <c r="F25" s="9"/>
+      <c r="J25" s="9"/>
+    </row>
+    <row r="26" spans="3:10">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
-      <c r="I26" s="9"/>
-    </row>
-    <row r="27" spans="3:9">
+      <c r="F26" s="9"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="3:10">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
-      <c r="I27" s="9"/>
-    </row>
-    <row r="28" spans="3:9">
+      <c r="F27" s="9"/>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="3:10">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="3:9">
+      <c r="F28" s="9"/>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="3:10">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="3:9">
+      <c r="F29" s="9"/>
+      <c r="J29" s="9"/>
+    </row>
+    <row r="30" spans="3:10">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="3:9">
+      <c r="F30" s="9"/>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="3:10">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="3:9">
+      <c r="F31" s="9"/>
+      <c r="J31" s="9"/>
+    </row>
+    <row r="32" spans="3:10">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
-      <c r="I32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FBA1699A-C505-8C41-9338-26277C216689}">
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1013</xm:f>
           </x14:formula1>
-          <xm:sqref>N3:N7 L3:L7 P3:P7</xm:sqref>
+          <xm:sqref>O3:O7 Q3:Q7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1815,7 +2214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
   <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -1834,33 +2233,35 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="5"/>
+      <c r="M1" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -1875,34 +2276,34 @@
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="6"/>
+        <v>52</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -1919,37 +2320,38 @@
         <v>Item_WoodSword</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>52</v>
+      <c r="K3" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>8</v>
+        <v>53</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1958,37 +2360,38 @@
         <v>Item_WoodStaff</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>8</v>
+        <v>53</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1997,41 +2400,45 @@
         <v>Item_WoodBow</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>47</v>
-      </c>
       <c r="I5" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>8</v>
+        <v>53</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="7"/>
+      <c r="A6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="1"/>
       <c r="I6" s="9"/>
@@ -2039,14 +2446,43 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="7" t="str">
-        <f t="shared" ref="A4:A7" si="0">_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
+        <v>Item_Human</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="D7" s="9"/>
-      <c r="E7" s="1"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="E7" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="C8" s="9"/>
@@ -2089,24 +2525,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B59ECF9-BEB9-264A-A494-976028F5B748}">
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1013</xm:f>
           </x14:formula1>
-          <xm:sqref>N3:N7 L6:L7 P3:P7</xm:sqref>
+          <xm:sqref>N3:N7 P3:P7 L6</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{17B1ACDF-E711-444F-BA32-32976EC6EADF}">
           <x14:formula1>
             <xm:f>#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>F6:F7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ED8B69D1-8784-8B4D-AD8C-A682934511C6}">
-          <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1013</xm:f>
-          </x14:formula1>
-          <xm:sqref>C6</xm:sqref>
+          <xm:sqref>F6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2114,7 +2544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -2128,7 +2558,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>0</v>
@@ -2144,13 +2574,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2159,19 +2589,19 @@
         <v>Grade_Common</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2180,19 +2610,19 @@
         <v>Grade_Uncommon</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -2203,19 +2633,19 @@
         <v>Grade_Rare</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -2226,19 +2656,19 @@
         <v>Grade_Epic</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -2249,19 +2679,19 @@
         <v>Grade_Unique</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -2272,19 +2702,19 @@
         <v>Grade_Legend</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>75</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2293,7 +2723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -2312,7 +2742,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -2326,13 +2756,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2341,19 +2771,19 @@
         <v>SynergeBiome_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2398,7 +2828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -2415,7 +2845,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -2429,13 +2859,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2444,19 +2874,19 @@
         <v>SynergeElement_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702C2339-B6B0-AE4B-8412-0C65FDEFDD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650B2035-80A0-4E4D-91F7-FBC55F92FBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="2" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="100">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2485,22 +2485,124 @@
       </c>
     </row>
     <row r="8" spans="1:22">
-      <c r="C8" s="9"/>
+      <c r="A8" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B8,C8)</f>
+        <v>Item_Dog</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="E8" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
-      <c r="C9" s="9"/>
+      <c r="A9" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B9,C9)</f>
+        <v>Item_Eagle</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="E9" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
-      <c r="C10" s="9"/>
+      <c r="A10" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B10,C10)</f>
+        <v>Item_Snake</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="E10" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="C11" s="9"/>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650B2035-80A0-4E4D-91F7-FBC55F92FBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0117BE5C-A8F2-D34E-A7ED-776B6AD14E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="101">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -436,6 +436,10 @@
   </si>
   <si>
     <t>tick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxAmount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2262,7 +2266,9 @@
       <c r="M1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="5"/>
+      <c r="N1" s="5" t="s">
+        <v>1</v>
+      </c>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
@@ -2304,7 +2310,9 @@
       <c r="M2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="6"/>
+      <c r="N2" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
@@ -2353,6 +2361,9 @@
       <c r="M3" s="15" t="s">
         <v>9</v>
       </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="7" t="str">
@@ -2393,6 +2404,9 @@
       <c r="M4" s="15" t="s">
         <v>9</v>
       </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="7" t="str">
@@ -2432,6 +2446,9 @@
       </c>
       <c r="M5" s="15" t="s">
         <v>9</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2483,6 +2500,9 @@
       <c r="M7" s="15" t="s">
         <v>9</v>
       </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="7" t="str">
@@ -2523,6 +2543,9 @@
       <c r="M8" s="15" t="s">
         <v>9</v>
       </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="7" t="str">
@@ -2563,6 +2586,9 @@
       <c r="M9" s="15" t="s">
         <v>9</v>
       </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="7" t="str">
@@ -2602,6 +2628,9 @@
       </c>
       <c r="M10" s="15" t="s">
         <v>9</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -2632,7 +2661,7 @@
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1013</xm:f>
           </x14:formula1>
-          <xm:sqref>N3:N7 P3:P7 L6</xm:sqref>
+          <xm:sqref>L6 P3:P7</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{17B1ACDF-E711-444F-BA32-32976EC6EADF}">
           <x14:formula1>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0117BE5C-A8F2-D34E-A7ED-776B6AD14E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9052B554-0DBC-284B-94D1-8D4313069FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="100">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -368,10 +368,6 @@
   </si>
   <si>
     <t>dropPlayerPercent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Animal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1307,7 +1303,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1552,7 +1548,7 @@
         <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -1567,16 +1563,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -1592,19 +1588,19 @@
         <v>Spawner_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G3" s="20">
         <v>100100</v>
@@ -1806,7 +1802,7 @@
         <v>28</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>29</v>
@@ -1857,7 +1853,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>53</v>
@@ -1878,7 +1874,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M3">
         <v>100</v>
@@ -1899,7 +1895,7 @@
         <v>53</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>53</v>
@@ -1920,7 +1916,7 @@
         <v>22</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -1941,7 +1937,7 @@
         <v>53</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>53</v>
@@ -1962,7 +1958,7 @@
         <v>22</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -1983,7 +1979,7 @@
         <v>53</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>53</v>
@@ -2004,7 +2000,7 @@
         <v>22</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -2311,7 +2307,7 @@
         <v>9</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -2474,7 +2470,7 @@
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="18" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>22</v>
@@ -2517,7 +2513,7 @@
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="18" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>22</v>
@@ -2560,7 +2556,7 @@
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="18" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>22</v>
@@ -2603,7 +2599,7 @@
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="18" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>22</v>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9052B554-0DBC-284B-94D1-8D4313069FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16015290-64A9-1F49-8CC1-419FF8348147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51160" yWindow="1100" windowWidth="51200" windowHeight="26600" activeTab="3" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="Spawner" sheetId="23" r:id="rId3"/>
     <sheet name="Player" sheetId="4" r:id="rId4"/>
     <sheet name="Item" sheetId="19" r:id="rId5"/>
-    <sheet name="Grade" sheetId="22" r:id="rId6"/>
-    <sheet name="SynergeBiome" sheetId="20" r:id="rId7"/>
-    <sheet name="SynergeElement" sheetId="21" r:id="rId8"/>
+    <sheet name="FactionRelation" sheetId="24" r:id="rId6"/>
+    <sheet name="Grade" sheetId="22" r:id="rId7"/>
+    <sheet name="SynergeBiome" sheetId="20" r:id="rId8"/>
+    <sheet name="SynergeElement" sheetId="21" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="113">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -436,6 +437,58 @@
   </si>
   <si>
     <t>maxAmount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FactionRelationType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FactionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Faction3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Faction4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Faction2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hostile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neutral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Friendly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>factionTypes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FactionRelation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;FactionRelationType&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>factionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hero</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1307,39 +1360,81 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="1"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="1"/>
+      <c r="A27" s="1">
+        <v>1</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="1"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="1"/>
+      <c r="A28" s="1">
+        <v>2</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="1"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="1"/>
+      <c r="A29" s="1">
+        <v>3</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="1"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="1"/>
+      <c r="A30" s="1">
+        <v>1</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="1"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="1"/>
+      <c r="A31" s="1">
+        <v>2</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="1"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="1"/>
+      <c r="A32" s="1">
+        <v>3</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="1"/>
+      <c r="A33" s="1">
+        <v>4</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1"/>
@@ -1493,7 +1588,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I14:I15" xr:uid="{2665461F-3737-5C48-86C3-985860BED678}">
       <formula1>$I$2:$I$1013</formula1>
     </dataValidation>
@@ -1746,6 +1841,7 @@
     <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1784,7 +1880,9 @@
       <c r="M1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="N1" s="5"/>
+      <c r="N1" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
@@ -1828,7 +1926,9 @@
       <c r="M2" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="N2" s="6"/>
+      <c r="N2" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
@@ -1876,8 +1976,11 @@
       <c r="L3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="9">
         <v>100</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1918,8 +2021,11 @@
       <c r="L4" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="9">
         <v>100</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1960,8 +2066,11 @@
       <c r="L5" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="9">
         <v>100</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2002,8 +2111,11 @@
       <c r="L6" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="9">
         <v>100</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -2201,12 +2313,12 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FBA1699A-C505-8C41-9338-26277C216689}">
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1013</xm:f>
           </x14:formula1>
-          <xm:sqref>O3:O7 Q3:Q7</xm:sqref>
+          <xm:sqref>Q3:Q7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2672,6 +2784,283 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
+        <v>FactionRelation_Hero</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,E3:O3)</f>
+        <v>Friendly,Hostile,Hostile,Hostile</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="15"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
+        <v>FactionRelation_Faction2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="9" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,E4:O4)</f>
+        <v>Hostile,Friendly,Hostile,Hostile</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
+        <v>FactionRelation_Faction3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="9" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,E5:O5)</f>
+        <v>Hostile,Hostile,Friendly,Hostile</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
+        <v>FactionRelation_Faction4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="9" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,E6:O6)</f>
+        <v>Hostile,Hostile,Hostile,Friendly</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="C7" s="9"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="C8" s="9"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="C9" s="9"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="C10" s="9"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="H11" s="9"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="H12" s="9"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="H13" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D3DBA599-4157-B940-AFCF-2F7B820F1087}">
+          <x14:formula1>
+            <xm:f>Enum!$H$2:$H$1013</xm:f>
+          </x14:formula1>
+          <xm:sqref>K6 O3:O7</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -2850,7 +3239,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -2955,7 +3344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16015290-64A9-1F49-8CC1-419FF8348147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1D79F0-AEDD-6F46-B6D1-8F5F7CED4291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51160" yWindow="1100" windowWidth="51200" windowHeight="26600" activeTab="3" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51160" yWindow="1100" windowWidth="51200" windowHeight="26600" activeTab="5" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="113">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -674,7 +674,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -733,6 +733,12 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2785,25 +2791,27 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -2817,22 +2825,26 @@
       <c r="H1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="I1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="K1" s="8"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>112</v>
@@ -2847,27 +2859,27 @@
         <v>103</v>
       </c>
       <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="J2" s="6" t="s">
+        <v>108</v>
+      </c>
       <c r="K2" s="8"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3,D3)</f>
         <v>FactionRelation_Hero</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="D3" s="9" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,E3:O3)</f>
-        <v>Friendly,Hostile,Hostile,Hostile</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>107</v>
@@ -2881,25 +2893,26 @@
       <c r="H3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="15"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="9" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,E3:H3)</f>
+        <v>Friendly,Hostile,Hostile,Hostile</v>
+      </c>
+      <c r="K3" s="9"/>
       <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
+        <f>_xlfn.TEXTJOIN("_",TRUE,B4,D4)</f>
         <v>FactionRelation_Faction2</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="D4" s="9" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,E4:O4)</f>
-        <v>Hostile,Friendly,Hostile,Hostile</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>105</v>
@@ -2913,25 +2926,26 @@
       <c r="H4" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="15"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="9" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,E4:H4)</f>
+        <v>Hostile,Friendly,Hostile,Hostile</v>
+      </c>
+      <c r="K4" s="9"/>
       <c r="L4" s="15"/>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
+        <f>_xlfn.TEXTJOIN("_",TRUE,B5,D5)</f>
         <v>FactionRelation_Faction3</v>
       </c>
       <c r="B5" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="D5" s="9" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,E5:O5)</f>
-        <v>Hostile,Hostile,Friendly,Hostile</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>105</v>
@@ -2945,25 +2959,26 @@
       <c r="H5" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="15"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="9" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,E5:H5)</f>
+        <v>Hostile,Hostile,Friendly,Hostile</v>
+      </c>
+      <c r="K5" s="9"/>
       <c r="L5" s="15"/>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
+        <f>_xlfn.TEXTJOIN("_",TRUE,B6,D6)</f>
         <v>FactionRelation_Faction4</v>
       </c>
       <c r="B6" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="D6" s="9" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,E6:O6)</f>
-        <v>Hostile,Hostile,Hostile,Friendly</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>105</v>
@@ -2977,70 +2992,81 @@
       <c r="H6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="C7" s="9"/>
-      <c r="D7" s="18"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="9" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,E6:H6)</f>
+        <v>Hostile,Hostile,Hostile,Friendly</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="15"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="9"/>
       <c r="L7" s="15"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="C8" s="9"/>
-      <c r="D8" s="18"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="15"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="9"/>
       <c r="L8" s="15"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="C9" s="9"/>
-      <c r="D9" s="18"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="15"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="9"/>
       <c r="L9" s="15"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="C10" s="9"/>
-      <c r="D10" s="18"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="15"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="9"/>
       <c r="L10" s="15"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="C11" s="9"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="D11" s="9"/>
       <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="C12" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="9"/>
       <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="C13" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="D13" s="9"/>
       <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3052,7 +3078,7 @@
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1013</xm:f>
           </x14:formula1>
-          <xm:sqref>K6 O3:O7</xm:sqref>
+          <xm:sqref>L6:M6 Q3:Q7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1D79F0-AEDD-6F46-B6D1-8F5F7CED4291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64194306-E741-8D45-AF66-41EAB788FE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51160" yWindow="1100" windowWidth="51200" windowHeight="26600" activeTab="5" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="53460" yWindow="960" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="113">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,14 +88,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Pants</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Weapon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Accessory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>List&lt;StatType&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -231,20 +231,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Str,Dex,Int</t>
-  </si>
-  <si>
-    <t>Str,Dex,Int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,1</t>
-  </si>
-  <si>
-    <t>1,1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>WoodSword</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -489,6 +475,22 @@
   </si>
   <si>
     <t>Hero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,1,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Str,Dex,Int,Physical,Magical</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1054,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -1108,244 +1110,242 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="11"/>
+        <v>39</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="11"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="12"/>
+        <v>46</v>
+      </c>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>24</v>
@@ -1353,104 +1353,118 @@
       <c r="C25" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E26" s="12"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>105</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1">
+        <v>2</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1">
+        <v>3</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1">
         <v>4</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="1"/>
+      <c r="B35" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1"/>
@@ -1474,12 +1488,12 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="1"/>
-      <c r="B40" s="11"/>
+      <c r="B40" s="13"/>
       <c r="C40" s="1"/>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="1"/>
-      <c r="B41" s="11"/>
+      <c r="B41" s="13"/>
       <c r="C41" s="1"/>
     </row>
     <row r="42" spans="1:3">
@@ -1539,10 +1553,12 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="1"/>
+      <c r="B53" s="11"/>
       <c r="C53" s="1"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="1"/>
+      <c r="B54" s="11"/>
       <c r="C54" s="1"/>
     </row>
     <row r="55" spans="1:3">
@@ -1591,12 +1607,20 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="1"/>
+      <c r="C66" s="1"/>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="1"/>
+      <c r="C67" s="1"/>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I14:I15" xr:uid="{2665461F-3737-5C48-86C3-985860BED678}">
-      <formula1>$I$2:$I$1013</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I16:I17" xr:uid="{2665461F-3737-5C48-86C3-985860BED678}">
+      <formula1>$I$2:$I$1015</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1643,13 +1667,13 @@
         <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -1664,16 +1688,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -1689,19 +1713,19 @@
         <v>Spawner_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G3" s="20">
         <v>100100</v>
@@ -1884,10 +1908,10 @@
         <v>0</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -1906,7 +1930,7 @@
         <v>28</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>29</v>
@@ -1921,19 +1945,19 @@
         <v>16</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>23</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -1956,37 +1980,37 @@
         <v>45</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M3" s="9">
         <v>100</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1998,40 +2022,40 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>22</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M4" s="9">
         <v>100</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2043,40 +2067,40 @@
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M5" s="9">
         <v>100</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2088,40 +2112,40 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>22</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M6" s="9">
         <v>100</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -2319,10 +2343,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FBA1699A-C505-8C41-9338-26277C216689}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1013</xm:f>
+            <xm:f>Enum!$H$2:$H$1015</xm:f>
           </x14:formula1>
           <xm:sqref>Q3:Q7</xm:sqref>
         </x14:dataValidation>
@@ -2334,12 +2358,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -2416,7 +2441,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>30</v>
@@ -2425,7 +2450,7 @@
         <v>9</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -2445,32 +2470,32 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>50</v>
+        <v>61</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>9</v>
@@ -2488,32 +2513,32 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>9</v>
@@ -2531,32 +2556,32 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>50</v>
+        <v>63</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>9</v>
@@ -2572,8 +2597,8 @@
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="1"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="7" t="str">
@@ -2594,22 +2619,22 @@
         <v>22</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>50</v>
+        <v>63</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>9</v>
@@ -2627,7 +2652,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="18" t="s">
@@ -2637,22 +2662,22 @@
         <v>22</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>50</v>
+        <v>63</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M8" s="15" t="s">
         <v>9</v>
@@ -2670,7 +2695,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="18" t="s">
@@ -2680,22 +2705,22 @@
         <v>22</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>50</v>
+        <v>63</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>9</v>
@@ -2713,7 +2738,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="18" t="s">
@@ -2723,22 +2748,22 @@
         <v>22</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>50</v>
+        <v>63</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M10" s="15" t="s">
         <v>9</v>
@@ -2763,7 +2788,10 @@
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="I14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2773,7 +2801,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B59ECF9-BEB9-264A-A494-976028F5B748}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1013</xm:f>
+            <xm:f>Enum!$H$2:$H$1015</xm:f>
           </x14:formula1>
           <xm:sqref>L6 P3:P7</xm:sqref>
         </x14:dataValidation>
@@ -2811,7 +2839,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -2829,7 +2857,7 @@
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -2844,23 +2872,23 @@
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -2876,22 +2904,22 @@
         <v>FactionRelation_Hero</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9" t="str">
@@ -2909,22 +2937,22 @@
         <v>FactionRelation_Faction2</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="str">
@@ -2942,22 +2970,22 @@
         <v>FactionRelation_Faction3</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="9" t="str">
@@ -2975,22 +3003,22 @@
         <v>FactionRelation_Faction4</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="9" t="str">
@@ -3076,7 +3104,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D3DBA599-4157-B940-AFCF-2F7B820F1087}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1013</xm:f>
+            <xm:f>Enum!$H$2:$H$1015</xm:f>
           </x14:formula1>
           <xm:sqref>L6:M6 Q3:Q7</xm:sqref>
         </x14:dataValidation>
@@ -3131,7 +3159,7 @@
         <v>Grade_Common</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
@@ -3140,10 +3168,10 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3152,19 +3180,19 @@
         <v>Grade_Uncommon</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -3175,7 +3203,7 @@
         <v>Grade_Rare</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -3184,10 +3212,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -3198,7 +3226,7 @@
         <v>Grade_Epic</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
@@ -3207,10 +3235,10 @@
         <v>19</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -3221,7 +3249,7 @@
         <v>Grade_Unique</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -3230,10 +3258,10 @@
         <v>20</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -3244,7 +3272,7 @@
         <v>Grade_Legend</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>21</v>
@@ -3253,10 +3281,10 @@
         <v>21</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3298,13 +3326,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3313,10 +3341,10 @@
         <v>SynergeBiome_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>32</v>
@@ -3325,7 +3353,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3360,7 +3388,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F0F1FFA4-2FD9-9C45-A6EF-56B810B8EE53}">
           <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1013</xm:f>
+            <xm:f>Enum!$I$2:$I$1015</xm:f>
           </x14:formula1>
           <xm:sqref>C5:C6</xm:sqref>
         </x14:dataValidation>
@@ -3401,13 +3429,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3416,10 +3444,10 @@
         <v>SynergeElement_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>41</v>
@@ -3428,7 +3456,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3452,7 +3480,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
           <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1013</xm:f>
+            <xm:f>Enum!$I$2:$I$1015</xm:f>
           </x14:formula1>
           <xm:sqref>B5:B6</xm:sqref>
         </x14:dataValidation>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64194306-E741-8D45-AF66-41EAB788FE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC75DFB-03C5-4246-9E7F-00FD9DB4255C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="53460" yWindow="960" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="122">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -491,6 +491,42 @@
   </si>
   <si>
     <t>Str,Dex,Int,Physical,Magical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player/icon_player</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sprite_char_human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sprite_char_dog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sprite_char_eagle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sprite_char_snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_dog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_eagle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_snake</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1867,7 +1903,7 @@
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
@@ -1980,13 +2016,13 @@
         <v>45</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>49</v>
@@ -2025,13 +2061,13 @@
         <v>73</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>81</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>49</v>
@@ -2070,13 +2106,13 @@
         <v>74</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>82</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>49</v>
@@ -2115,13 +2151,13 @@
         <v>75</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>83</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>49</v>
@@ -2622,7 +2658,7 @@
         <v>64</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>112</v>
@@ -2665,7 +2701,7 @@
         <v>64</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>112</v>
@@ -2708,7 +2744,7 @@
         <v>64</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>112</v>
@@ -2751,7 +2787,7 @@
         <v>64</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>112</v>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC75DFB-03C5-4246-9E7F-00FD9DB4255C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B81783-FAB7-1340-A0DE-E9F0160D5BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53460" yWindow="960" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="53460" yWindow="960" windowWidth="51200" windowHeight="26600" activeTab="5" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B81783-FAB7-1340-A0DE-E9F0160D5BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D63300-7898-4E43-AC6D-DA6B19DC249B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53460" yWindow="960" windowWidth="51200" windowHeight="26600" activeTab="5" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="53460" yWindow="960" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Grade" sheetId="22" r:id="rId7"/>
     <sheet name="SynergeBiome" sheetId="20" r:id="rId8"/>
     <sheet name="SynergeElement" sheetId="21" r:id="rId9"/>
+    <sheet name="Skill" sheetId="27" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="138">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -140,6 +141,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>ItemType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -527,6 +532,66 @@
   </si>
   <si>
     <t>icon_item_snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Projectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillTimeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillAreaType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillAreaType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parameter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타입별 읽기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1152,7 +1217,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1163,7 +1228,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1185,7 +1250,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1237,10 +1302,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1248,10 +1313,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1259,10 +1324,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1270,10 +1335,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1281,10 +1346,10 @@
         <v>5</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1292,10 +1357,10 @@
         <v>6</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1303,10 +1368,10 @@
         <v>7</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1314,10 +1379,10 @@
         <v>8</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1325,10 +1390,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1336,10 +1401,10 @@
         <v>2</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21" s="11"/>
     </row>
@@ -1348,10 +1413,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E22" s="11"/>
     </row>
@@ -1360,10 +1425,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E23" s="11"/>
     </row>
@@ -1372,10 +1437,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" s="11"/>
     </row>
@@ -1384,7 +1449,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>11</v>
@@ -1396,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
@@ -1408,7 +1473,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>12</v>
@@ -1419,7 +1484,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>7</v>
@@ -1430,10 +1495,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1441,10 +1506,10 @@
         <v>2</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1452,10 +1517,10 @@
         <v>3</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1463,106 +1528,154 @@
         <v>1</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="1">
         <v>2</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="1">
         <v>3</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="1">
         <v>4</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="1"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="1"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="1"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="1"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="1"/>
-    </row>
-    <row r="43" spans="1:3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="1">
+        <v>1</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="1">
+        <v>2</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="1">
+        <v>1</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="1">
+        <v>1</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="1">
+        <v>2</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="1">
+        <v>3</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="1">
+        <v>4</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="1"/>
       <c r="B43" s="11"/>
       <c r="C43" s="1"/>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:11">
       <c r="A44" s="1"/>
       <c r="B44" s="11"/>
       <c r="C44" s="1"/>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:11">
       <c r="A45" s="1"/>
       <c r="B45" s="11"/>
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:11">
       <c r="A46" s="1"/>
       <c r="B46" s="11"/>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:11">
       <c r="A47" s="1"/>
       <c r="B47" s="11"/>
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:11">
       <c r="A48" s="1"/>
       <c r="B48" s="11"/>
       <c r="C48" s="1"/>
@@ -1660,6 +1773,352 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
+  <dimension ref="A1:AB17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+    </row>
+    <row r="2" spans="1:28">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K3" s="15"/>
+      <c r="L3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M3" s="11"/>
+      <c r="N3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B4:F4)</f>
+        <v>Skill_Human_Projectile_1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="9">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="L4" s="15"/>
+      <c r="M4" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N4" s="11"/>
+      <c r="Q4" s="15"/>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B5:F5)</f>
+        <v>Skill_Projectile_Hit_1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="9">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="N5" s="11"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="I6" s="18"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="18"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="O11" s="13"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="O12" s="13"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="O13" s="13"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="O14" s="13"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="O15" s="13"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:28">
+      <c r="O16" s="13"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="15:16">
+      <c r="O17" s="13"/>
+      <c r="P17" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5BEECEA4-F1BD-8D4A-93E2-C11D4CADC5DF}">
+          <x14:formula1>
+            <xm:f>#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>J6</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{87CC3E0A-FE7A-3B4B-906C-582F0788E53E}">
+          <x14:formula1>
+            <xm:f>Enum!$H$2:$H$1015</xm:f>
+          </x14:formula1>
+          <xm:sqref>P6 P4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1703,13 +2162,13 @@
         <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -1724,16 +2183,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -1749,19 +2208,19 @@
         <v>Spawner_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G3" s="20">
         <v>100100</v>
@@ -1935,7 +2394,7 @@
         <v>15</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>17</v>
@@ -1944,10 +2403,10 @@
         <v>0</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -1963,16 +2422,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>14</v>
@@ -1981,19 +2440,19 @@
         <v>16</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>23</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -2013,40 +2472,40 @@
         <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="J3" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M3" s="9">
         <v>100</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -2058,40 +2517,40 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="J4" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>22</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M4" s="9">
         <v>100</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2103,40 +2562,40 @@
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="J5" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M5" s="9">
         <v>100</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2148,40 +2607,40 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="J6" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>22</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M6" s="9">
         <v>100</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -2415,7 +2874,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>17</v>
@@ -2459,16 +2918,16 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>14</v>
@@ -2477,16 +2936,16 @@
         <v>16</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -2503,10 +2962,10 @@
         <v>Item_WoodSword</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9" t="s">
@@ -2516,22 +2975,22 @@
         <v>22</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="K3" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>9</v>
@@ -2546,10 +3005,10 @@
         <v>Item_WoodStaff</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
@@ -2559,22 +3018,22 @@
         <v>22</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I4" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="J4" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="K4" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>9</v>
@@ -2589,10 +3048,10 @@
         <v>Item_WoodBow</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
@@ -2602,22 +3061,22 @@
         <v>22</v>
       </c>
       <c r="G5" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>63</v>
-      </c>
       <c r="I5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="K5" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>9</v>
@@ -2642,10 +3101,10 @@
         <v>Item_Human</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="18" t="s">
@@ -2655,22 +3114,22 @@
         <v>22</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I7" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="K7" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>9</v>
@@ -2685,10 +3144,10 @@
         <v>Item_Dog</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="18" t="s">
@@ -2698,22 +3157,22 @@
         <v>22</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I8" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="K8" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M8" s="15" t="s">
         <v>9</v>
@@ -2728,10 +3187,10 @@
         <v>Item_Eagle</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="18" t="s">
@@ -2741,22 +3200,22 @@
         <v>22</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I9" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="J9" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="K9" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>9</v>
@@ -2771,10 +3230,10 @@
         <v>Item_Snake</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="18" t="s">
@@ -2784,22 +3243,22 @@
         <v>22</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I10" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="J10" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="K10" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M10" s="15" t="s">
         <v>9</v>
@@ -2875,7 +3334,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -2893,7 +3352,7 @@
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -2908,23 +3367,23 @@
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -2940,22 +3399,22 @@
         <v>FactionRelation_Hero</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9" t="str">
@@ -2973,22 +3432,22 @@
         <v>FactionRelation_Faction2</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="str">
@@ -3006,22 +3465,22 @@
         <v>FactionRelation_Faction3</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="9" t="str">
@@ -3039,22 +3498,22 @@
         <v>FactionRelation_Faction4</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="9" t="str">
@@ -3183,10 +3642,10 @@
         <v>23</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3195,7 +3654,7 @@
         <v>Grade_Common</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
@@ -3204,10 +3663,10 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3216,19 +3675,19 @@
         <v>Grade_Uncommon</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -3239,7 +3698,7 @@
         <v>Grade_Rare</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -3248,10 +3707,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -3262,7 +3721,7 @@
         <v>Grade_Epic</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
@@ -3271,10 +3730,10 @@
         <v>19</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -3285,7 +3744,7 @@
         <v>Grade_Unique</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -3294,10 +3753,10 @@
         <v>20</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -3308,7 +3767,7 @@
         <v>Grade_Legend</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>21</v>
@@ -3317,10 +3776,10 @@
         <v>21</v>
       </c>
       <c r="E8" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>72</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3348,7 +3807,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -3362,13 +3821,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3377,19 +3836,19 @@
         <v>SynergeBiome_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3451,7 +3910,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -3465,13 +3924,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3480,19 +3939,19 @@
         <v>SynergeElement_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6">

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D63300-7898-4E43-AC6D-DA6B19DC249B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E56ADE-DB5D-3347-8562-A594BD04CEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="53460" yWindow="960" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="140">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -583,15 +583,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>parameter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>타입별 읽기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Hit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillTimeParam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillAreaParam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillActionParam</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1816,19 +1824,19 @@
         <v>124</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>0</v>
+      <c r="L1" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="N1" s="8" t="s">
-        <v>0</v>
+      <c r="N1" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
@@ -1862,19 +1870,19 @@
         <v>124</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>127</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>130</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -1902,15 +1910,15 @@
       <c r="H3" s="15"/>
       <c r="I3" s="9"/>
       <c r="J3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K3" s="15"/>
       <c r="L3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M3" s="11"/>
       <c r="N3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="15"/>
@@ -1966,7 +1974,7 @@
         <v>123</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E5" s="9">
         <v>1</v>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E56ADE-DB5D-3347-8562-A594BD04CEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B6D41B-78E7-0840-A6B6-E4DBC4E9A540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53460" yWindow="960" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="141">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -142,6 +142,10 @@
   </si>
   <si>
     <t>Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1165,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
-  <dimension ref="A1:S68"/>
+  <dimension ref="A1:S69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -1225,7 +1229,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1236,7 +1240,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1258,7 +1262,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1310,10 +1314,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1321,10 +1325,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1332,10 +1336,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1343,10 +1347,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1354,10 +1358,10 @@
         <v>5</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1365,10 +1369,10 @@
         <v>6</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1376,10 +1380,10 @@
         <v>7</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1387,10 +1391,10 @@
         <v>8</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1398,10 +1402,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1409,10 +1413,10 @@
         <v>2</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" s="11"/>
     </row>
@@ -1421,10 +1425,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E22" s="11"/>
     </row>
@@ -1433,10 +1437,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E23" s="11"/>
     </row>
@@ -1445,10 +1449,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E24" s="11"/>
     </row>
@@ -1457,7 +1461,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>11</v>
@@ -1469,7 +1473,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
@@ -1481,7 +1485,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>12</v>
@@ -1492,7 +1496,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>7</v>
@@ -1503,10 +1507,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1514,10 +1518,10 @@
         <v>2</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1525,10 +1529,10 @@
         <v>3</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1536,10 +1540,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1547,10 +1551,10 @@
         <v>2</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1558,10 +1562,10 @@
         <v>3</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1569,10 +1573,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1580,10 +1584,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1591,10 +1595,10 @@
         <v>2</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1602,66 +1606,72 @@
         <v>1</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="1"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="1"/>
+      <c r="A43" s="1">
+        <v>4</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="1"/>
@@ -1720,6 +1730,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="1"/>
+      <c r="B55" s="11"/>
       <c r="C55" s="1"/>
     </row>
     <row r="56" spans="1:3">
@@ -1772,12 +1783,16 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="1"/>
+      <c r="C68" s="1"/>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I16:I17" xr:uid="{2665461F-3737-5C48-86C3-985860BED678}">
-      <formula1>$I$2:$I$1015</formula1>
+      <formula1>$I$2:$I$1016</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1821,19 +1836,19 @@
         <v>0</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>8</v>
@@ -1861,28 +1876,28 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -1910,15 +1925,15 @@
       <c r="H3" s="15"/>
       <c r="I3" s="9"/>
       <c r="J3" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K3" s="15"/>
       <c r="L3" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M3" s="11"/>
       <c r="N3" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="15"/>
@@ -1933,31 +1948,33 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E4" s="9">
         <v>1</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="L4" s="15"/>
+        <v>25</v>
+      </c>
+      <c r="L4" s="15">
+        <v>5</v>
+      </c>
       <c r="M4" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N4" s="11"/>
       <c r="Q4" s="15"/>
@@ -1971,31 +1988,33 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E5" s="9">
         <v>1</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>64</v>
-      </c>
       <c r="I5" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="L5" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="L5" s="15">
+        <v>5</v>
+      </c>
       <c r="M5" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N5" s="11"/>
       <c r="O5" s="9"/>
@@ -2111,7 +2130,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5BEECEA4-F1BD-8D4A-93E2-C11D4CADC5DF}">
           <x14:formula1>
             <xm:f>#REF!</xm:f>
@@ -2120,7 +2139,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{87CC3E0A-FE7A-3B4B-906C-582F0788E53E}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1015</xm:f>
+            <xm:f>Enum!$H$2:$H$1016</xm:f>
           </x14:formula1>
           <xm:sqref>P6 P4</xm:sqref>
         </x14:dataValidation>
@@ -2170,13 +2189,13 @@
         <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -2191,16 +2210,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -2216,19 +2235,19 @@
         <v>Spawner_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3" s="20">
         <v>100100</v>
@@ -2402,7 +2421,7 @@
         <v>15</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>17</v>
@@ -2411,10 +2430,10 @@
         <v>0</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -2430,16 +2449,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>14</v>
@@ -2448,19 +2467,19 @@
         <v>16</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>23</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -2480,40 +2499,40 @@
         <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="J3" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M3" s="9">
         <v>100</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -2525,40 +2544,40 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="J4" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>22</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M4" s="9">
         <v>100</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2570,40 +2589,40 @@
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="J5" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M5" s="9">
         <v>100</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2615,40 +2634,40 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="J6" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>22</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M6" s="9">
         <v>100</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -2849,7 +2868,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FBA1699A-C505-8C41-9338-26277C216689}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1015</xm:f>
+            <xm:f>Enum!$H$2:$H$1016</xm:f>
           </x14:formula1>
           <xm:sqref>Q3:Q7</xm:sqref>
         </x14:dataValidation>
@@ -2882,7 +2901,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>17</v>
@@ -2926,16 +2945,16 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>14</v>
@@ -2944,16 +2963,16 @@
         <v>16</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -2970,10 +2989,10 @@
         <v>Item_WoodSword</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9" t="s">
@@ -2983,22 +3002,22 @@
         <v>22</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I3" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="K3" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>9</v>
@@ -3013,10 +3032,10 @@
         <v>Item_WoodStaff</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
@@ -3026,22 +3045,22 @@
         <v>22</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I4" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J4" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="K4" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>9</v>
@@ -3056,10 +3075,10 @@
         <v>Item_WoodBow</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
@@ -3069,22 +3088,22 @@
         <v>22</v>
       </c>
       <c r="G5" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>64</v>
-      </c>
       <c r="I5" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="K5" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>9</v>
@@ -3109,10 +3128,10 @@
         <v>Item_Human</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="18" t="s">
@@ -3122,22 +3141,22 @@
         <v>22</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I7" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="K7" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>9</v>
@@ -3152,10 +3171,10 @@
         <v>Item_Dog</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="18" t="s">
@@ -3165,22 +3184,22 @@
         <v>22</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I8" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J8" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="K8" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M8" s="15" t="s">
         <v>9</v>
@@ -3195,10 +3214,10 @@
         <v>Item_Eagle</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="18" t="s">
@@ -3208,22 +3227,22 @@
         <v>22</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I9" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J9" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="K9" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>9</v>
@@ -3238,10 +3257,10 @@
         <v>Item_Snake</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="18" t="s">
@@ -3251,22 +3270,22 @@
         <v>22</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I10" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J10" s="11" t="s">
-        <v>112</v>
-      </c>
       <c r="K10" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M10" s="15" t="s">
         <v>9</v>
@@ -3304,7 +3323,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B59ECF9-BEB9-264A-A494-976028F5B748}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1015</xm:f>
+            <xm:f>Enum!$H$2:$H$1016</xm:f>
           </x14:formula1>
           <xm:sqref>L6 P3:P7</xm:sqref>
         </x14:dataValidation>
@@ -3342,7 +3361,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -3360,7 +3379,7 @@
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -3375,23 +3394,23 @@
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -3407,22 +3426,22 @@
         <v>FactionRelation_Hero</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9" t="str">
@@ -3440,22 +3459,22 @@
         <v>FactionRelation_Faction2</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="str">
@@ -3473,22 +3492,22 @@
         <v>FactionRelation_Faction3</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="9" t="str">
@@ -3506,22 +3525,22 @@
         <v>FactionRelation_Faction4</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="9" t="str">
@@ -3607,7 +3626,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D3DBA599-4157-B940-AFCF-2F7B820F1087}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1015</xm:f>
+            <xm:f>Enum!$H$2:$H$1016</xm:f>
           </x14:formula1>
           <xm:sqref>L6:M6 Q3:Q7</xm:sqref>
         </x14:dataValidation>
@@ -3650,10 +3669,10 @@
         <v>23</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3662,7 +3681,7 @@
         <v>Grade_Common</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
@@ -3671,10 +3690,10 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3683,19 +3702,19 @@
         <v>Grade_Uncommon</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -3706,7 +3725,7 @@
         <v>Grade_Rare</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -3715,10 +3734,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -3729,7 +3748,7 @@
         <v>Grade_Epic</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
@@ -3738,10 +3757,10 @@
         <v>19</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -3752,7 +3771,7 @@
         <v>Grade_Unique</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -3761,10 +3780,10 @@
         <v>20</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -3775,7 +3794,7 @@
         <v>Grade_Legend</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>21</v>
@@ -3784,10 +3803,10 @@
         <v>21</v>
       </c>
       <c r="E8" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>73</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3834,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -3829,13 +3848,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3844,19 +3863,19 @@
         <v>SynergeBiome_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3891,7 +3910,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F0F1FFA4-2FD9-9C45-A6EF-56B810B8EE53}">
           <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1015</xm:f>
+            <xm:f>Enum!$I$2:$I$1016</xm:f>
           </x14:formula1>
           <xm:sqref>C5:C6</xm:sqref>
         </x14:dataValidation>
@@ -3918,7 +3937,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -3932,13 +3951,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3947,19 +3966,19 @@
         <v>SynergeElement_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3983,7 +4002,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
           <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1015</xm:f>
+            <xm:f>Enum!$I$2:$I$1016</xm:f>
           </x14:formula1>
           <xm:sqref>B5:B6</xm:sqref>
         </x14:dataValidation>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B6D41B-78E7-0840-A6B6-E4DBC4E9A540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676F07F5-2960-644F-A85E-69C1AC786D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51380" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="146">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -560,6 +560,9 @@
   </si>
   <si>
     <t>Circle</t>
+  </si>
+  <si>
+    <t>Circle</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -604,6 +607,21 @@
   </si>
   <si>
     <t>skillActionParam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Human_MeleeAttack_1</t>
+  </si>
+  <si>
+    <t>MeleeAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillTimeType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -789,7 +807,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -853,6 +871,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1598,7 +1619,7 @@
         <v>125</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1620,7 +1641,7 @@
         <v>127</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1628,10 +1649,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -1639,7 +1660,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>124</v>
@@ -1650,10 +1671,10 @@
         <v>3</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -1661,10 +1682,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -1801,18 +1822,18 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
-  <dimension ref="A1:AB17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -1829,117 +1850,124 @@
       <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>0</v>
+      <c r="G1" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="8"/>
       <c r="P1" s="8"/>
-      <c r="Q1" s="5"/>
+      <c r="Q1" s="8"/>
       <c r="R1" s="5"/>
-      <c r="S1" s="8"/>
+      <c r="S1" s="5"/>
       <c r="T1" s="8"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="5"/>
       <c r="W1" s="8"/>
       <c r="X1" s="8"/>
       <c r="Y1" s="8"/>
       <c r="Z1" s="8"/>
-      <c r="AA1" s="5"/>
+      <c r="AA1" s="8"/>
       <c r="AB1" s="5"/>
-    </row>
-    <row r="2" spans="1:28">
+      <c r="AC1" s="5"/>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="J2" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="K2" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>139</v>
-      </c>
       <c r="M2" s="8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="O2" s="8"/>
+        <v>132</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="P2" s="8"/>
-      <c r="Q2" s="6"/>
+      <c r="Q2" s="8"/>
       <c r="R2" s="6"/>
-      <c r="S2" s="8"/>
+      <c r="S2" s="6"/>
       <c r="T2" s="8"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="6"/>
       <c r="W2" s="8"/>
       <c r="X2" s="8"/>
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
-      <c r="AA2" s="6"/>
+      <c r="AA2" s="8"/>
       <c r="AB2" s="6"/>
-    </row>
-    <row r="3" spans="1:28">
+      <c r="AC2" s="6"/>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="15"/>
+      <c r="G3" s="9"/>
       <c r="H3" s="15"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="M3" s="11"/>
-      <c r="N3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O3" s="9"/>
-      <c r="P3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="L3" s="15"/>
+      <c r="M3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="N3" s="11"/>
+      <c r="O3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="P3" s="9"/>
       <c r="Q3" s="15"/>
-    </row>
-    <row r="4" spans="1:28">
+      <c r="R3" s="15"/>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4:F4)</f>
         <v>Skill_Human_Projectile_1</v>
@@ -1957,29 +1985,32 @@
         <v>1</v>
       </c>
       <c r="F4" s="9"/>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="9">
+        <v>10</v>
+      </c>
+      <c r="H4" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="I4" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="J4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="2"/>
+      <c r="L4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="15">
+      <c r="M4" s="15">
         <v>5</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="N4" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="Q4" s="15"/>
-    </row>
-    <row r="5" spans="1:28">
+      <c r="O4" s="11"/>
+      <c r="R4" s="15"/>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5:F5)</f>
         <v>Skill_Projectile_Hit_1</v>
@@ -1991,157 +2022,196 @@
         <v>124</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E5" s="9">
         <v>1</v>
       </c>
       <c r="F5" s="9"/>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="I5" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="2"/>
+      <c r="L5" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="L5" s="15">
+      <c r="M5" s="15">
         <v>5</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="N5" s="11"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="15"/>
+      <c r="N5" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="9"/>
       <c r="Q5" s="15"/>
-    </row>
-    <row r="6" spans="1:28">
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="R5" s="15"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B6:F6)</f>
+        <v>Skill_Human_MeleeAttack_1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="9">
+        <v>1</v>
+      </c>
       <c r="F6" s="9"/>
-      <c r="I6" s="18"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="1:28">
+      <c r="G6" s="9">
+        <v>1</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="M6" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="O6" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="15"/>
+      <c r="G7" s="9"/>
       <c r="H7" s="15"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="9"/>
       <c r="L7" s="15"/>
-      <c r="M7" s="11"/>
+      <c r="M7" s="15"/>
       <c r="N7" s="11"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="15"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="9"/>
       <c r="Q7" s="15"/>
-    </row>
-    <row r="8" spans="1:28">
+      <c r="R7" s="15"/>
+    </row>
+    <row r="8" spans="1:29">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
-      <c r="G8" s="15"/>
+      <c r="G8" s="9"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="9"/>
       <c r="L8" s="15"/>
-      <c r="M8" s="11"/>
+      <c r="M8" s="15"/>
       <c r="N8" s="11"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="15"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="9"/>
       <c r="Q8" s="15"/>
-    </row>
-    <row r="9" spans="1:28">
+      <c r="R8" s="15"/>
+    </row>
+    <row r="9" spans="1:29">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
-      <c r="G9" s="15"/>
+      <c r="G9" s="9"/>
       <c r="H9" s="15"/>
-      <c r="I9" s="18"/>
-      <c r="K9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="18"/>
       <c r="L9" s="15"/>
-      <c r="M9" s="11"/>
+      <c r="M9" s="15"/>
       <c r="N9" s="11"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="15"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="9"/>
       <c r="Q9" s="15"/>
-    </row>
-    <row r="10" spans="1:28">
+      <c r="R9" s="15"/>
+    </row>
+    <row r="10" spans="1:29">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="15"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="15"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="9"/>
       <c r="L10" s="15"/>
-      <c r="M10" s="11"/>
+      <c r="M10" s="15"/>
       <c r="N10" s="11"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="15"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="9"/>
       <c r="Q10" s="15"/>
-    </row>
-    <row r="11" spans="1:28">
-      <c r="O11" s="13"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:28">
-      <c r="O12" s="13"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:28">
-      <c r="O13" s="13"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:28">
-      <c r="O14" s="13"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:28">
-      <c r="O15" s="13"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:28">
-      <c r="O16" s="13"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="15:16">
-      <c r="O17" s="13"/>
-      <c r="P17" s="1"/>
+      <c r="R10" s="15"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="P11" s="13"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="P12" s="13"/>
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="P13" s="13"/>
+      <c r="Q13" s="1"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="P14" s="13"/>
+      <c r="Q14" s="1"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="P15" s="13"/>
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="P16" s="13"/>
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="16:17">
+      <c r="P17" s="13"/>
+      <c r="Q17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5BEECEA4-F1BD-8D4A-93E2-C11D4CADC5DF}">
           <x14:formula1>
             <xm:f>#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>J6</xm:sqref>
+          <xm:sqref>K6</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{87CC3E0A-FE7A-3B4B-906C-582F0788E53E}">
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1016</xm:f>
           </x14:formula1>
-          <xm:sqref>P6 P4</xm:sqref>
+          <xm:sqref>Q6 Q4</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2511,7 +2581,7 @@
         <v>116</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>114</v>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676F07F5-2960-644F-A85E-69C1AC786D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AC4BEB-A465-EF45-AED3-3748F13C2A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51380" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51380" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
     <sheet name="Localization" sheetId="8" r:id="rId2"/>
     <sheet name="Spawner" sheetId="23" r:id="rId3"/>
     <sheet name="Player" sheetId="4" r:id="rId4"/>
-    <sheet name="Item" sheetId="19" r:id="rId5"/>
-    <sheet name="FactionRelation" sheetId="24" r:id="rId6"/>
-    <sheet name="Grade" sheetId="22" r:id="rId7"/>
-    <sheet name="SynergeBiome" sheetId="20" r:id="rId8"/>
-    <sheet name="SynergeElement" sheetId="21" r:id="rId9"/>
-    <sheet name="Skill" sheetId="27" r:id="rId10"/>
+    <sheet name="Projectile" sheetId="28" r:id="rId5"/>
+    <sheet name="Item" sheetId="19" r:id="rId6"/>
+    <sheet name="FactionRelation" sheetId="24" r:id="rId7"/>
+    <sheet name="Grade" sheetId="22" r:id="rId8"/>
+    <sheet name="SynergeBiome" sheetId="20" r:id="rId9"/>
+    <sheet name="SynergeElement" sheetId="21" r:id="rId10"/>
+    <sheet name="Skill" sheetId="27" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="151">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -614,14 +615,34 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_Human_MeleeAttack_1</t>
-  </si>
-  <si>
     <t>MeleeAttack</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>skillTimeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Projectile/HumanProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Projectile_Hit_1</t>
+  </si>
+  <si>
+    <t>3,5,Projectile_Human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collisionCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Human_Projectile_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 사용 시.주변 적 서치용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1821,19 +1842,114 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
+        <v>SynergeElement_Test</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="C4" s="9"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="C5" s="9"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
+          <x14:formula1>
+            <xm:f>Enum!$I$2:$I$1016</xm:f>
+          </x14:formula1>
+          <xm:sqref>B5:B6</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="19.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:31">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -1879,20 +1995,22 @@
       </c>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="5"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="8"/>
       <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
+      <c r="X1" s="5"/>
       <c r="Y1" s="8"/>
       <c r="Z1" s="8"/>
       <c r="AA1" s="8"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -1909,7 +2027,7 @@
         <v>31</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>139</v>
@@ -1928,27 +2046,31 @@
       </c>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="6"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="8"/>
       <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
+      <c r="X2" s="6"/>
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
       <c r="AA2" s="8"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AB2" s="8"/>
+      <c r="AC2" s="8"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+    </row>
+    <row r="3" spans="1:31">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
+      <c r="G3" s="9" t="s">
+        <v>150</v>
+      </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
       <c r="J3" s="9"/>
@@ -1965,9 +2087,11 @@
       </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-    </row>
-    <row r="4" spans="1:29">
+      <c r="R3" s="9"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+    </row>
+    <row r="4" spans="1:31">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4:F4)</f>
         <v>Skill_Human_Projectile_1</v>
@@ -2001,16 +2125,16 @@
       <c r="L4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="15">
-        <v>5</v>
-      </c>
+      <c r="M4" s="15"/>
       <c r="N4" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="O4" s="11"/>
-      <c r="R4" s="15"/>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="O4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="T4" s="15"/>
+    </row>
+    <row r="5" spans="1:31">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5:F5)</f>
         <v>Skill_Projectile_Hit_1</v>
@@ -2028,7 +2152,9 @@
         <v>1</v>
       </c>
       <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="G5" s="9">
+        <v>1</v>
+      </c>
       <c r="H5" s="15" t="s">
         <v>66</v>
       </c>
@@ -2043,17 +2169,21 @@
         <v>129</v>
       </c>
       <c r="M5" s="15">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="O5" s="11"/>
+      <c r="O5" s="11">
+        <v>5</v>
+      </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-    </row>
-    <row r="6" spans="1:29">
+      <c r="R5" s="9"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+    </row>
+    <row r="6" spans="1:31">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6:F6)</f>
         <v>Skill_Human_MeleeAttack_1</v>
@@ -2065,7 +2195,7 @@
         <v>47</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" s="9">
         <v>1</v>
@@ -2096,7 +2226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7" spans="1:31">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2104,17 +2234,19 @@
       <c r="G7" s="9"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+    </row>
+    <row r="8" spans="1:31">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2122,17 +2254,19 @@
       <c r="G8" s="9"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-    </row>
-    <row r="9" spans="1:29">
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+    </row>
+    <row r="9" spans="1:31">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2140,16 +2274,18 @@
       <c r="G9" s="9"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="18"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-    </row>
-    <row r="10" spans="1:29">
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="18"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+    </row>
+    <row r="10" spans="1:31">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2157,51 +2293,53 @@
       <c r="G10" s="9"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-    </row>
-    <row r="11" spans="1:29">
-      <c r="P11" s="13"/>
-      <c r="Q11" s="1"/>
-    </row>
-    <row r="12" spans="1:29">
-      <c r="P12" s="13"/>
-      <c r="Q12" s="1"/>
-    </row>
-    <row r="13" spans="1:29">
-      <c r="P13" s="13"/>
-      <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="1:29">
-      <c r="P14" s="13"/>
-      <c r="Q14" s="1"/>
-    </row>
-    <row r="15" spans="1:29">
-      <c r="P15" s="13"/>
-      <c r="Q15" s="1"/>
-    </row>
-    <row r="16" spans="1:29">
-      <c r="P16" s="13"/>
-      <c r="Q16" s="1"/>
-    </row>
-    <row r="17" spans="16:17">
-      <c r="P17" s="13"/>
-      <c r="Q17" s="1"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+    </row>
+    <row r="11" spans="1:31">
+      <c r="R11" s="13"/>
+      <c r="S11" s="1"/>
+    </row>
+    <row r="12" spans="1:31">
+      <c r="R12" s="13"/>
+      <c r="S12" s="1"/>
+    </row>
+    <row r="13" spans="1:31">
+      <c r="R13" s="13"/>
+      <c r="S13" s="1"/>
+    </row>
+    <row r="14" spans="1:31">
+      <c r="R14" s="13"/>
+      <c r="S14" s="1"/>
+    </row>
+    <row r="15" spans="1:31">
+      <c r="R15" s="13"/>
+      <c r="S15" s="1"/>
+    </row>
+    <row r="16" spans="1:31">
+      <c r="R16" s="13"/>
+      <c r="S16" s="1"/>
+    </row>
+    <row r="17" spans="18:19">
+      <c r="R17" s="13"/>
+      <c r="S17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5BEECEA4-F1BD-8D4A-93E2-C11D4CADC5DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{27A11A15-E75D-9B40-BA34-50931BED73C4}">
           <x14:formula1>
             <xm:f>#REF!</xm:f>
           </x14:formula1>
@@ -2211,7 +2349,7 @@
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1016</xm:f>
           </x14:formula1>
-          <xm:sqref>Q6 Q4</xm:sqref>
+          <xm:sqref>S6 S4 Q6 Q4</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2581,7 +2719,7 @@
         <v>116</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>114</v>
@@ -2741,6 +2879,9 @@
       </c>
     </row>
     <row r="7" spans="1:22">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2784,6 +2925,7 @@
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
+      <c r="G12" s="4"/>
       <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:22">
@@ -2949,6 +3091,175 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="11"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="11"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
+        <v>Projectile_Human</v>
+      </c>
+      <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="9">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="11"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="11"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
   <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -3409,7 +3720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
   <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -3706,7 +4017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -3885,7 +4196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -3988,96 +4299,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
-        <v>SynergeElement_Test</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="C5" s="9"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
-          <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1016</xm:f>
-          </x14:formula1>
-          <xm:sqref>B5:B6</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
 </file>
--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AC4BEB-A465-EF45-AED3-3748F13C2A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46156A65-0BD1-9441-8897-C17D0BC75D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51380" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
@@ -17,13 +17,14 @@
     <sheet name="Localization" sheetId="8" r:id="rId2"/>
     <sheet name="Spawner" sheetId="23" r:id="rId3"/>
     <sheet name="Player" sheetId="4" r:id="rId4"/>
-    <sheet name="Projectile" sheetId="28" r:id="rId5"/>
-    <sheet name="Item" sheetId="19" r:id="rId6"/>
-    <sheet name="FactionRelation" sheetId="24" r:id="rId7"/>
-    <sheet name="Grade" sheetId="22" r:id="rId8"/>
-    <sheet name="SynergeBiome" sheetId="20" r:id="rId9"/>
-    <sheet name="SynergeElement" sheetId="21" r:id="rId10"/>
-    <sheet name="Skill" sheetId="27" r:id="rId11"/>
+    <sheet name="Item" sheetId="19" r:id="rId5"/>
+    <sheet name="FactionRelation" sheetId="24" r:id="rId6"/>
+    <sheet name="Grade" sheetId="22" r:id="rId7"/>
+    <sheet name="SynergeBiome" sheetId="20" r:id="rId8"/>
+    <sheet name="SynergeElement" sheetId="21" r:id="rId9"/>
+    <sheet name="Skill" sheetId="27" r:id="rId10"/>
+    <sheet name="Buff" sheetId="29" r:id="rId11"/>
+    <sheet name="Projectile" sheetId="28" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="157">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,10 +79,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>List&lt;string&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>description</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -643,6 +652,22 @@
   </si>
   <si>
     <t>스킬 사용 시.주변 적 서치용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxStack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startSkillKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endSkillKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1271,7 +1296,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1282,7 +1307,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1290,10 +1315,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1301,10 +1326,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1312,10 +1337,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1323,10 +1348,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1334,10 +1359,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1345,10 +1370,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1356,10 +1381,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1367,10 +1392,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1378,10 +1403,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1389,10 +1414,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1400,10 +1425,10 @@
         <v>5</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1411,10 +1436,10 @@
         <v>6</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1422,10 +1447,10 @@
         <v>7</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1433,10 +1458,10 @@
         <v>8</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1444,10 +1469,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1455,10 +1480,10 @@
         <v>2</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E21" s="11"/>
     </row>
@@ -1467,10 +1492,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E22" s="11"/>
     </row>
@@ -1479,10 +1504,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E23" s="11"/>
     </row>
@@ -1491,10 +1516,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E24" s="11"/>
     </row>
@@ -1503,10 +1528,10 @@
         <v>2</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E25" s="11"/>
     </row>
@@ -1515,10 +1540,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E26" s="12"/>
     </row>
@@ -1527,10 +1552,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1538,7 +1563,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>7</v>
@@ -1549,10 +1574,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1560,10 +1585,10 @@
         <v>2</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1571,10 +1596,10 @@
         <v>3</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1582,10 +1607,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1593,10 +1618,10 @@
         <v>2</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1604,10 +1629,10 @@
         <v>3</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1615,10 +1640,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1626,10 +1651,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1637,10 +1662,10 @@
         <v>2</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1648,10 +1673,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1659,10 +1684,10 @@
         <v>2</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1670,10 +1695,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -1681,10 +1706,10 @@
         <v>2</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -1692,10 +1717,10 @@
         <v>3</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -1703,10 +1728,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -1842,98 +1867,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
-        <v>SynergeElement_Test</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="C5" s="9"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
-          <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1016</xm:f>
-          </x14:formula1>
-          <xm:sqref>B5:B6</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
   <dimension ref="A1:AE17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -1967,7 +1900,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>0</v>
@@ -1976,22 +1909,22 @@
         <v>0</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
@@ -2018,31 +1951,31 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>140</v>
-      </c>
       <c r="N2" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
@@ -2069,21 +2002,21 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
       <c r="J3" s="9"/>
       <c r="K3" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L3" s="15"/>
       <c r="M3" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N3" s="11"/>
       <c r="O3" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="15"/>
@@ -2097,13 +2030,13 @@
         <v>Skill_Human_Projectile_1</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E4" s="9">
         <v>1</v>
@@ -2113,24 +2046,24 @@
         <v>10</v>
       </c>
       <c r="H4" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="15" t="s">
-        <v>64</v>
-      </c>
       <c r="J4" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M4" s="15"/>
       <c r="N4" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="T4" s="15"/>
     </row>
@@ -2140,13 +2073,13 @@
         <v>Skill_Projectile_Hit_1</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E5" s="9">
         <v>1</v>
@@ -2156,23 +2089,23 @@
         <v>1</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M5" s="15">
         <v>0.6</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O5" s="11">
         <v>5</v>
@@ -2189,13 +2122,13 @@
         <v>Skill_Human_MeleeAttack_1</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E6" s="9">
         <v>1</v>
@@ -2205,22 +2138,22 @@
         <v>1</v>
       </c>
       <c r="H6" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="I6" s="15" t="s">
-        <v>64</v>
-      </c>
       <c r="J6" s="18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M6" s="15">
         <v>0.1</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O6" s="11">
         <v>5</v>
@@ -2354,6 +2287,316 @@
       </x14:dataValidations>
     </ext>
   </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C8E724-28BD-8649-A64E-E00F04A859F7}">
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3:E3)</f>
+        <v>Buff_1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="9">
+        <v>1</v>
+      </c>
+      <c r="H3" s="9">
+        <v>1</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="11"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="11"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
+        <v>Projectile_Human</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="9">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="11"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="11"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2397,13 +2640,13 @@
         <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -2418,16 +2661,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -2443,19 +2686,19 @@
         <v>Spawner_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G3" s="20">
         <v>100100</v>
@@ -2623,25 +2866,25 @@
         <v>0</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -2657,37 +2900,37 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="M2" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -2707,40 +2950,40 @@
         <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>113</v>
-      </c>
       <c r="J3" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M3" s="9">
         <v>100</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -2752,40 +2995,40 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>113</v>
-      </c>
       <c r="J4" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M4" s="9">
         <v>100</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2797,40 +3040,40 @@
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>113</v>
-      </c>
       <c r="J5" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M5" s="9">
         <v>100</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2842,40 +3085,40 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>113</v>
-      </c>
       <c r="J6" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M6" s="9">
         <v>100</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3091,175 +3334,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="11"/>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="11"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
-        <v>Projectile_Human</v>
-      </c>
-      <c r="B3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="9">
-        <v>1</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="11"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="11"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="11"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="9"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
   <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -3282,10 +3356,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>0</v>
@@ -3294,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>0</v>
@@ -3326,34 +3400,34 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -3370,38 +3444,38 @@
         <v>Item_WoodSword</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="15" t="s">
         <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>9</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -3413,38 +3487,38 @@
         <v>Item_WoodStaff</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" s="15" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>9</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -3456,38 +3530,38 @@
         <v>Item_WoodBow</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" s="15" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>9</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -3509,38 +3583,38 @@
         <v>Item_Human</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="18" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -3552,38 +3626,38 @@
         <v>Item_Dog</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="18" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -3595,38 +3669,38 @@
         <v>Item_Eagle</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="18" t="s">
         <v>7</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -3638,38 +3712,38 @@
         <v>Item_Snake</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="18" t="s">
         <v>7</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N10">
         <v>1</v>
@@ -3720,7 +3794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
   <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -3742,7 +3816,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -3760,7 +3834,7 @@
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -3775,23 +3849,23 @@
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="H2" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -3807,22 +3881,22 @@
         <v>FactionRelation_Hero</v>
       </c>
       <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9" t="str">
@@ -3840,22 +3914,22 @@
         <v>FactionRelation_Faction2</v>
       </c>
       <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="str">
@@ -3873,22 +3947,22 @@
         <v>FactionRelation_Faction3</v>
       </c>
       <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="9" t="str">
@@ -3906,22 +3980,22 @@
         <v>FactionRelation_Faction4</v>
       </c>
       <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="9" t="str">
@@ -4017,7 +4091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -4031,7 +4105,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>0</v>
@@ -4047,13 +4121,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4062,19 +4136,19 @@
         <v>Grade_Common</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4083,19 +4157,19 @@
         <v>Grade_Uncommon</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -4106,19 +4180,19 @@
         <v>Grade_Rare</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -4129,19 +4203,19 @@
         <v>Grade_Epic</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -4152,19 +4226,19 @@
         <v>Grade_Unique</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E7" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>74</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>72</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -4175,19 +4249,19 @@
         <v>Grade_Legend</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4196,7 +4270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -4215,7 +4289,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -4229,13 +4303,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4244,19 +4318,19 @@
         <v>SynergeBiome_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4299,4 +4373,96 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
+        <v>SynergeElement_Test</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="C4" s="9"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="C5" s="9"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
+          <x14:formula1>
+            <xm:f>Enum!$I$2:$I$1016</xm:f>
+          </x14:formula1>
+          <xm:sqref>B5:B6</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Toy\Project\FactoryProject\Generated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46156A65-0BD1-9441-8897-C17D0BC75D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC60843-E4F8-4563-AFAB-E1CE89B42B50}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51380" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51380" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="3" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -31,21 +31,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="164">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -651,10 +642,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스킬 사용 시.주변 적 서치용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>duration</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -668,6 +655,38 @@
   </si>
   <si>
     <t>endSkillKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Projectile Example</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Attack Example</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 사용 가능 범위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Stat Example</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BiomeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biomeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ElementType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elementType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -675,7 +694,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1237,13 +1256,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
   <dimension ref="A1:S69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -1266,7 +1285,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -1277,7 +1296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -1288,7 +1307,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -1299,7 +1318,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -1310,7 +1329,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1321,7 +1340,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -1332,7 +1351,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1343,7 +1362,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1354,7 +1373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -1365,7 +1384,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -1376,7 +1395,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1387,7 +1406,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -1398,7 +1417,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -1409,7 +1428,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -1420,7 +1439,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -1431,7 +1450,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>6</v>
       </c>
@@ -1442,7 +1461,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>7</v>
       </c>
@@ -1453,7 +1472,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>8</v>
       </c>
@@ -1464,7 +1483,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1475,7 +1494,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -1487,7 +1506,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1499,7 +1518,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -1511,7 +1530,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1523,7 +1542,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -1535,7 +1554,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1547,7 +1566,7 @@
       </c>
       <c r="E26" s="12"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -1558,7 +1577,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>5</v>
       </c>
@@ -1569,7 +1588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1580,7 +1599,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -1591,7 +1610,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -1602,7 +1621,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1613,7 +1632,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -1624,7 +1643,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>3</v>
       </c>
@@ -1635,7 +1654,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -1646,7 +1665,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -1657,7 +1676,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>2</v>
       </c>
@@ -1668,7 +1687,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -1679,7 +1698,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>2</v>
       </c>
@@ -1690,7 +1709,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -1701,7 +1720,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -1712,7 +1731,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>3</v>
       </c>
@@ -1723,7 +1742,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>4</v>
       </c>
@@ -1740,119 +1759,119 @@
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="1"/>
       <c r="B44" s="11"/>
       <c r="C44" s="1"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="1"/>
       <c r="B45" s="11"/>
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="1"/>
       <c r="B46" s="11"/>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="1"/>
       <c r="B47" s="11"/>
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="1"/>
       <c r="B48" s="11"/>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="1"/>
       <c r="B49" s="11"/>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="1"/>
       <c r="B50" s="11"/>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" s="1"/>
       <c r="B51" s="11"/>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" s="1"/>
       <c r="B52" s="11"/>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" s="1"/>
       <c r="B53" s="11"/>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="1"/>
       <c r="B54" s="11"/>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" s="1"/>
       <c r="B55" s="11"/>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" s="1"/>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" s="1"/>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="1"/>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" s="1"/>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" s="1"/>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" s="1"/>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" s="1"/>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" s="1"/>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" s="1"/>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" s="1"/>
       <c r="C65" s="1"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" s="1"/>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" s="1"/>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" s="1"/>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="1"/>
     </row>
   </sheetData>
@@ -1868,21 +1887,21 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
-  <dimension ref="A1:AE17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <dimension ref="A1:AE15"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.53515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="19.3046875" customWidth="1"/>
+    <col min="12" max="12" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -1943,7 +1962,7 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -1994,7 +2013,7 @@
       <c r="AD2" s="6"/>
       <c r="AE2" s="6"/>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -2002,7 +2021,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
@@ -2024,285 +2043,223 @@
       <c r="S3" s="15"/>
       <c r="T3" s="15"/>
     </row>
-    <row r="4" spans="1:31">
-      <c r="A4" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B4:F4)</f>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R4" s="13"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="15"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="R5" s="13"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="15"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="R6" s="13"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
         <v>Skill_Human_Projectile_1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C7" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E7" s="9">
         <v>1</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9">
+      <c r="F7" s="9"/>
+      <c r="G7" s="9">
         <v>10</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H7" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I7" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="15" t="s">
+      <c r="K7" s="2"/>
+      <c r="L7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="11" t="s">
+      <c r="M7" s="15"/>
+      <c r="N7" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O7" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="T4" s="15"/>
-    </row>
-    <row r="5" spans="1:31">
-      <c r="A5" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B5:F5)</f>
+      <c r="R7" s="13"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="15"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R8" s="13"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="15"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="R9" s="13"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="15"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="T10" s="15"/>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
         <v>Skill_Projectile_Hit_1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B11" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C11" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E11" s="9">
         <v>1</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9">
+      <c r="F11" s="9"/>
+      <c r="G11" s="9">
         <v>1</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H11" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I11" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J11" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="15" t="s">
+      <c r="K11" s="2"/>
+      <c r="L11" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M11" s="15">
         <v>0.6</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O11" s="11">
         <v>5</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-    </row>
-    <row r="6" spans="1:31">
-      <c r="A6" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B6:F6)</f>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B12:F12)</f>
         <v>Skill_Human_MeleeAttack_1</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C12" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E12" s="9">
         <v>1</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9">
+      <c r="F12" s="9"/>
+      <c r="G12" s="9">
         <v>1</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H12" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I12" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J12" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L12" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M12" s="15">
         <v>0.1</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N12" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O12" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-    </row>
-    <row r="8" spans="1:31">
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-    </row>
-    <row r="9" spans="1:31">
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="18"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-    </row>
-    <row r="10" spans="1:31">
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-    </row>
-    <row r="11" spans="1:31">
-      <c r="R11" s="13"/>
-      <c r="S11" s="1"/>
-    </row>
-    <row r="12" spans="1:31">
-      <c r="R12" s="13"/>
-      <c r="S12" s="1"/>
-    </row>
-    <row r="13" spans="1:31">
-      <c r="R13" s="13"/>
-      <c r="S13" s="1"/>
-    </row>
-    <row r="14" spans="1:31">
-      <c r="R14" s="13"/>
-      <c r="S14" s="1"/>
-    </row>
-    <row r="15" spans="1:31">
-      <c r="R15" s="13"/>
-      <c r="S15" s="1"/>
-    </row>
-    <row r="16" spans="1:31">
-      <c r="R16" s="13"/>
-      <c r="S16" s="1"/>
-    </row>
-    <row r="17" spans="18:19">
-      <c r="R17" s="13"/>
-      <c r="S17" s="1"/>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A13" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A14" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
+        <v>159</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K12" xr:uid="{27A11A15-E75D-9B40-BA34-50931BED73C4}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{27A11A15-E75D-9B40-BA34-50931BED73C4}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>K6</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{87CC3E0A-FE7A-3B4B-906C-582F0788E53E}">
-          <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1016</xm:f>
-          </x14:formula1>
-          <xm:sqref>S6 S4 Q6 Q4</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C8E724-28BD-8649-A64E-E00F04A859F7}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2338,20 +2295,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>32</v>
@@ -2360,13 +2317,13 @@
         <v>33</v>
       </c>
       <c r="K2" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="L2" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="L2" s="14" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3:E3)</f>
         <v>Buff_1</v>
@@ -2395,7 +2352,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2405,20 +2362,20 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
@@ -2428,24 +2385,25 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2476,7 +2434,7 @@
       <c r="N1" s="9"/>
       <c r="O1" s="11"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2503,7 +2461,7 @@
       <c r="N2" s="9"/>
       <c r="O2" s="11"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Projectile_Human</v>
@@ -2537,7 +2495,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2552,7 +2510,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="11"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2567,7 +2525,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="11"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2582,7 +2540,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="11"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2603,7 +2561,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9012A38-B8D5-894C-A1D0-EDAD32738ED4}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2613,22 +2571,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7454E3B-BCDE-5A49-BB39-4B30666D97F3}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.15234375" customWidth="1"/>
+    <col min="6" max="6" width="20.69140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.3046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.69140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2656,7 +2614,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2680,7 +2638,7 @@
       <c r="M2" s="9"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Spawner_Test</v>
@@ -2711,7 +2669,7 @@
       <c r="M3" s="9"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2725,7 +2683,7 @@
       <c r="M4" s="9"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2739,7 +2697,7 @@
       <c r="M5" s="9"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2755,7 +2713,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2771,7 +2729,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2785,7 +2743,7 @@
       <c r="M8" s="9"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2799,7 +2757,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2808,7 +2766,7 @@
       <c r="H10" s="9"/>
       <c r="L10" s="9"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2817,7 +2775,7 @@
       <c r="H11" s="9"/>
       <c r="L11" s="9"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2835,19 +2793,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A933480A-994B-A74A-B07D-EEB09A80B87F}">
   <dimension ref="A1:V32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.69140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="21.69140625" customWidth="1"/>
+    <col min="12" max="12" width="21.69140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2886,8 +2844,12 @@
       <c r="N1" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
+      <c r="O1" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>162</v>
+      </c>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
@@ -2895,7 +2857,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2932,8 +2894,12 @@
       <c r="N2" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
+      <c r="O2" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="14"/>
       <c r="S2" s="6"/>
@@ -2941,7 +2907,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Player_Human</v>
@@ -2986,7 +2952,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Player_Dog</v>
@@ -3031,7 +2997,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Player_Eagle</v>
@@ -3076,7 +3042,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
         <v>Player_Snake</v>
@@ -3121,7 +3087,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -3135,35 +3101,35 @@
       <c r="J7" s="11"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -3171,14 +3137,14 @@
       <c r="G12" s="4"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -3186,7 +3152,7 @@
       <c r="G14" s="3"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -3194,7 +3160,7 @@
       <c r="G15" s="4"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -3202,7 +3168,7 @@
       <c r="G16" s="4"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="3:10">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -3210,105 +3176,105 @@
       <c r="G17" s="4"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="3:10">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="3:10">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="3:10">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="3:10">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="3:10">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="3:10">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="3:10">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="3:10">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="3:10">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="3:10">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="3:10">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="3:10">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="3:10">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="3:10">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="3:10">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -3320,7 +3286,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FBA1699A-C505-8C41-9338-26277C216689}">
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1016</xm:f>
@@ -3336,15 +3302,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
   <dimension ref="A1:V14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3394,7 +3360,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -3438,7 +3404,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Item_WoodSword</v>
@@ -3481,7 +3447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Item_WoodStaff</v>
@@ -3524,7 +3490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Item_WoodBow</v>
@@ -3567,7 +3533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -3577,7 +3543,7 @@
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v>Item_Human</v>
@@ -3620,7 +3586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B8,C8)</f>
         <v>Item_Dog</v>
@@ -3663,7 +3629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B9,C9)</f>
         <v>Item_Eagle</v>
@@ -3706,7 +3672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B10,C10)</f>
         <v>Item_Snake</v>
@@ -3749,44 +3715,43 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="I14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6" xr:uid="{17B1ACDF-E711-444F-BA32-32976EC6EADF}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B59ECF9-BEB9-264A-A494-976028F5B748}">
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1016</xm:f>
           </x14:formula1>
           <xm:sqref>L6 P3:P7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{17B1ACDF-E711-444F-BA32-32976EC6EADF}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>F6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3797,17 +3762,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.53515625" customWidth="1"/>
+    <col min="4" max="4" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3844,7 +3809,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3875,7 +3840,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,D3)</f>
         <v>FactionRelation_Hero</v>
@@ -3908,7 +3873,7 @@
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,D4)</f>
         <v>FactionRelation_Faction2</v>
@@ -3941,7 +3906,7 @@
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,D5)</f>
         <v>FactionRelation_Faction3</v>
@@ -3974,7 +3939,7 @@
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,D6)</f>
         <v>FactionRelation_Faction4</v>
@@ -4003,7 +3968,7 @@
         <v>Hostile,Hostile,Hostile,Friendly</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="15"/>
@@ -4016,7 +3981,7 @@
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="15"/>
@@ -4029,7 +3994,7 @@
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="15"/>
@@ -4042,7 +4007,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="15"/>
@@ -4055,19 +4020,19 @@
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -4094,9 +4059,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4116,7 +4081,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4130,9 +4095,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
+        <f t="shared" ref="A3:A8" si="0">_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Grade_Common</v>
       </c>
       <c r="B3" t="s">
@@ -4151,9 +4116,9 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
+        <f t="shared" si="0"/>
         <v>Grade_Uncommon</v>
       </c>
       <c r="B4" t="s">
@@ -4174,9 +4139,9 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
+        <f t="shared" si="0"/>
         <v>Grade_Rare</v>
       </c>
       <c r="B5" t="s">
@@ -4197,9 +4162,9 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
+        <f t="shared" si="0"/>
         <v>Grade_Epic</v>
       </c>
       <c r="B6" t="s">
@@ -4220,9 +4185,9 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
+        <f t="shared" si="0"/>
         <v>Grade_Unique</v>
       </c>
       <c r="B7" t="s">
@@ -4243,9 +4208,9 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B8,C8)</f>
+        <f t="shared" si="0"/>
         <v>Grade_Legend</v>
       </c>
       <c r="B8" t="s">
@@ -4273,14 +4238,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4298,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4312,7 +4277,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeBiome_Test</v>
@@ -4333,27 +4298,27 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="7"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="7"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
-        <f t="shared" ref="A7:A8" si="0">_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
+        <f t="shared" ref="A7" si="0">_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v/>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
     </row>
@@ -4378,12 +4343,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4401,7 +4366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4415,7 +4380,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeElement_Test</v>
@@ -4436,16 +4401,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
     </row>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Toy\Project\FactoryProject\Generated\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC60843-E4F8-4563-AFAB-E1CE89B42B50}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAFF3A4-0BEB-984B-95A1-AB4A0DF70B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51380" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="3" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -31,12 +31,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="167">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -687,6 +696,18 @@
   </si>
   <si>
     <t>elementType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApplyStat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Str,5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +715,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -872,7 +893,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -914,31 +935,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1256,13 +1268,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
   <dimension ref="A1:S69"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="13.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -1285,7 +1297,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:19">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -1296,7 +1308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:19">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -1307,7 +1319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:19">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -1318,7 +1330,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -1329,7 +1341,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1340,7 +1352,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -1351,7 +1363,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1362,7 +1374,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1373,7 +1385,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -1384,7 +1396,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -1395,7 +1407,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1406,7 +1418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -1417,7 +1429,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -1428,7 +1440,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -1439,7 +1451,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -1450,7 +1462,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>6</v>
       </c>
@@ -1461,7 +1473,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>7</v>
       </c>
@@ -1472,7 +1484,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>8</v>
       </c>
@@ -1483,7 +1495,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1494,7 +1506,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -1506,7 +1518,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1518,7 +1530,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -1530,7 +1542,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1542,7 +1554,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -1554,7 +1566,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1566,7 +1578,7 @@
       </c>
       <c r="E26" s="12"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -1577,7 +1589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>5</v>
       </c>
@@ -1588,7 +1600,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1599,7 +1611,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -1610,7 +1622,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -1621,7 +1633,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1632,7 +1644,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -1643,7 +1655,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11">
       <c r="A34" s="1">
         <v>3</v>
       </c>
@@ -1654,7 +1666,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -1665,7 +1677,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -1676,7 +1688,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11">
       <c r="A37" s="1">
         <v>2</v>
       </c>
@@ -1687,7 +1699,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -1698,7 +1710,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11">
       <c r="A39" s="1">
         <v>2</v>
       </c>
@@ -1709,7 +1721,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -1720,7 +1732,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -1731,7 +1743,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11">
       <c r="A42" s="1">
         <v>3</v>
       </c>
@@ -1742,7 +1754,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11">
       <c r="A43" s="1">
         <v>4</v>
       </c>
@@ -1754,124 +1766,128 @@
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A44" s="1"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11">
+      <c r="A44" s="1">
+        <v>5</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="1"/>
       <c r="B45" s="11"/>
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11">
       <c r="A46" s="1"/>
       <c r="B46" s="11"/>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11">
       <c r="A47" s="1"/>
       <c r="B47" s="11"/>
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11">
       <c r="A48" s="1"/>
       <c r="B48" s="11"/>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3">
       <c r="A49" s="1"/>
       <c r="B49" s="11"/>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3">
       <c r="A50" s="1"/>
       <c r="B50" s="11"/>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3">
       <c r="A51" s="1"/>
       <c r="B51" s="11"/>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3">
       <c r="A52" s="1"/>
       <c r="B52" s="11"/>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3">
       <c r="A53" s="1"/>
       <c r="B53" s="11"/>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3">
       <c r="A54" s="1"/>
       <c r="B54" s="11"/>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3">
       <c r="A55" s="1"/>
       <c r="B55" s="11"/>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3">
       <c r="A56" s="1"/>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3">
       <c r="A57" s="1"/>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3">
       <c r="A58" s="1"/>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3">
       <c r="A59" s="1"/>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3">
       <c r="A60" s="1"/>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3">
       <c r="A61" s="1"/>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3">
       <c r="A62" s="1"/>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3">
       <c r="A63" s="1"/>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3">
       <c r="A64" s="1"/>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3">
       <c r="A65" s="1"/>
       <c r="C65" s="1"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3">
       <c r="A66" s="1"/>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3">
       <c r="A67" s="1"/>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3">
       <c r="A68" s="1"/>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3">
       <c r="A69" s="1"/>
     </row>
   </sheetData>
@@ -1887,21 +1903,21 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
-  <dimension ref="A1:AE15"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AE16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="23.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.3046875" customWidth="1"/>
-    <col min="12" max="12" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="19.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -1918,7 +1934,7 @@
       <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="19" t="s">
         <v>80</v>
       </c>
       <c r="H1" s="8" t="s">
@@ -1962,14 +1978,14 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="19" t="s">
         <v>144</v>
       </c>
       <c r="H2" s="8" t="s">
@@ -2013,7 +2029,7 @@
       <c r="AD2" s="6"/>
       <c r="AE2" s="6"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -2023,13 +2039,10 @@
       <c r="G3" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
       <c r="J3" s="9"/>
       <c r="K3" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="L3" s="15"/>
       <c r="M3" s="2" t="s">
         <v>139</v>
       </c>
@@ -2038,35 +2051,30 @@
         <v>139</v>
       </c>
       <c r="P3" s="9"/>
-      <c r="Q3" s="15"/>
       <c r="R3" s="9"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:31">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="R4" s="13"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="15"/>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:31">
       <c r="A5" s="7" t="s">
         <v>156</v>
       </c>
       <c r="R5" s="13"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="15"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:31">
       <c r="A6" s="7" t="s">
         <v>156</v>
       </c>
       <c r="R6" s="13"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
         <v>Skill_Human_Projectile_1</v>
@@ -2087,20 +2095,19 @@
       <c r="G7" s="9">
         <v>10</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" t="s">
         <v>66</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>128</v>
       </c>
       <c r="K7" s="2"/>
-      <c r="L7" s="15" t="s">
+      <c r="L7" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="15"/>
       <c r="N7" s="11" t="s">
         <v>126</v>
       </c>
@@ -2109,31 +2116,27 @@
       </c>
       <c r="R7" s="13"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="15"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:31">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="R8" s="13"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="15"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:31">
       <c r="A9" s="7" t="s">
         <v>157</v>
       </c>
       <c r="R9" s="13"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="15"/>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:31">
       <c r="A10" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="T10" s="15"/>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
         <v>Skill_Projectile_Hit_1</v>
@@ -2154,20 +2157,20 @@
       <c r="G11" s="9">
         <v>1</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" t="s">
         <v>67</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>128</v>
       </c>
       <c r="K11" s="2"/>
-      <c r="L11" s="15" t="s">
+      <c r="L11" t="s">
         <v>131</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11">
         <v>0.6</v>
       </c>
       <c r="N11" s="11" t="s">
@@ -2177,7 +2180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:31">
       <c r="A12" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B12:F12)</f>
         <v>Skill_Human_MeleeAttack_1</v>
@@ -2198,19 +2201,19 @@
       <c r="G12" s="9">
         <v>1</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" t="s">
         <v>68</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" t="s">
         <v>66</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" t="s">
         <v>131</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12">
         <v>0.1</v>
       </c>
       <c r="N12" s="11" t="s">
@@ -2220,19 +2223,61 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:31">
       <c r="A13" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:31">
       <c r="A14" s="7" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:31">
       <c r="A15" s="7" t="s">
         <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
+      <c r="A16" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B16:F16)</f>
+        <v>Skill_Stat_1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="M16">
+        <v>0.1</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2250,16 +2295,16 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C8E724-28BD-8649-A64E-E00F04A859F7}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.15234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2288,14 +2333,14 @@
       <c r="J1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2323,7 +2368,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3:E3)</f>
         <v>Buff_1</v>
@@ -2352,7 +2397,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2362,20 +2407,20 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12">
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12">
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12">
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
@@ -2392,18 +2437,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2434,7 +2479,7 @@
       <c r="N1" s="9"/>
       <c r="O1" s="11"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2461,7 +2506,7 @@
       <c r="N2" s="9"/>
       <c r="O2" s="11"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Projectile_Human</v>
@@ -2495,7 +2540,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2510,7 +2555,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="11"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2525,7 +2570,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="11"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2536,11 +2581,11 @@
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="19"/>
+      <c r="M6" s="11"/>
       <c r="N6" s="9"/>
       <c r="O6" s="11"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2561,7 +2606,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9012A38-B8D5-894C-A1D0-EDAD32738ED4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2571,22 +2616,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7454E3B-BCDE-5A49-BB39-4B30666D97F3}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="4" max="4" width="19.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.15234375" customWidth="1"/>
-    <col min="6" max="6" width="20.69140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.3046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.69140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2614,7 +2659,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2638,7 +2683,7 @@
       <c r="M2" s="9"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Spawner_Test</v>
@@ -2658,7 +2703,7 @@
       <c r="F3" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="17">
         <v>100100</v>
       </c>
       <c r="H3" s="9"/>
@@ -2669,7 +2714,7 @@
       <c r="M3" s="9"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2683,7 +2728,7 @@
       <c r="M4" s="9"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2697,7 +2742,7 @@
       <c r="M5" s="9"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2713,7 +2758,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2729,7 +2774,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2743,7 +2788,7 @@
       <c r="M8" s="9"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2757,7 +2802,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2766,7 +2811,7 @@
       <c r="H10" s="9"/>
       <c r="L10" s="9"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2775,7 +2820,7 @@
       <c r="H11" s="9"/>
       <c r="L11" s="9"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2793,19 +2838,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A933480A-994B-A74A-B07D-EEB09A80B87F}">
   <dimension ref="A1:V32"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21.69140625" customWidth="1"/>
-    <col min="12" max="12" width="21.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2829,7 +2874,7 @@
       <c r="I1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="15" t="s">
         <v>31</v>
       </c>
       <c r="K1" s="8" t="s">
@@ -2857,7 +2902,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2879,7 +2924,7 @@
       <c r="I2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="16" t="s">
         <v>62</v>
       </c>
       <c r="K2" s="8" t="s">
@@ -2907,7 +2952,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Player_Human</v>
@@ -2952,7 +2997,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Player_Dog</v>
@@ -2997,7 +3042,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Player_Eagle</v>
@@ -3042,7 +3087,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
         <v>Player_Snake</v>
@@ -3077,7 +3122,7 @@
       <c r="K6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="11" t="s">
         <v>91</v>
       </c>
       <c r="M6" s="9">
@@ -3087,7 +3132,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -3101,35 +3146,35 @@
       <c r="J7" s="11"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -3137,14 +3182,14 @@
       <c r="G12" s="4"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22">
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -3152,7 +3197,7 @@
       <c r="G14" s="3"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:22">
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -3160,7 +3205,7 @@
       <c r="G15" s="4"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:22">
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -3168,7 +3213,7 @@
       <c r="G16" s="4"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:10">
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -3176,105 +3221,105 @@
       <c r="G17" s="4"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:10">
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:10">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:10">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:10">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:10">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:10">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:10">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:10">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:10">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:10">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:10">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:10">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:10">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:10">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:10">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -3302,15 +3347,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
   <dimension ref="A1:V14"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3360,7 +3405,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -3404,7 +3449,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Item_WoodSword</v>
@@ -3422,10 +3467,10 @@
       <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" t="s">
         <v>68</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" t="s">
         <v>65</v>
       </c>
       <c r="I3" s="11" t="s">
@@ -3437,17 +3482,17 @@
       <c r="K3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" t="s">
         <v>11</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Item_WoodStaff</v>
@@ -3465,10 +3510,10 @@
       <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" t="s">
         <v>66</v>
       </c>
       <c r="I4" s="11" t="s">
@@ -3480,17 +3525,17 @@
       <c r="K4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" t="s">
         <v>11</v>
       </c>
       <c r="N4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Item_WoodBow</v>
@@ -3508,10 +3553,10 @@
       <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" t="s">
         <v>67</v>
       </c>
       <c r="I5" s="11" t="s">
@@ -3523,17 +3568,17 @@
       <c r="K5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" t="s">
         <v>53</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" t="s">
         <v>11</v>
       </c>
       <c r="N5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -3543,7 +3588,7 @@
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v>Item_Human</v>
@@ -3555,16 +3600,16 @@
         <v>49</v>
       </c>
       <c r="D7" s="9"/>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" t="s">
         <v>122</v>
       </c>
       <c r="I7" s="11" t="s">
@@ -3576,17 +3621,17 @@
       <c r="K7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="M7" t="s">
         <v>11</v>
       </c>
       <c r="N7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22">
       <c r="A8" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B8,C8)</f>
         <v>Item_Dog</v>
@@ -3598,16 +3643,16 @@
         <v>77</v>
       </c>
       <c r="D8" s="9"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" t="s">
         <v>123</v>
       </c>
       <c r="I8" s="11" t="s">
@@ -3619,17 +3664,17 @@
       <c r="K8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" t="s">
         <v>11</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22">
       <c r="A9" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B9,C9)</f>
         <v>Item_Eagle</v>
@@ -3641,16 +3686,16 @@
         <v>78</v>
       </c>
       <c r="D9" s="9"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="9" t="s">
         <v>7</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" t="s">
         <v>124</v>
       </c>
       <c r="I9" s="11" t="s">
@@ -3662,17 +3707,17 @@
       <c r="K9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" t="s">
         <v>53</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" t="s">
         <v>11</v>
       </c>
       <c r="N9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22">
       <c r="A10" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B10,C10)</f>
         <v>Item_Snake</v>
@@ -3684,16 +3729,16 @@
         <v>79</v>
       </c>
       <c r="D10" s="9"/>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="9" t="s">
         <v>7</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" t="s">
         <v>125</v>
       </c>
       <c r="I10" s="11" t="s">
@@ -3705,35 +3750,35 @@
       <c r="K10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" t="s">
         <v>53</v>
       </c>
-      <c r="M10" s="15" t="s">
+      <c r="M10" t="s">
         <v>11</v>
       </c>
       <c r="N10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22">
       <c r="I14" s="1"/>
     </row>
   </sheetData>
@@ -3762,17 +3807,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="21.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.53515625" customWidth="1"/>
-    <col min="4" max="4" width="10.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="26.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3795,7 +3840,7 @@
       <c r="H1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
@@ -3809,7 +3854,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3840,7 +3885,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,D3)</f>
         <v>FactionRelation_Hero</v>
@@ -3869,11 +3914,8 @@
         <v>Friendly,Hostile,Hostile,Hostile</v>
       </c>
       <c r="K3" s="9"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,D4)</f>
         <v>FactionRelation_Faction2</v>
@@ -3902,11 +3944,8 @@
         <v>Hostile,Friendly,Hostile,Hostile</v>
       </c>
       <c r="K4" s="9"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,D5)</f>
         <v>FactionRelation_Faction3</v>
@@ -3935,11 +3974,8 @@
         <v>Hostile,Hostile,Friendly,Hostile</v>
       </c>
       <c r="K5" s="9"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,D6)</f>
         <v>FactionRelation_Faction4</v>
@@ -3962,77 +3998,48 @@
       <c r="H6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I6" s="22"/>
       <c r="J6" s="9" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,E6:H6)</f>
         <v>Hostile,Hostile,Hostile,Friendly</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17">
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="18"/>
+      <c r="J7" s="9"/>
       <c r="K7" s="9"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:17">
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="18"/>
+      <c r="J8" s="9"/>
       <c r="K8" s="9"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="18"/>
+      <c r="J9" s="9"/>
       <c r="K9" s="9"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:17">
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="18"/>
+      <c r="J10" s="9"/>
       <c r="K10" s="9"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:17">
       <c r="D11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17">
       <c r="D12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17">
       <c r="D13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -4059,9 +4066,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4081,7 +4088,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4095,7 +4102,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10">
       <c r="A3" s="7" t="str">
         <f t="shared" ref="A3:A8" si="0">_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Grade_Common</v>
@@ -4109,14 +4116,14 @@
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10">
       <c r="A4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Uncommon</v>
@@ -4130,16 +4137,16 @@
       <c r="D4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" t="s">
         <v>71</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10">
       <c r="A5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Rare</v>
@@ -4153,16 +4160,16 @@
       <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" t="s">
         <v>72</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10">
       <c r="A6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Epic</v>
@@ -4176,16 +4183,16 @@
       <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" t="s">
         <v>73</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10">
       <c r="A7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Unique</v>
@@ -4199,16 +4206,16 @@
       <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" t="s">
         <v>74</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10">
       <c r="A8" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Legend</v>
@@ -4222,10 +4229,10 @@
       <c r="D8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4238,14 +4245,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="16.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4263,7 +4270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4277,7 +4284,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeBiome_Test</v>
@@ -4298,19 +4305,19 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="7"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" s="7"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" s="7"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="7" t="str">
         <f t="shared" ref="A7" si="0">_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v/>
@@ -4318,7 +4325,7 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
     </row>
@@ -4343,12 +4350,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="18.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4366,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4380,7 +4387,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeElement_Test</v>
@@ -4401,16 +4408,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
     </row>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Toy\Project\FactoryProject\Generated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAFF3A4-0BEB-984B-95A1-AB4A0DF70B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251E54E1-BC48-4B90-8A2E-BCC711D3D088}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -31,21 +31,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="172">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -659,14 +650,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>startSkillKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>endSkillKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>// Projectile Example</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -708,6 +691,34 @@
   </si>
   <si>
     <t>Str,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatModifier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GrantSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseSkillOnEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffEffectType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffEffectType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffEffectParam</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -715,7 +726,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1268,13 +1279,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
   <dimension ref="A1:S69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -1297,7 +1308,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -1308,7 +1319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -1319,7 +1330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -1330,7 +1341,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -1341,7 +1352,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1352,7 +1363,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -1363,7 +1374,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1374,7 +1385,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1385,7 +1396,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -1396,7 +1407,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -1407,7 +1418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1418,7 +1429,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -1429,7 +1440,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -1440,7 +1451,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -1451,7 +1462,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -1462,7 +1473,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>6</v>
       </c>
@@ -1473,7 +1484,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>7</v>
       </c>
@@ -1484,7 +1495,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>8</v>
       </c>
@@ -1495,7 +1506,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1506,7 +1517,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -1518,7 +1529,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1530,7 +1541,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -1542,7 +1553,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1554,7 +1565,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -1566,7 +1577,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1578,7 +1589,7 @@
       </c>
       <c r="E26" s="12"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -1589,7 +1600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>5</v>
       </c>
@@ -1600,7 +1611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1611,7 +1622,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -1622,7 +1633,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -1633,7 +1644,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1644,7 +1655,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -1655,7 +1666,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>3</v>
       </c>
@@ -1666,7 +1677,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -1677,7 +1688,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -1688,7 +1699,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>2</v>
       </c>
@@ -1699,7 +1710,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -1710,7 +1721,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>2</v>
       </c>
@@ -1721,7 +1732,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -1732,7 +1743,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -1743,7 +1754,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>3</v>
       </c>
@@ -1754,7 +1765,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>4</v>
       </c>
@@ -1769,7 +1780,7 @@
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -1777,117 +1788,135 @@
         <v>133</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A45" s="1">
+        <v>1</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="1"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="1"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="1"/>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="1"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="1"/>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="C45" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A46" s="1">
+        <v>2</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A47" s="1">
+        <v>3</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="1"/>
       <c r="B48" s="11"/>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="1"/>
       <c r="B49" s="11"/>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="1"/>
       <c r="B50" s="11"/>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" s="1"/>
       <c r="B51" s="11"/>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" s="1"/>
       <c r="B52" s="11"/>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" s="1"/>
       <c r="B53" s="11"/>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="1"/>
       <c r="B54" s="11"/>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" s="1"/>
       <c r="B55" s="11"/>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" s="1"/>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" s="1"/>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="1"/>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" s="1"/>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" s="1"/>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" s="1"/>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" s="1"/>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" s="1"/>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" s="1"/>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" s="1"/>
       <c r="C65" s="1"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" s="1"/>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" s="1"/>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" s="1"/>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="1"/>
     </row>
   </sheetData>
@@ -1898,26 +1927,27 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
   <dimension ref="A1:AE16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.53515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="19.3046875" customWidth="1"/>
+    <col min="12" max="12" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -1978,7 +2008,7 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2029,7 +2059,7 @@
       <c r="AD2" s="6"/>
       <c r="AE2" s="6"/>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -2037,7 +2067,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="2" t="s">
@@ -2053,28 +2083,28 @@
       <c r="P3" s="9"/>
       <c r="R3" s="9"/>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="R4" s="13"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R5" s="13"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R6" s="13"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
         <v>Skill_Human_Projectile_1</v>
@@ -2117,26 +2147,26 @@
       <c r="R7" s="13"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="R8" s="13"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R9" s="13"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
         <v>Skill_Projectile_Hit_1</v>
@@ -2180,7 +2210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B12:F12)</f>
         <v>Skill_Human_MeleeAttack_1</v>
@@ -2223,22 +2253,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B16:F16)</f>
         <v>Skill_Stat_1</v>
@@ -2247,7 +2277,7 @@
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9">
@@ -2274,10 +2304,10 @@
         <v>0.1</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2295,16 +2325,16 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C8E724-28BD-8649-A64E-E00F04A859F7}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2334,13 +2364,13 @@
         <v>0</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>169</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2361,14 +2391,14 @@
       <c r="J2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="K2" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3:E3)</f>
         <v>Buff_1</v>
@@ -2397,7 +2427,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2407,20 +2437,20 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
@@ -2437,18 +2467,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2479,7 +2509,7 @@
       <c r="N1" s="9"/>
       <c r="O1" s="11"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2506,7 +2536,7 @@
       <c r="N2" s="9"/>
       <c r="O2" s="11"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Projectile_Human</v>
@@ -2540,7 +2570,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2555,7 +2585,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="11"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2570,7 +2600,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="11"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2585,7 +2615,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="11"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2606,7 +2636,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9012A38-B8D5-894C-A1D0-EDAD32738ED4}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2616,22 +2646,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7454E3B-BCDE-5A49-BB39-4B30666D97F3}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.15234375" customWidth="1"/>
+    <col min="6" max="6" width="20.69140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.3046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.69140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2659,7 +2689,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2683,7 +2713,7 @@
       <c r="M2" s="9"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Spawner_Test</v>
@@ -2714,7 +2744,7 @@
       <c r="M3" s="9"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2728,7 +2758,7 @@
       <c r="M4" s="9"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2742,7 +2772,7 @@
       <c r="M5" s="9"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2758,7 +2788,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2774,7 +2804,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2788,7 +2818,7 @@
       <c r="M8" s="9"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2802,7 +2832,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2811,7 +2841,7 @@
       <c r="H10" s="9"/>
       <c r="L10" s="9"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2820,7 +2850,7 @@
       <c r="H11" s="9"/>
       <c r="L11" s="9"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2838,19 +2868,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A933480A-994B-A74A-B07D-EEB09A80B87F}">
   <dimension ref="A1:V32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.69140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="21.69140625" customWidth="1"/>
+    <col min="12" max="12" width="21.69140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2890,10 +2920,10 @@
         <v>101</v>
       </c>
       <c r="O1" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
@@ -2902,7 +2932,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2940,10 +2970,10 @@
         <v>111</v>
       </c>
       <c r="O2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="14"/>
@@ -2952,7 +2982,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Player_Human</v>
@@ -2997,7 +3027,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Player_Dog</v>
@@ -3042,7 +3072,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Player_Eagle</v>
@@ -3087,7 +3117,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
         <v>Player_Snake</v>
@@ -3132,7 +3162,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -3146,35 +3176,35 @@
       <c r="J7" s="11"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -3182,14 +3212,14 @@
       <c r="G12" s="4"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -3197,7 +3227,7 @@
       <c r="G14" s="3"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -3205,7 +3235,7 @@
       <c r="G15" s="4"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -3213,7 +3243,7 @@
       <c r="G16" s="4"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="3:10">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -3221,105 +3251,105 @@
       <c r="G17" s="4"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="3:10">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="3:10">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="3:10">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="3:10">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="3:10">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="3:10">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="3:10">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="3:10">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="3:10">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="3:10">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="3:10">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="3:10">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="3:10">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="3:10">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="3:10">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -3347,15 +3377,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
   <dimension ref="A1:V14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3405,7 +3435,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -3449,7 +3479,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Item_WoodSword</v>
@@ -3492,7 +3522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Item_WoodStaff</v>
@@ -3535,7 +3565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Item_WoodBow</v>
@@ -3578,7 +3608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -3588,7 +3618,7 @@
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v>Item_Human</v>
@@ -3631,7 +3661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B8,C8)</f>
         <v>Item_Dog</v>
@@ -3674,7 +3704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B9,C9)</f>
         <v>Item_Eagle</v>
@@ -3717,7 +3747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B10,C10)</f>
         <v>Item_Snake</v>
@@ -3760,25 +3790,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="I14" s="1"/>
     </row>
   </sheetData>
@@ -3807,17 +3837,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.53515625" customWidth="1"/>
+    <col min="4" max="4" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3854,7 +3884,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3885,7 +3915,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,D3)</f>
         <v>FactionRelation_Hero</v>
@@ -3915,7 +3945,7 @@
       </c>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,D4)</f>
         <v>FactionRelation_Faction2</v>
@@ -3945,7 +3975,7 @@
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,D5)</f>
         <v>FactionRelation_Faction3</v>
@@ -3975,7 +4005,7 @@
       </c>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,D6)</f>
         <v>FactionRelation_Faction4</v>
@@ -4003,43 +4033,43 @@
         <v>Hostile,Hostile,Hostile,Friendly</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -4066,9 +4096,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4088,7 +4118,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4102,7 +4132,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f t="shared" ref="A3:A8" si="0">_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Grade_Common</v>
@@ -4123,7 +4153,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Uncommon</v>
@@ -4146,7 +4176,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Rare</v>
@@ -4169,7 +4199,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Epic</v>
@@ -4192,7 +4222,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Unique</v>
@@ -4215,7 +4245,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Legend</v>
@@ -4245,14 +4275,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4270,7 +4300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4284,7 +4314,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeBiome_Test</v>
@@ -4305,19 +4335,19 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="7"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="7"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f t="shared" ref="A7" si="0">_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v/>
@@ -4325,7 +4355,7 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
     </row>
@@ -4350,12 +4380,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4373,7 +4403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4387,7 +4417,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeElement_Test</v>
@@ -4408,16 +4438,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
     </row>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Toy\Project\FactoryProject\Generated\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251E54E1-BC48-4B90-8A2E-BCC711D3D088}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4980B5BF-4E76-B849-A07C-915501F21E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
@@ -31,12 +31,22 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="171">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -691,10 +701,6 @@
   </si>
   <si>
     <t>Str,5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffActionType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -726,7 +732,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -904,7 +910,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -959,9 +965,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1279,13 +1282,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
   <dimension ref="A1:S69"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="13.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -1308,7 +1311,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:19">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -1319,7 +1322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:19">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -1330,7 +1333,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:19">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -1341,7 +1344,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -1352,7 +1355,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1363,7 +1366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -1374,7 +1377,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1385,7 +1388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1396,7 +1399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -1407,7 +1410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -1418,7 +1421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1429,7 +1432,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -1440,7 +1443,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -1451,7 +1454,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -1462,7 +1465,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -1473,7 +1476,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>6</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>7</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>8</v>
       </c>
@@ -1506,7 +1509,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -1529,7 +1532,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1541,7 +1544,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -1553,7 +1556,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1565,7 +1568,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -1577,7 +1580,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1589,7 +1592,7 @@
       </c>
       <c r="E26" s="12"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -1600,7 +1603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>5</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -1633,7 +1636,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -1644,7 +1647,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1655,7 +1658,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -1666,7 +1669,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11">
       <c r="A34" s="1">
         <v>3</v>
       </c>
@@ -1677,7 +1680,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11">
       <c r="A37" s="1">
         <v>2</v>
       </c>
@@ -1710,7 +1713,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -1721,7 +1724,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11">
       <c r="A39" s="1">
         <v>2</v>
       </c>
@@ -1732,7 +1735,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -1743,7 +1746,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -1754,7 +1757,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11">
       <c r="A42" s="1">
         <v>3</v>
       </c>
@@ -1765,7 +1768,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11">
       <c r="A43" s="1">
         <v>4</v>
       </c>
@@ -1780,7 +1783,7 @@
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -1791,132 +1794,132 @@
         <v>163</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11">
       <c r="A45" s="1">
         <v>1</v>
       </c>
       <c r="B45" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C45" s="1" t="s">
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="1">
+        <v>2</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A46" s="1">
-        <v>2</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11">
       <c r="A47" s="1">
         <v>3</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="1"/>
       <c r="B48" s="11"/>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3">
       <c r="A49" s="1"/>
       <c r="B49" s="11"/>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3">
       <c r="A50" s="1"/>
       <c r="B50" s="11"/>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3">
       <c r="A51" s="1"/>
       <c r="B51" s="11"/>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3">
       <c r="A52" s="1"/>
       <c r="B52" s="11"/>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3">
       <c r="A53" s="1"/>
       <c r="B53" s="11"/>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3">
       <c r="A54" s="1"/>
       <c r="B54" s="11"/>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3">
       <c r="A55" s="1"/>
       <c r="B55" s="11"/>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3">
       <c r="A56" s="1"/>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3">
       <c r="A57" s="1"/>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3">
       <c r="A58" s="1"/>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3">
       <c r="A59" s="1"/>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3">
       <c r="A60" s="1"/>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3">
       <c r="A61" s="1"/>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3">
       <c r="A62" s="1"/>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3">
       <c r="A63" s="1"/>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3">
       <c r="A64" s="1"/>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3">
       <c r="A65" s="1"/>
       <c r="C65" s="1"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3">
       <c r="A66" s="1"/>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3">
       <c r="A67" s="1"/>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3">
       <c r="A68" s="1"/>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3">
       <c r="A69" s="1"/>
     </row>
   </sheetData>
@@ -1934,20 +1937,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
   <dimension ref="A1:AE16"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="23.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.3046875" customWidth="1"/>
-    <col min="12" max="12" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="19.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2008,7 +2011,7 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2059,7 +2062,7 @@
       <c r="AD2" s="6"/>
       <c r="AE2" s="6"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -2083,28 +2086,28 @@
       <c r="P3" s="9"/>
       <c r="R3" s="9"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="R4" s="13"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31">
       <c r="A5" s="7" t="s">
         <v>154</v>
       </c>
       <c r="R5" s="13"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31">
       <c r="A6" s="7" t="s">
         <v>154</v>
       </c>
       <c r="R6" s="13"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
         <v>Skill_Human_Projectile_1</v>
@@ -2147,26 +2150,26 @@
       <c r="R7" s="13"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="R8" s="13"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:31">
       <c r="A9" s="7" t="s">
         <v>155</v>
       </c>
       <c r="R9" s="13"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:31">
       <c r="A10" s="7" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:31">
       <c r="A11" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
         <v>Skill_Projectile_Hit_1</v>
@@ -2210,7 +2213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:31">
       <c r="A12" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B12:F12)</f>
         <v>Skill_Human_MeleeAttack_1</v>
@@ -2253,22 +2256,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:31">
       <c r="A13" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:31">
       <c r="A14" s="7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:31">
       <c r="A15" s="7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:31">
       <c r="A16" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B16:F16)</f>
         <v>Skill_Stat_1</v>
@@ -2297,7 +2300,7 @@
         <v>128</v>
       </c>
       <c r="K16" s="2"/>
-      <c r="L16" s="20" t="s">
+      <c r="L16" t="s">
         <v>132</v>
       </c>
       <c r="M16">
@@ -2325,16 +2328,16 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C8E724-28BD-8649-A64E-E00F04A859F7}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.15234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2364,13 +2367,13 @@
         <v>0</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2392,13 +2395,13 @@
         <v>33</v>
       </c>
       <c r="K2" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3:E3)</f>
         <v>Buff_1</v>
@@ -2427,7 +2430,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2437,20 +2440,20 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12">
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12">
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12">
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
@@ -2467,18 +2470,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2509,7 +2512,7 @@
       <c r="N1" s="9"/>
       <c r="O1" s="11"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2536,7 +2539,7 @@
       <c r="N2" s="9"/>
       <c r="O2" s="11"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Projectile_Human</v>
@@ -2570,7 +2573,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2585,7 +2588,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="11"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2600,7 +2603,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="11"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2615,7 +2618,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="11"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2636,7 +2639,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9012A38-B8D5-894C-A1D0-EDAD32738ED4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2646,22 +2649,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7454E3B-BCDE-5A49-BB39-4B30666D97F3}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="4" max="4" width="19.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.15234375" customWidth="1"/>
-    <col min="6" max="6" width="20.69140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.3046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.69140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2689,7 +2692,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2713,7 +2716,7 @@
       <c r="M2" s="9"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Spawner_Test</v>
@@ -2744,7 +2747,7 @@
       <c r="M3" s="9"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2758,7 +2761,7 @@
       <c r="M4" s="9"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2772,7 +2775,7 @@
       <c r="M5" s="9"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2788,7 +2791,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2804,7 +2807,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2818,7 +2821,7 @@
       <c r="M8" s="9"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2832,7 +2835,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2841,7 +2844,7 @@
       <c r="H10" s="9"/>
       <c r="L10" s="9"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2850,7 +2853,7 @@
       <c r="H11" s="9"/>
       <c r="L11" s="9"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2868,19 +2871,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A933480A-994B-A74A-B07D-EEB09A80B87F}">
   <dimension ref="A1:V32"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21.69140625" customWidth="1"/>
-    <col min="12" max="12" width="21.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2932,7 +2935,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2982,7 +2985,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Player_Human</v>
@@ -3027,7 +3030,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Player_Dog</v>
@@ -3072,7 +3075,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Player_Eagle</v>
@@ -3117,7 +3120,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
         <v>Player_Snake</v>
@@ -3162,7 +3165,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -3176,35 +3179,35 @@
       <c r="J7" s="11"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -3212,14 +3215,14 @@
       <c r="G12" s="4"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22">
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -3227,7 +3230,7 @@
       <c r="G14" s="3"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:22">
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -3235,7 +3238,7 @@
       <c r="G15" s="4"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:22">
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -3243,7 +3246,7 @@
       <c r="G16" s="4"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:10">
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -3251,105 +3254,105 @@
       <c r="G17" s="4"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:10">
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:10">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:10">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:10">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:10">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:10">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:10">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:10">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:10">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:10">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:10">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:10">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:10">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:10">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:10">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -3377,15 +3380,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
   <dimension ref="A1:V14"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3435,7 +3438,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -3479,7 +3482,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Item_WoodSword</v>
@@ -3522,7 +3525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Item_WoodStaff</v>
@@ -3565,7 +3568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Item_WoodBow</v>
@@ -3608,7 +3611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -3618,7 +3621,7 @@
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v>Item_Human</v>
@@ -3661,7 +3664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22">
       <c r="A8" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B8,C8)</f>
         <v>Item_Dog</v>
@@ -3704,7 +3707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22">
       <c r="A9" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B9,C9)</f>
         <v>Item_Eagle</v>
@@ -3747,7 +3750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22">
       <c r="A10" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B10,C10)</f>
         <v>Item_Snake</v>
@@ -3790,25 +3793,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22">
       <c r="I14" s="1"/>
     </row>
   </sheetData>
@@ -3837,17 +3840,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="21.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.53515625" customWidth="1"/>
-    <col min="4" max="4" width="10.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="26.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3884,7 +3887,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3915,7 +3918,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,D3)</f>
         <v>FactionRelation_Hero</v>
@@ -3945,7 +3948,7 @@
       </c>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,D4)</f>
         <v>FactionRelation_Faction2</v>
@@ -3975,7 +3978,7 @@
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,D5)</f>
         <v>FactionRelation_Faction3</v>
@@ -4005,7 +4008,7 @@
       </c>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,D6)</f>
         <v>FactionRelation_Faction4</v>
@@ -4033,43 +4036,43 @@
         <v>Hostile,Hostile,Hostile,Friendly</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17">
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17">
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17">
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17">
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17">
       <c r="D11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17">
       <c r="D12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17">
       <c r="D13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -4096,9 +4099,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4118,7 +4121,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4132,7 +4135,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10">
       <c r="A3" s="7" t="str">
         <f t="shared" ref="A3:A8" si="0">_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Grade_Common</v>
@@ -4153,7 +4156,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10">
       <c r="A4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Uncommon</v>
@@ -4176,7 +4179,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10">
       <c r="A5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Rare</v>
@@ -4199,7 +4202,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10">
       <c r="A6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Epic</v>
@@ -4222,7 +4225,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10">
       <c r="A7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Unique</v>
@@ -4245,7 +4248,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10">
       <c r="A8" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Legend</v>
@@ -4275,14 +4278,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="16.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4300,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4314,7 +4317,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeBiome_Test</v>
@@ -4335,19 +4338,19 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="7"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" s="7"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" s="7"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="7" t="str">
         <f t="shared" ref="A7" si="0">_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v/>
@@ -4355,7 +4358,7 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
     </row>
@@ -4380,12 +4383,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="18.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4403,7 +4406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4417,7 +4420,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeElement_Test</v>
@@ -4438,16 +4441,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
     </row>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4980B5BF-4E76-B849-A07C-915501F21E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001990C4-D471-9440-9562-7076B9ADD5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="172">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -279,10 +279,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>synergeSkillKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SynergeElement</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -725,6 +721,14 @@
   </si>
   <si>
     <t>buffEffectParam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synergeBuffKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1341,7 +1345,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1352,7 +1356,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1374,7 +1378,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1619,10 +1623,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1630,10 +1634,10 @@
         <v>2</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1641,10 +1645,10 @@
         <v>3</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1652,10 +1656,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1663,10 +1667,10 @@
         <v>2</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1674,10 +1678,10 @@
         <v>3</v>
       </c>
       <c r="B34" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1685,10 +1689,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1696,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1707,10 +1711,10 @@
         <v>2</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1718,7 +1722,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>27</v>
@@ -1729,10 +1733,10 @@
         <v>2</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1740,10 +1744,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -1751,10 +1755,10 @@
         <v>2</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -1762,10 +1766,10 @@
         <v>3</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -1773,10 +1777,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -1788,10 +1792,10 @@
         <v>5</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -1799,10 +1803,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -1810,10 +1814,10 @@
         <v>2</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -1821,10 +1825,10 @@
         <v>3</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -1968,7 +1972,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>0</v>
@@ -1977,19 +1981,19 @@
         <v>0</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>9</v>
@@ -2019,7 +2023,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>32</v>
@@ -2028,22 +2032,22 @@
         <v>33</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K2" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>142</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>143</v>
       </c>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
@@ -2070,18 +2074,18 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N3" s="11"/>
       <c r="O3" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P3" s="9"/>
       <c r="R3" s="9"/>
@@ -2095,14 +2099,14 @@
     </row>
     <row r="5" spans="1:31">
       <c r="A5" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R5" s="13"/>
       <c r="S5" s="1"/>
     </row>
     <row r="6" spans="1:31">
       <c r="A6" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R6" s="13"/>
       <c r="S6" s="1"/>
@@ -2119,7 +2123,7 @@
         <v>49</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E7" s="9">
         <v>1</v>
@@ -2129,23 +2133,23 @@
         <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R7" s="13"/>
       <c r="S7" s="1"/>
@@ -2159,14 +2163,14 @@
     </row>
     <row r="9" spans="1:31">
       <c r="A9" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R9" s="13"/>
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:31">
       <c r="A10" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -2178,10 +2182,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E11" s="9">
         <v>1</v>
@@ -2191,23 +2195,23 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M11">
         <v>0.6</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O11" s="11">
         <v>5</v>
@@ -2225,7 +2229,7 @@
         <v>49</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E12" s="9">
         <v>1</v>
@@ -2235,22 +2239,22 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M12">
         <v>0.1</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O12" s="11">
         <v>5</v>
@@ -2263,12 +2267,12 @@
     </row>
     <row r="14" spans="1:31">
       <c r="A14" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:31">
       <c r="A15" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -2280,7 +2284,7 @@
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9">
@@ -2291,26 +2295,26 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M16">
         <v>0.1</v>
       </c>
       <c r="N16" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="O16" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="O16" s="11" t="s">
-        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2352,7 +2356,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>1</v>
@@ -2367,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>9</v>
@@ -2380,13 +2384,13 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>32</v>
@@ -2395,10 +2399,10 @@
         <v>33</v>
       </c>
       <c r="K2" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2424,10 +2428,10 @@
         <v>1</v>
       </c>
       <c r="I3" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2517,13 +2521,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>33</v>
@@ -2545,7 +2549,7 @@
         <v>Projectile_Human</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -2554,16 +2558,16 @@
         <v>1</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -2676,13 +2680,13 @@
         <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -2697,16 +2701,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -2722,19 +2726,19 @@
         <v>Spawner_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3" s="17">
         <v>100100</v>
@@ -2917,16 +2921,16 @@
         <v>0</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
@@ -2943,7 +2947,7 @@
         <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>33</v>
@@ -2958,25 +2962,25 @@
         <v>18</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="N2" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="14"/>
@@ -2997,37 +3001,37 @@
         <v>49</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>118</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>23</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M3" s="9">
         <v>100</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -3039,40 +3043,40 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>53</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>24</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M4" s="9">
         <v>100</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3084,40 +3088,40 @@
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>53</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>24</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M5" s="9">
         <v>100</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3129,40 +3133,40 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>53</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M6" s="9">
         <v>100</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3471,7 +3475,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -3501,16 +3505,16 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>53</v>
@@ -3534,7 +3538,7 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
@@ -3544,16 +3548,16 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>53</v>
@@ -3577,7 +3581,7 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
@@ -3587,16 +3591,16 @@
         <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>53</v>
@@ -3640,16 +3644,16 @@
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>53</v>
@@ -3673,7 +3677,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
@@ -3683,16 +3687,16 @@
         <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>53</v>
@@ -3716,7 +3720,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9" t="s">
@@ -3726,16 +3730,16 @@
         <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>53</v>
@@ -3759,7 +3763,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
@@ -3769,16 +3773,16 @@
         <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>53</v>
@@ -3859,7 +3863,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -3877,7 +3881,7 @@
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -3892,23 +3896,23 @@
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="F2" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -3924,22 +3928,22 @@
         <v>FactionRelation_Hero</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9" t="str">
@@ -3954,22 +3958,22 @@
         <v>FactionRelation_Faction2</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="str">
@@ -3984,22 +3988,22 @@
         <v>FactionRelation_Faction3</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="9" t="str">
@@ -4014,22 +4018,22 @@
         <v>FactionRelation_Faction4</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J6" s="9" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,E6:H6)</f>
@@ -4141,7 +4145,7 @@
         <v>Grade_Common</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
@@ -4150,10 +4154,10 @@
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4162,19 +4166,19 @@
         <v>Grade_Uncommon</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" t="s">
         <v>70</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" t="s">
-        <v>71</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -4185,7 +4189,7 @@
         <v>Grade_Rare</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -4194,10 +4198,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -4208,7 +4212,7 @@
         <v>Grade_Epic</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>21</v>
@@ -4217,10 +4221,10 @@
         <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -4231,7 +4235,7 @@
         <v>Grade_Unique</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>22</v>
@@ -4240,10 +4244,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -4254,7 +4258,7 @@
         <v>Grade_Legend</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
@@ -4263,10 +4267,10 @@
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -4314,7 +4318,7 @@
         <v>57</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4411,13 +4415,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>57</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4426,7 +4430,7 @@
         <v>SynergeElement_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
         <v>55</v>
@@ -4438,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:6">

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001990C4-D471-9440-9562-7076B9ADD5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A6CC72-6E18-764C-A72D-ADA2B05260EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51180" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="173">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -729,6 +729,10 @@
   </si>
   <si>
     <t>Buff_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddBuff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -914,7 +918,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -969,6 +973,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1285,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
-  <dimension ref="A1:S69"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -1797,44 +1807,54 @@
       <c r="C44" s="1" t="s">
         <v>162</v>
       </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="21"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="1">
-        <v>1</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>167</v>
+        <v>6</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>167</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>167</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="1">
+        <v>3</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="1"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="1"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="1"/>
@@ -1873,6 +1893,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="1"/>
+      <c r="B56" s="11"/>
       <c r="C56" s="1"/>
     </row>
     <row r="57" spans="1:3">
@@ -1925,12 +1946,16 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1"/>
+      <c r="C69" s="1"/>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I16:I17" xr:uid="{2665461F-3737-5C48-86C3-985860BED678}">
-      <formula1>$I$2:$I$1016</formula1>
+      <formula1>$I$2:$I$1017</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1940,7 +1965,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
@@ -2315,6 +2340,55 @@
       </c>
       <c r="O16" s="11" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B19:F19)</f>
+        <v>Skill_Human_AddBuff_1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="K19" s="2"/>
+      <c r="L19" t="s">
+        <v>131</v>
+      </c>
+      <c r="M19">
+        <v>0.1</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2432,6 +2506,12 @@
       </c>
       <c r="J3" s="9" t="s">
         <v>117</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3371,7 +3451,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FBA1699A-C505-8C41-9338-26277C216689}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1016</xm:f>
+            <xm:f>Enum!$H$2:$H$1017</xm:f>
           </x14:formula1>
           <xm:sqref>Q3:Q7</xm:sqref>
         </x14:dataValidation>
@@ -3831,7 +3911,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B59ECF9-BEB9-264A-A494-976028F5B748}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1016</xm:f>
+            <xm:f>Enum!$H$2:$H$1017</xm:f>
           </x14:formula1>
           <xm:sqref>L6 P3:P7</xm:sqref>
         </x14:dataValidation>
@@ -4090,7 +4170,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D3DBA599-4157-B940-AFCF-2F7B820F1087}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1016</xm:f>
+            <xm:f>Enum!$H$2:$H$1017</xm:f>
           </x14:formula1>
           <xm:sqref>L6:M6 Q3:Q7</xm:sqref>
         </x14:dataValidation>
@@ -4374,7 +4454,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F0F1FFA4-2FD9-9C45-A6EF-56B810B8EE53}">
           <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1016</xm:f>
+            <xm:f>Enum!$I$2:$I$1017</xm:f>
           </x14:formula1>
           <xm:sqref>C5:C6</xm:sqref>
         </x14:dataValidation>
@@ -4466,7 +4546,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
           <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1016</xm:f>
+            <xm:f>Enum!$I$2:$I$1017</xm:f>
           </x14:formula1>
           <xm:sqref>B5:B6</xm:sqref>
         </x14:dataValidation>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A6CC72-6E18-764C-A72D-ADA2B05260EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BBA77A-6979-4A40-AE1E-64ADAF616D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51180" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="173">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -255,10 +255,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>attackSkillKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>none</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -734,6 +730,9 @@
   <si>
     <t>AddBuff</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Human_Projectile_1</t>
   </si>
 </sst>
 </file>
@@ -918,7 +917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -973,12 +972,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1355,7 +1348,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1366,7 +1359,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1388,7 +1381,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1633,10 +1626,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1644,10 +1637,10 @@
         <v>2</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1655,10 +1648,10 @@
         <v>3</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1666,10 +1659,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1677,10 +1670,10 @@
         <v>2</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1688,10 +1681,10 @@
         <v>3</v>
       </c>
       <c r="B34" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1699,10 +1692,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1710,10 +1703,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1721,10 +1714,10 @@
         <v>2</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1732,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>27</v>
@@ -1743,10 +1736,10 @@
         <v>2</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1754,10 +1747,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -1765,10 +1758,10 @@
         <v>2</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -1776,10 +1769,10 @@
         <v>3</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -1787,10 +1780,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -1802,13 +1795,12 @@
         <v>5</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F44" s="9"/>
-      <c r="G44" s="21"/>
       <c r="J44" s="11"/>
       <c r="K44" s="11"/>
     </row>
@@ -1817,10 +1809,10 @@
         <v>6</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -1828,10 +1820,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -1839,10 +1831,10 @@
         <v>2</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -1850,10 +1842,10 @@
         <v>3</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1997,7 +1989,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>0</v>
@@ -2006,19 +1998,19 @@
         <v>0</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>9</v>
@@ -2048,7 +2040,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>32</v>
@@ -2057,22 +2049,22 @@
         <v>33</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K2" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>142</v>
       </c>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
@@ -2099,18 +2091,18 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N3" s="11"/>
       <c r="O3" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P3" s="9"/>
       <c r="R3" s="9"/>
@@ -2124,14 +2116,14 @@
     </row>
     <row r="5" spans="1:31">
       <c r="A5" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R5" s="13"/>
       <c r="S5" s="1"/>
     </row>
     <row r="6" spans="1:31">
       <c r="A6" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R6" s="13"/>
       <c r="S6" s="1"/>
@@ -2148,7 +2140,7 @@
         <v>49</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E7" s="9">
         <v>1</v>
@@ -2158,23 +2150,23 @@
         <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R7" s="13"/>
       <c r="S7" s="1"/>
@@ -2188,14 +2180,14 @@
     </row>
     <row r="9" spans="1:31">
       <c r="A9" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R9" s="13"/>
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:31">
       <c r="A10" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -2207,10 +2199,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E11" s="9">
         <v>1</v>
@@ -2220,23 +2212,23 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M11">
         <v>0.6</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O11" s="11">
         <v>5</v>
@@ -2254,7 +2246,7 @@
         <v>49</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E12" s="9">
         <v>1</v>
@@ -2264,22 +2256,22 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M12">
         <v>0.1</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O12" s="11">
         <v>5</v>
@@ -2292,12 +2284,12 @@
     </row>
     <row r="14" spans="1:31">
       <c r="A14" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:31">
       <c r="A15" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -2309,7 +2301,7 @@
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9">
@@ -2320,30 +2312,30 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M16">
         <v>0.1</v>
       </c>
       <c r="N16" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="O16" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="O16" s="11" t="s">
-        <v>163</v>
-      </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="19" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2359,7 +2351,7 @@
         <v>49</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E19" s="9">
         <v>1</v>
@@ -2369,26 +2361,26 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M19">
         <v>0.1</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2430,7 +2422,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>1</v>
@@ -2445,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>9</v>
@@ -2458,13 +2450,13 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>32</v>
@@ -2473,10 +2465,10 @@
         <v>33</v>
       </c>
       <c r="K2" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2502,16 +2494,16 @@
         <v>1</v>
       </c>
       <c r="I3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2601,13 +2593,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>33</v>
@@ -2629,7 +2621,7 @@
         <v>Projectile_Human</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -2638,16 +2630,16 @@
         <v>1</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>146</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>147</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -2760,13 +2752,13 @@
         <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -2781,16 +2773,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -2806,19 +2798,19 @@
         <v>Spawner_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G3" s="17">
         <v>100100</v>
@@ -3001,16 +2993,16 @@
         <v>0</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
@@ -3027,7 +3019,7 @@
         <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>33</v>
@@ -3042,25 +3034,25 @@
         <v>18</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="N2" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="14"/>
@@ -3081,37 +3073,37 @@
         <v>49</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>23</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M3" s="9">
         <v>100</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -3123,40 +3115,40 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>24</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M4" s="9">
         <v>100</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3168,40 +3160,40 @@
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>24</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M5" s="9">
         <v>100</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3213,40 +3205,40 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M6" s="9">
         <v>100</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3335,7 +3327,7 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
-      <c r="G17" s="4"/>
+      <c r="G17" s="9"/>
       <c r="J17" s="9"/>
     </row>
     <row r="18" spans="3:10">
@@ -3504,15 +3496,13 @@
       <c r="K1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="5" t="s">
         <v>1</v>
       </c>
+      <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
@@ -3546,17 +3536,15 @@
         <v>18</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="L2" s="8" t="s">
         <v>34</v>
       </c>
+      <c r="L2" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="M2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
@@ -3585,27 +3573,24 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="L3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" t="s">
         <v>11</v>
       </c>
-      <c r="N3">
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -3618,7 +3603,7 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
@@ -3628,27 +3613,24 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" t="s">
         <v>11</v>
       </c>
-      <c r="N4">
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -3661,7 +3643,7 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
@@ -3671,27 +3653,24 @@
         <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="L5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" t="s">
         <v>11</v>
       </c>
-      <c r="N5">
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -3724,27 +3703,24 @@
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" t="s">
         <v>11</v>
       </c>
-      <c r="N7">
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -3757,7 +3733,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
@@ -3767,27 +3743,24 @@
         <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="L8" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" t="s">
         <v>11</v>
       </c>
-      <c r="N8">
+      <c r="M8">
         <v>1</v>
       </c>
     </row>
@@ -3800,7 +3773,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9" t="s">
@@ -3810,27 +3783,24 @@
         <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="L9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M9" t="s">
         <v>11</v>
       </c>
-      <c r="N9">
+      <c r="M9">
         <v>1</v>
       </c>
     </row>
@@ -3843,7 +3813,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
@@ -3853,27 +3823,24 @@
         <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="L10" t="s">
-        <v>53</v>
-      </c>
-      <c r="M10" t="s">
         <v>11</v>
       </c>
-      <c r="N10">
+      <c r="M10">
         <v>1</v>
       </c>
     </row>
@@ -3900,7 +3867,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6" xr:uid="{17B1ACDF-E711-444F-BA32-32976EC6EADF}">
       <formula1>#REF!</formula1>
     </dataValidation>
@@ -3908,12 +3875,12 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B59ECF9-BEB9-264A-A494-976028F5B748}">
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1017</xm:f>
           </x14:formula1>
-          <xm:sqref>L6 P3:P7</xm:sqref>
+          <xm:sqref>P3:P7 K6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3943,7 +3910,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -3961,7 +3928,7 @@
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -3976,23 +3943,23 @@
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="F2" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -4008,22 +3975,22 @@
         <v>FactionRelation_Hero</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9" t="str">
@@ -4038,22 +4005,22 @@
         <v>FactionRelation_Faction2</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="str">
@@ -4068,22 +4035,22 @@
         <v>FactionRelation_Faction3</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="9" t="str">
@@ -4098,22 +4065,22 @@
         <v>FactionRelation_Faction4</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J6" s="9" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,E6:H6)</f>
@@ -4225,7 +4192,7 @@
         <v>Grade_Common</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
@@ -4234,10 +4201,10 @@
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4246,19 +4213,19 @@
         <v>Grade_Uncommon</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
         <v>69</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" t="s">
-        <v>70</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -4269,7 +4236,7 @@
         <v>Grade_Rare</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -4278,10 +4245,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -4292,7 +4259,7 @@
         <v>Grade_Epic</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>21</v>
@@ -4301,10 +4268,10 @@
         <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -4315,7 +4282,7 @@
         <v>Grade_Unique</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>22</v>
@@ -4324,10 +4291,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -4338,7 +4305,7 @@
         <v>Grade_Legend</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
@@ -4347,10 +4314,10 @@
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -4392,13 +4359,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="F2" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4407,10 +4374,10 @@
         <v>SynergeBiome_Test</v>
       </c>
       <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>54</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>36</v>
@@ -4419,7 +4386,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4495,13 +4462,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4510,10 +4477,10 @@
         <v>SynergeElement_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>45</v>
@@ -4522,7 +4489,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:6">

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BBA77A-6979-4A40-AE1E-64ADAF616D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39391682-7D7E-7244-AA24-904AED66B76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="8" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="173">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3105,6 +3105,9 @@
       <c r="N3" s="11" t="s">
         <v>110</v>
       </c>
+      <c r="P3" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="7" t="str">
@@ -3150,6 +3153,9 @@
       <c r="N4" s="11" t="s">
         <v>102</v>
       </c>
+      <c r="P4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="7" t="str">
@@ -3195,6 +3201,9 @@
       <c r="N5" s="11" t="s">
         <v>102</v>
       </c>
+      <c r="P5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="7" t="str">
@@ -3239,6 +3248,9 @@
       </c>
       <c r="N6" s="11" t="s">
         <v>102</v>
+      </c>
+      <c r="P6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3440,7 +3452,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FBA1699A-C505-8C41-9338-26277C216689}">
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1017</xm:f>
@@ -4486,7 +4498,7 @@
         <v>45</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>170</v>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Toy\Project\FactoryProject\Generated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39391682-7D7E-7244-AA24-904AED66B76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0206A45-9534-49AC-9AFE-D1FA6DCADE56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="8" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -31,22 +31,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="175">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -733,13 +723,21 @@
   </si>
   <si>
     <t>Skill_Human_Projectile_1</t>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cooldown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -917,7 +915,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -972,6 +970,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1289,13 +1290,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
   <dimension ref="A1:S70"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -1318,7 +1319,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -1329,7 +1330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -1340,7 +1341,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -1351,7 +1352,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -1362,7 +1363,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1373,7 +1374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -1384,7 +1385,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1395,7 +1396,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1406,7 +1407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -1417,7 +1418,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -1428,7 +1429,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1439,7 +1440,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -1450,7 +1451,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -1461,7 +1462,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -1472,7 +1473,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -1483,7 +1484,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>6</v>
       </c>
@@ -1494,7 +1495,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>7</v>
       </c>
@@ -1505,7 +1506,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>8</v>
       </c>
@@ -1516,7 +1517,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1527,7 +1528,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -1539,7 +1540,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1551,7 +1552,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -1563,7 +1564,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1575,7 +1576,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -1587,7 +1588,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1599,7 +1600,7 @@
       </c>
       <c r="E26" s="12"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -1610,7 +1611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>5</v>
       </c>
@@ -1621,7 +1622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1632,7 +1633,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -1643,7 +1644,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -1654,7 +1655,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1665,7 +1666,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -1676,7 +1677,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>3</v>
       </c>
@@ -1687,7 +1688,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -1698,7 +1699,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -1709,7 +1710,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>2</v>
       </c>
@@ -1720,7 +1721,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -1731,7 +1732,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>2</v>
       </c>
@@ -1742,7 +1743,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -1753,7 +1754,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -1764,7 +1765,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>3</v>
       </c>
@@ -1775,7 +1776,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>4</v>
       </c>
@@ -1790,7 +1791,7 @@
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -1804,7 +1805,7 @@
       <c r="J44" s="11"/>
       <c r="K44" s="11"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -1815,7 +1816,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>1</v>
       </c>
@@ -1826,7 +1827,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>2</v>
       </c>
@@ -1837,7 +1838,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>3</v>
       </c>
@@ -1848,99 +1849,99 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="1"/>
       <c r="B49" s="11"/>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="1"/>
       <c r="B50" s="11"/>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" s="1"/>
       <c r="B51" s="11"/>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" s="1"/>
       <c r="B52" s="11"/>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" s="1"/>
       <c r="B53" s="11"/>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="1"/>
       <c r="B54" s="11"/>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" s="1"/>
       <c r="B55" s="11"/>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" s="1"/>
       <c r="B56" s="11"/>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" s="1"/>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="1"/>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" s="1"/>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" s="1"/>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" s="1"/>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" s="1"/>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" s="1"/>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" s="1"/>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" s="1"/>
       <c r="C65" s="1"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" s="1"/>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" s="1"/>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" s="1"/>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="1"/>
       <c r="C69" s="1"/>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" s="1"/>
     </row>
   </sheetData>
@@ -1957,21 +1958,21 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
-  <dimension ref="A1:AE19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <dimension ref="A1:AF19"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.53515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="19.3046875" customWidth="1"/>
+    <col min="13" max="13" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -1988,147 +1989,154 @@
       <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="19" t="s">
         <v>78</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>0</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
-      <c r="T1" s="5"/>
+      <c r="T1" s="8"/>
       <c r="U1" s="5"/>
-      <c r="V1" s="8"/>
+      <c r="V1" s="5"/>
       <c r="W1" s="8"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="5"/>
       <c r="Z1" s="8"/>
       <c r="AA1" s="8"/>
       <c r="AB1" s="8"/>
       <c r="AC1" s="8"/>
-      <c r="AD1" s="5"/>
+      <c r="AD1" s="8"/>
       <c r="AE1" s="5"/>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="5"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="H2" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
       <c r="S2" s="8"/>
-      <c r="T2" s="6"/>
+      <c r="T2" s="8"/>
       <c r="U2" s="6"/>
-      <c r="V2" s="8"/>
+      <c r="V2" s="6"/>
       <c r="W2" s="8"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="6"/>
       <c r="Z2" s="8"/>
       <c r="AA2" s="8"/>
       <c r="AB2" s="8"/>
       <c r="AC2" s="8"/>
-      <c r="AD2" s="6"/>
+      <c r="AD2" s="8"/>
       <c r="AE2" s="6"/>
-    </row>
-    <row r="3" spans="1:31">
+      <c r="AF2" s="6"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="9"/>
+      <c r="L3" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="N3" s="11"/>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="11"/>
+      <c r="P3" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="P3" s="9"/>
-      <c r="R3" s="9"/>
-    </row>
-    <row r="4" spans="1:31">
+      <c r="Q3" s="9"/>
+      <c r="S3" s="9"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="13"/>
-      <c r="S4" s="1"/>
-    </row>
-    <row r="5" spans="1:31">
+      <c r="S4" s="13"/>
+      <c r="T4" s="1"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="R5" s="13"/>
-      <c r="S5" s="1"/>
-    </row>
-    <row r="6" spans="1:31">
+      <c r="S5" s="13"/>
+      <c r="T5" s="1"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="R6" s="13"/>
-      <c r="S6" s="1"/>
-    </row>
-    <row r="7" spans="1:31">
+      <c r="S6" s="13"/>
+      <c r="T6" s="1"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
         <v>Skill_Human_Projectile_1</v>
@@ -2147,50 +2155,53 @@
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9">
         <v>10</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>66</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="K7" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" t="s">
+      <c r="L7" s="2"/>
+      <c r="M7" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="O7" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="P7" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="R7" s="13"/>
-      <c r="S7" s="1"/>
-    </row>
-    <row r="8" spans="1:31">
+      <c r="S7" s="13"/>
+      <c r="T7" s="1"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="R8" s="13"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="1:31">
+      <c r="S8" s="13"/>
+      <c r="T8" s="1"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="R9" s="13"/>
-      <c r="S9" s="1"/>
-    </row>
-    <row r="10" spans="1:31">
+      <c r="S9" s="13"/>
+      <c r="T9" s="1"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
         <v>Skill_Projectile_Hit_1</v>
@@ -2209,32 +2220,35 @@
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
         <v>1</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>66</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="K11" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" t="s">
+      <c r="L11" s="2"/>
+      <c r="M11" t="s">
         <v>129</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.6</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="O11" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="O11" s="11">
+      <c r="P11" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B12:F12)</f>
         <v>Skill_Human_MeleeAttack_1</v>
@@ -2255,44 +2269,47 @@
       <c r="G12" s="9">
         <v>1</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
         <v>66</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="K12" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>129</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.1</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="O12" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="O12" s="11">
+      <c r="P12" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B16:F16)</f>
         <v>Skill_Stat_1</v>
@@ -2309,37 +2326,40 @@
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
         <v>1</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>66</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>65</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="K16" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="K16" s="2"/>
-      <c r="L16" t="s">
+      <c r="L16" s="2"/>
+      <c r="M16" t="s">
         <v>130</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.1</v>
       </c>
-      <c r="N16" s="11" t="s">
+      <c r="O16" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="P16" s="11" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18" s="19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B19:F19)</f>
         <v>Skill_Human_AddBuff_1</v>
@@ -2358,35 +2378,38 @@
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
         <v>1</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>66</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>65</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="K19" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="K19" s="2"/>
-      <c r="L19" t="s">
+      <c r="L19" s="2"/>
+      <c r="M19" t="s">
         <v>130</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.1</v>
       </c>
-      <c r="N19" s="11" t="s">
+      <c r="O19" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="O19" s="11" t="s">
+      <c r="P19" s="11" t="s">
         <v>170</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K12" xr:uid="{27A11A15-E75D-9B40-BA34-50931BED73C4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12" xr:uid="{27A11A15-E75D-9B40-BA34-50931BED73C4}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -2398,16 +2421,16 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C8E724-28BD-8649-A64E-E00F04A859F7}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2443,7 +2466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2471,7 +2494,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3:E3)</f>
         <v>Buff_1</v>
@@ -2506,7 +2529,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2516,20 +2539,20 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
@@ -2546,18 +2569,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2588,7 +2611,7 @@
       <c r="N1" s="9"/>
       <c r="O1" s="11"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2615,7 +2638,7 @@
       <c r="N2" s="9"/>
       <c r="O2" s="11"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Projectile_Human</v>
@@ -2649,7 +2672,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2664,7 +2687,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="11"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2679,7 +2702,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="11"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2694,7 +2717,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="11"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2715,7 +2738,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9012A38-B8D5-894C-A1D0-EDAD32738ED4}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2725,22 +2748,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7454E3B-BCDE-5A49-BB39-4B30666D97F3}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.15234375" customWidth="1"/>
+    <col min="6" max="6" width="20.69140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.3046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.69140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2768,7 +2791,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2792,7 +2815,7 @@
       <c r="M2" s="9"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Spawner_Test</v>
@@ -2823,7 +2846,7 @@
       <c r="M3" s="9"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2837,7 +2860,7 @@
       <c r="M4" s="9"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2851,7 +2874,7 @@
       <c r="M5" s="9"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2867,7 +2890,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2883,7 +2906,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2897,7 +2920,7 @@
       <c r="M8" s="9"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2911,7 +2934,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2920,7 +2943,7 @@
       <c r="H10" s="9"/>
       <c r="L10" s="9"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2929,7 +2952,7 @@
       <c r="H11" s="9"/>
       <c r="L11" s="9"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2947,19 +2970,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A933480A-994B-A74A-B07D-EEB09A80B87F}">
   <dimension ref="A1:V32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.69140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="21.69140625" customWidth="1"/>
+    <col min="12" max="12" width="21.69140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3011,7 +3034,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -3061,7 +3084,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Player_Human</v>
@@ -3109,7 +3132,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Player_Dog</v>
@@ -3157,7 +3180,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Player_Eagle</v>
@@ -3205,7 +3228,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
         <v>Player_Snake</v>
@@ -3253,7 +3276,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -3267,35 +3290,35 @@
       <c r="J7" s="11"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -3303,14 +3326,14 @@
       <c r="G12" s="4"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -3318,7 +3341,7 @@
       <c r="G14" s="3"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -3326,7 +3349,7 @@
       <c r="G15" s="4"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -3334,7 +3357,7 @@
       <c r="G16" s="4"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="3:10">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -3342,105 +3365,105 @@
       <c r="G17" s="9"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="3:10">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="3:10">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="3:10">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="3:10">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="3:10">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="3:10">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="3:10">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="3:10">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="3:10">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="3:10">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="3:10">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="3:10">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="3:10">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="3:10">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="3:10">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -3468,15 +3491,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
   <dimension ref="A1:V14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3524,7 +3547,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -3566,7 +3589,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Item_WoodSword</v>
@@ -3606,7 +3629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Item_WoodStaff</v>
@@ -3646,7 +3669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Item_WoodBow</v>
@@ -3686,7 +3709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -3696,7 +3719,7 @@
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v>Item_Human</v>
@@ -3736,7 +3759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B8,C8)</f>
         <v>Item_Dog</v>
@@ -3776,7 +3799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B9,C9)</f>
         <v>Item_Eagle</v>
@@ -3816,7 +3839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B10,C10)</f>
         <v>Item_Snake</v>
@@ -3856,25 +3879,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="I14" s="1"/>
     </row>
   </sheetData>
@@ -3903,17 +3926,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.53515625" customWidth="1"/>
+    <col min="4" max="4" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3950,7 +3973,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3981,7 +4004,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,D3)</f>
         <v>FactionRelation_Hero</v>
@@ -4011,7 +4034,7 @@
       </c>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,D4)</f>
         <v>FactionRelation_Faction2</v>
@@ -4041,7 +4064,7 @@
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,D5)</f>
         <v>FactionRelation_Faction3</v>
@@ -4071,7 +4094,7 @@
       </c>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,D6)</f>
         <v>FactionRelation_Faction4</v>
@@ -4099,43 +4122,43 @@
         <v>Hostile,Hostile,Hostile,Friendly</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -4162,9 +4185,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4184,7 +4207,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4198,7 +4221,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f t="shared" ref="A3:A8" si="0">_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Grade_Common</v>
@@ -4219,7 +4242,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Uncommon</v>
@@ -4242,7 +4265,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Rare</v>
@@ -4265,7 +4288,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Epic</v>
@@ -4288,7 +4311,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Unique</v>
@@ -4311,7 +4334,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Legend</v>
@@ -4341,14 +4364,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4366,7 +4389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4380,7 +4403,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeBiome_Test</v>
@@ -4401,19 +4424,19 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="7"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="7"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f t="shared" ref="A7" si="0">_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v/>
@@ -4421,7 +4444,7 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
     </row>
@@ -4446,12 +4469,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4469,7 +4492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4483,7 +4506,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeElement_Test</v>
@@ -4504,16 +4527,16 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
     </row>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -1,42 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Toy\Project\FactoryProject\Generated\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0206A45-9534-49AC-9AFE-D1FA6DCADE56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F249AE7-7F29-B742-9C37-4A6A19CF14BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="9" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51180" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
-    <sheet name="Localization" sheetId="8" r:id="rId2"/>
-    <sheet name="Spawner" sheetId="23" r:id="rId3"/>
-    <sheet name="Player" sheetId="4" r:id="rId4"/>
-    <sheet name="Item" sheetId="19" r:id="rId5"/>
-    <sheet name="FactionRelation" sheetId="24" r:id="rId6"/>
-    <sheet name="Grade" sheetId="22" r:id="rId7"/>
-    <sheet name="SynergeBiome" sheetId="20" r:id="rId8"/>
-    <sheet name="SynergeElement" sheetId="21" r:id="rId9"/>
-    <sheet name="Skill" sheetId="27" r:id="rId10"/>
-    <sheet name="Buff" sheetId="29" r:id="rId11"/>
-    <sheet name="Projectile" sheetId="28" r:id="rId12"/>
+    <sheet name="Constant" sheetId="30" r:id="rId2"/>
+    <sheet name="Localization" sheetId="8" r:id="rId3"/>
+    <sheet name="Spawner" sheetId="23" r:id="rId4"/>
+    <sheet name="Player" sheetId="4" r:id="rId5"/>
+    <sheet name="Item" sheetId="19" r:id="rId6"/>
+    <sheet name="FactionRelation" sheetId="24" r:id="rId7"/>
+    <sheet name="Grade" sheetId="22" r:id="rId8"/>
+    <sheet name="SynergeBiome" sheetId="20" r:id="rId9"/>
+    <sheet name="SynergeElement" sheetId="21" r:id="rId10"/>
+    <sheet name="Skill" sheetId="27" r:id="rId11"/>
+    <sheet name="Buff" sheetId="29" r:id="rId12"/>
+    <sheet name="Projectile" sheetId="28" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="190">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -730,6 +741,66 @@
   </si>
   <si>
     <t>cooldown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rawValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefaultDetectionRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefaultAttackRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TargetLostRangeOffset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoolowDistanceRatio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// AI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>: Str * 100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -737,7 +808,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -915,7 +986,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -970,9 +1041,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1290,13 +1358,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
   <dimension ref="A1:S70"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="13.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -1319,7 +1387,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:19">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -1330,7 +1398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:19">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -1341,7 +1409,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:19">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -1352,7 +1420,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -1363,7 +1431,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1374,7 +1442,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -1385,7 +1453,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1396,7 +1464,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1407,7 +1475,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -1418,7 +1486,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -1429,7 +1497,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1440,7 +1508,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -1451,7 +1519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -1462,7 +1530,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -1473,7 +1541,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -1484,7 +1552,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>6</v>
       </c>
@@ -1495,7 +1563,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>7</v>
       </c>
@@ -1506,7 +1574,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>8</v>
       </c>
@@ -1517,7 +1585,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1528,7 +1596,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -1540,7 +1608,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1552,7 +1620,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -1564,7 +1632,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1576,7 +1644,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -1588,7 +1656,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1600,7 +1668,7 @@
       </c>
       <c r="E26" s="12"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -1611,7 +1679,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>5</v>
       </c>
@@ -1622,7 +1690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1633,7 +1701,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -1644,7 +1712,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -1655,7 +1723,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1666,7 +1734,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -1677,7 +1745,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11">
       <c r="A34" s="1">
         <v>3</v>
       </c>
@@ -1688,7 +1756,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -1699,7 +1767,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -1710,7 +1778,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11">
       <c r="A37" s="1">
         <v>2</v>
       </c>
@@ -1721,7 +1789,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -1732,7 +1800,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11">
       <c r="A39" s="1">
         <v>2</v>
       </c>
@@ -1743,7 +1811,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -1754,7 +1822,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -1765,7 +1833,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11">
       <c r="A42" s="1">
         <v>3</v>
       </c>
@@ -1776,7 +1844,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11">
       <c r="A43" s="1">
         <v>4</v>
       </c>
@@ -1791,7 +1859,7 @@
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -1805,7 +1873,7 @@
       <c r="J44" s="11"/>
       <c r="K44" s="11"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -1816,7 +1884,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11">
       <c r="A46" s="1">
         <v>1</v>
       </c>
@@ -1827,7 +1895,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11">
       <c r="A47" s="1">
         <v>2</v>
       </c>
@@ -1838,7 +1906,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11">
       <c r="A48" s="1">
         <v>3</v>
       </c>
@@ -1849,99 +1917,123 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A49" s="1"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="1"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A50" s="1"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="1"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A51" s="1"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="1"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52" s="1"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="1"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3">
+      <c r="A49" s="1">
+        <v>1</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1">
+        <v>2</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1">
+        <v>3</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1">
+        <v>4</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="1"/>
       <c r="B53" s="11"/>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3">
       <c r="A54" s="1"/>
       <c r="B54" s="11"/>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3">
       <c r="A55" s="1"/>
       <c r="B55" s="11"/>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3">
       <c r="A56" s="1"/>
       <c r="B56" s="11"/>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3">
       <c r="A57" s="1"/>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3">
       <c r="A58" s="1"/>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3">
       <c r="A59" s="1"/>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3">
       <c r="A60" s="1"/>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3">
       <c r="A61" s="1"/>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3">
       <c r="A62" s="1"/>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3">
       <c r="A63" s="1"/>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3">
       <c r="A64" s="1"/>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3">
       <c r="A65" s="1"/>
       <c r="C65" s="1"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3">
       <c r="A66" s="1"/>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3">
       <c r="A67" s="1"/>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3">
       <c r="A68" s="1"/>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3">
       <c r="A69" s="1"/>
       <c r="C69" s="1"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:3">
       <c r="A70" s="1"/>
     </row>
   </sheetData>
@@ -1957,22 +2049,114 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
+        <v>SynergeElement_Test</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="C4" s="9"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="C5" s="9"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
+          <x14:formula1>
+            <xm:f>Enum!$I$2:$I$1017</xm:f>
+          </x14:formula1>
+          <xm:sqref>B5:B6</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
   <dimension ref="A1:AF19"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="23.3046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.53515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="19.3046875" customWidth="1"/>
-    <col min="13" max="13" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.84375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="19.28515625" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -1989,7 +2173,7 @@
       <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="19" t="s">
         <v>173</v>
       </c>
       <c r="H1" s="19" t="s">
@@ -2036,14 +2220,14 @@
       <c r="AE1" s="5"/>
       <c r="AF1" s="5"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:32">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="19" t="s">
         <v>174</v>
       </c>
       <c r="H2" s="19" t="s">
@@ -2090,7 +2274,7 @@
       <c r="AE2" s="6"/>
       <c r="AF2" s="6"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:32">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -2115,28 +2299,28 @@
       <c r="Q3" s="9"/>
       <c r="S3" s="9"/>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:32">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="S4" s="13"/>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:32">
       <c r="A5" s="7" t="s">
         <v>152</v>
       </c>
       <c r="S5" s="13"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:32">
       <c r="A6" s="7" t="s">
         <v>152</v>
       </c>
       <c r="S6" s="13"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:32">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
         <v>Skill_Human_Projectile_1</v>
@@ -2182,26 +2366,26 @@
       <c r="S7" s="13"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:32">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="S8" s="13"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:32">
       <c r="A9" s="7" t="s">
         <v>153</v>
       </c>
       <c r="S9" s="13"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:32">
       <c r="A10" s="7" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:32">
       <c r="A11" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
         <v>Skill_Projectile_Hit_1</v>
@@ -2244,11 +2428,11 @@
       <c r="O11" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="P11" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="P11" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
       <c r="A12" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B12:F12)</f>
         <v>Skill_Human_MeleeAttack_1</v>
@@ -2290,26 +2474,26 @@
       <c r="O12" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="P12" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="P12" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
       <c r="A13" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:32">
       <c r="A14" s="7" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:32">
       <c r="A15" s="7" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:32">
       <c r="A16" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B16:F16)</f>
         <v>Skill_Stat_1</v>
@@ -2354,12 +2538,12 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16">
       <c r="A18" s="19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16">
       <c r="A19" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B19:F19)</f>
         <v>Skill_Human_AddBuff_1</v>
@@ -2418,19 +2602,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C8E724-28BD-8649-A64E-E00F04A859F7}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.15234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2466,7 +2650,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2494,7 +2678,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3:E3)</f>
         <v>Buff_1</v>
@@ -2529,7 +2713,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2539,20 +2723,20 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12">
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12">
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12">
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
@@ -2566,21 +2750,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2611,7 +2795,7 @@
       <c r="N1" s="9"/>
       <c r="O1" s="11"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2638,7 +2822,7 @@
       <c r="N2" s="9"/>
       <c r="O2" s="11"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Projectile_Human</v>
@@ -2672,7 +2856,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2687,7 +2871,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="11"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2702,7 +2886,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="11"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2717,7 +2901,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="11"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2736,34 +2920,181 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375CF63E-9079-1A4A-A3AF-0BA8892B823F}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B5:D5)</f>
+        <v>AI_Flow_DefaultDetectionRange</v>
+      </c>
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G5" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="7" t="str">
+        <f t="shared" ref="A6:A8" si="0">_xlfn.TEXTJOIN("_",TRUE,B6:D6)</f>
+        <v>AI_Flow_DefaultAttackRange</v>
+      </c>
+      <c r="B6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>AI_Flow_TargetLostRangeOffset</v>
+      </c>
+      <c r="B7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>AI_Flow_FoolowDistanceRatio</v>
+      </c>
+      <c r="B8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9012A38-B8D5-894C-A1D0-EDAD32738ED4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7454E3B-BCDE-5A49-BB39-4B30666D97F3}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="4" max="4" width="19.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.15234375" customWidth="1"/>
-    <col min="6" max="6" width="20.69140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.3046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.69140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -2791,7 +3122,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -2815,7 +3146,7 @@
       <c r="M2" s="9"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Spawner_Test</v>
@@ -2846,7 +3177,7 @@
       <c r="M3" s="9"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16">
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2860,7 +3191,7 @@
       <c r="M4" s="9"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2874,7 +3205,7 @@
       <c r="M5" s="9"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16">
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2890,7 +3221,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16">
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2906,7 +3237,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2920,7 +3251,7 @@
       <c r="M8" s="9"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2934,7 +3265,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2943,7 +3274,7 @@
       <c r="H10" s="9"/>
       <c r="L10" s="9"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2952,7 +3283,7 @@
       <c r="H11" s="9"/>
       <c r="L11" s="9"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2967,29 +3298,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A933480A-994B-A74A-B07D-EEB09A80B87F}">
-  <dimension ref="A1:V32"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:W32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21.69140625" customWidth="1"/>
-    <col min="12" max="12" width="21.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="21.7109375" customWidth="1"/>
+    <col min="13" max="13" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:23">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5" t="s">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>0</v>
@@ -3000,91 +3331,97 @@
       <c r="G1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="K1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W1" s="5"/>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="14"/>
       <c r="T2" s="6"/>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W2" s="6"/>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Player_Human</v>
@@ -3095,44 +3432,47 @@
       <c r="C3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="9">
+        <v>100</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="M3" s="9">
+      <c r="N3" s="9">
         <v>100</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:23">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Player_Dog</v>
@@ -3143,44 +3483,47 @@
       <c r="C4" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="9">
+        <v>100</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="K4" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="L4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="M4" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="M4" s="9">
+      <c r="N4" s="9">
         <v>100</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="O4" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:23">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Player_Eagle</v>
@@ -3191,44 +3534,47 @@
       <c r="C5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="9">
+        <v>100</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="K5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="L5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="M5" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="M5" s="9">
+      <c r="N5" s="9">
         <v>100</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="O5" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:23">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
         <v>Player_Snake</v>
@@ -3239,44 +3585,47 @@
       <c r="C6" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="9">
+        <v>100</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="K6" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="L6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="M6" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="M6" s="9">
+      <c r="N6" s="9">
         <v>100</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="O6" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:23">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -3285,190 +3634,216 @@
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="11"/>
+      <c r="H7" s="9"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
-      <c r="K7" s="9"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="K7" s="11"/>
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" spans="1:23">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="G8" s="9"/>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:23">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="G9" s="9"/>
+      <c r="K9" s="9"/>
+    </row>
+    <row r="10" spans="1:23">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="G10" s="9"/>
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11" spans="1:23">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="G11" s="9"/>
+      <c r="K11" s="9"/>
+    </row>
+    <row r="12" spans="1:23">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
-      <c r="G12" s="4"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="G12" s="9"/>
+      <c r="H12" s="4"/>
+      <c r="K12" s="9"/>
+    </row>
+    <row r="13" spans="1:23">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="G13" s="9"/>
+      <c r="K13" s="9"/>
+    </row>
+    <row r="14" spans="1:23">
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="3"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="G14" s="9"/>
+      <c r="H14" s="3"/>
+      <c r="K14" s="9"/>
+    </row>
+    <row r="15" spans="1:23">
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="4"/>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="G15" s="9"/>
+      <c r="H15" s="4"/>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" spans="1:23">
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="4"/>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G16" s="9"/>
+      <c r="H16" s="4"/>
+      <c r="K16" s="9"/>
+    </row>
+    <row r="17" spans="3:11">
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="H17" s="9"/>
+      <c r="K17" s="9"/>
+    </row>
+    <row r="18" spans="3:11">
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G18" s="9"/>
+      <c r="K18" s="9"/>
+    </row>
+    <row r="19" spans="3:11">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G19" s="9"/>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="3:11">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G20" s="9"/>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="3:11">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G21" s="9"/>
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" spans="3:11">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G22" s="9"/>
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" spans="3:11">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G23" s="9"/>
+      <c r="K23" s="9"/>
+    </row>
+    <row r="24" spans="3:11">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G24" s="9"/>
+      <c r="K24" s="9"/>
+    </row>
+    <row r="25" spans="3:11">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
-      <c r="J25" s="9"/>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G25" s="9"/>
+      <c r="K25" s="9"/>
+    </row>
+    <row r="26" spans="3:11">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
-      <c r="J26" s="9"/>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G26" s="9"/>
+      <c r="K26" s="9"/>
+    </row>
+    <row r="27" spans="3:11">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
-      <c r="J27" s="9"/>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G27" s="9"/>
+      <c r="K27" s="9"/>
+    </row>
+    <row r="28" spans="3:11">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="J28" s="9"/>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G28" s="9"/>
+      <c r="K28" s="9"/>
+    </row>
+    <row r="29" spans="3:11">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
-      <c r="J29" s="9"/>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G29" s="9"/>
+      <c r="K29" s="9"/>
+    </row>
+    <row r="30" spans="3:11">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
-      <c r="J30" s="9"/>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G30" s="9"/>
+      <c r="K30" s="9"/>
+    </row>
+    <row r="31" spans="3:11">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
-      <c r="J31" s="9"/>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="G31" s="9"/>
+      <c r="K31" s="9"/>
+    </row>
+    <row r="32" spans="3:11">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
-      <c r="J32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="K32" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3480,7 +3855,7 @@
           <x14:formula1>
             <xm:f>Enum!$H$2:$H$1017</xm:f>
           </x14:formula1>
-          <xm:sqref>Q3:Q7</xm:sqref>
+          <xm:sqref>R3:R7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3488,18 +3863,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
   <dimension ref="A1:V14"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3547,7 +3922,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -3589,7 +3964,7 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Item_WoodSword</v>
@@ -3629,7 +4004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Item_WoodStaff</v>
@@ -3669,7 +4044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Item_WoodBow</v>
@@ -3709,7 +4084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -3719,7 +4094,7 @@
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v>Item_Human</v>
@@ -3759,7 +4134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22">
       <c r="A8" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B8,C8)</f>
         <v>Item_Dog</v>
@@ -3799,7 +4174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22">
       <c r="A9" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B9,C9)</f>
         <v>Item_Eagle</v>
@@ -3839,7 +4214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22">
       <c r="A10" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B10,C10)</f>
         <v>Item_Snake</v>
@@ -3879,25 +4254,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22">
       <c r="I14" s="1"/>
     </row>
   </sheetData>
@@ -3923,20 +4298,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791254EB-5610-D14F-ACAF-D2B5E0C5153F}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="21.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.53515625" customWidth="1"/>
-    <col min="4" max="4" width="10.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="26.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -3973,7 +4348,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4004,7 +4379,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,D3)</f>
         <v>FactionRelation_Hero</v>
@@ -4034,7 +4409,7 @@
       </c>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,D4)</f>
         <v>FactionRelation_Faction2</v>
@@ -4064,7 +4439,7 @@
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,D5)</f>
         <v>FactionRelation_Faction3</v>
@@ -4094,7 +4469,7 @@
       </c>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,D6)</f>
         <v>FactionRelation_Faction4</v>
@@ -4122,43 +4497,43 @@
         <v>Hostile,Hostile,Hostile,Friendly</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17">
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17">
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17">
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17">
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17">
       <c r="D11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17">
       <c r="D12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17">
       <c r="D13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -4182,12 +4557,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD492A1-6B8F-1440-9D54-6461F12B20A3}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4207,7 +4582,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4221,7 +4596,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10">
       <c r="A3" s="7" t="str">
         <f t="shared" ref="A3:A8" si="0">_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Grade_Common</v>
@@ -4242,7 +4617,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10">
       <c r="A4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Uncommon</v>
@@ -4265,7 +4640,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10">
       <c r="A5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Rare</v>
@@ -4288,7 +4663,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10">
       <c r="A6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Epic</v>
@@ -4311,7 +4686,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10">
       <c r="A7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Unique</v>
@@ -4334,7 +4709,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10">
       <c r="A8" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Grade_Legend</v>
@@ -4361,17 +4736,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE1ACEB-A93E-084F-8B48-EB95313F04DB}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="16.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -4389,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
@@ -4403,7 +4778,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>SynergeBiome_Test</v>
@@ -4424,19 +4799,19 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="7"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" s="7"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" s="7"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="7" t="str">
         <f t="shared" ref="A7" si="0">_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
         <v/>
@@ -4444,7 +4819,7 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
     </row>
@@ -4464,96 +4839,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C1629-BD9D-564A-BFD4-EB36E5A37A98}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="18.3046875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
-        <v>SynergeElement_Test</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
-          <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1017</xm:f>
-          </x14:formula1>
-          <xm:sqref>B5:B6</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
 </file>
--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F249AE7-7F29-B742-9C37-4A6A19CF14BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13007B9-FF0B-7F4D-8BDA-677EE9945DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51180" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13007B9-FF0B-7F4D-8BDA-677EE9945DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48BD764-9FA3-8E43-8B93-A4D806DF4CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -24,8 +24,9 @@
     <sheet name="SynergeBiome" sheetId="20" r:id="rId9"/>
     <sheet name="SynergeElement" sheetId="21" r:id="rId10"/>
     <sheet name="Skill" sheetId="27" r:id="rId11"/>
-    <sheet name="Buff" sheetId="29" r:id="rId12"/>
-    <sheet name="Projectile" sheetId="28" r:id="rId13"/>
+    <sheet name="Skin" sheetId="31" r:id="rId12"/>
+    <sheet name="Buff" sheetId="29" r:id="rId13"/>
+    <sheet name="Projectile" sheetId="28" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="357">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -97,18 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Armor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accessory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>List&lt;StatType&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -252,10 +241,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WoodSword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>none</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -291,18 +276,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>WoodStaff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WoodBow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_woodsword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>icon_item_woodstaff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -802,6 +775,595 @@
   <si>
     <t>: Str * 100</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바디0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eye_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair_9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바디1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바디2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바디3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair_13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바디4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eye_7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바디5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eye_6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바디6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//</t>
+  </si>
+  <si>
+    <t>Skin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bodyKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hairKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eyeKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skinKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RHand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LHand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Top</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pants</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FaceAcc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HairAcc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemSlotType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemSlotType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_0</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_13</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_14</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_15</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_16</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_17</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_18</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_19</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_20</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_21</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_22</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_8</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_9</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/LeftHandWeapon/Weapon_10</t>
+  </si>
+  <si>
+    <t>equipPath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_0</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_2</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_3</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_4</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_5</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_6</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_7</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_8</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Shield/Shield_9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/RightHandWeapon/Bow_0</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/RightHandWeapon/Bow_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/RightHandWeapon/Bow_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/RightHandWeapon/Bow_3</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/RightHandWeapon/Bow_4</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/RightHandWeapon/Bow_5</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/RightHandWeapon/Bow_6</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/RightHandWeapon/Bow_7</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_0</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_2</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_3</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_4</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_5</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_6</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_7</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_8</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_9</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_10</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_11</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_12</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_13</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_14</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_15</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_16</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_17</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_18</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_19</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_20</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_21</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_22</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_23</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_24</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_25</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_26</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_27</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_28</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_29</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Top/Top_30</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_0</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_2</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_3</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_4</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_5</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_6</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_7</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_8</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_9</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_10</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_11</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_12</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_13</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_14</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_15</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_16</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_17</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_18</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_19</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Pants/Pants_20</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Cape/Cape_0</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Cape/Cape_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Cape/Cape_2</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Cape/Cape_3</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Cape/Cape_4</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Cape/Cape_5</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/FaceAcc_2/FaceAcc2_1</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/FaceAcc_2/FaceAcc2_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/FaceAcc_2/FaceAcc2_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/FaceAcc_2/FaceAcc2_8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/FaceAcc_2/FaceAcc2_9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/FaceAcc_1/FaceAcc2_10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/FaceAcc_1/FaceAcc2_12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_0</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_2</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_3</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_4</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_5</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_6</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_7</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_8</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_9</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_10</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_11</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_12</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_13</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_14</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_15</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_16</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_17</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_18</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/HairAcc/HairAcc_19</t>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon 리소스 추가 시 변경 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Buff Example</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Projectile_Bow_1</t>
+  </si>
+  <si>
+    <t>1,5,1,3,1</t>
+  </si>
+  <si>
+    <t>1,5,1,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Str,Dex,Int,Physical,Magical</t>
   </si>
 </sst>
 </file>
@@ -859,7 +1421,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -980,13 +1542,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1041,6 +1627,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1357,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4AE1AA-8A06-FD4D-90BD-9F8B147AB8E0}">
-  <dimension ref="A1:S70"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -1417,7 +2021,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1428,7 +2032,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1436,10 +2040,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1447,10 +2051,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1458,10 +2062,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1469,10 +2073,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1480,10 +2084,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1491,10 +2095,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1502,10 +2106,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1513,10 +2117,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1524,10 +2128,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1535,10 +2139,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1546,10 +2150,10 @@
         <v>5</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1557,10 +2161,10 @@
         <v>6</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1568,10 +2172,10 @@
         <v>7</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1579,10 +2183,10 @@
         <v>8</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1590,10 +2194,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1601,10 +2205,10 @@
         <v>2</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E21" s="11"/>
     </row>
@@ -1613,10 +2217,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="E22" s="11"/>
     </row>
@@ -1625,10 +2229,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E23" s="11"/>
     </row>
@@ -1637,10 +2241,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E24" s="11"/>
     </row>
@@ -1649,10 +2253,10 @@
         <v>2</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E25" s="11"/>
     </row>
@@ -1661,10 +2265,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>12</v>
+        <v>212</v>
       </c>
       <c r="E26" s="12"/>
     </row>
@@ -1673,10 +2277,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>14</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1684,363 +2288,522 @@
         <v>5</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>7</v>
+        <v>221</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>103</v>
+        <v>221</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>104</v>
+        <v>221</v>
+      </c>
+      <c r="C30" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>105</v>
+        <v>221</v>
+      </c>
+      <c r="C31" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1">
+        <v>9</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C32" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1">
         <v>1</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="1">
+      <c r="B33" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1">
         <v>2</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="1">
+      <c r="B34" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1">
         <v>3</v>
       </c>
-      <c r="B34" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="1">
+      <c r="B35" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="1">
         <v>4</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="1">
+      <c r="B36" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1">
+        <v>5</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="1">
+        <v>6</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1">
+        <v>7</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1">
+        <v>8</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1">
+        <v>9</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="1">
+        <v>10</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1">
         <v>1</v>
       </c>
-      <c r="B36" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="1">
+      <c r="B43" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="1">
         <v>2</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="1">
-        <v>1</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="1">
-        <v>2</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="1">
-        <v>1</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="1">
-        <v>2</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="1">
+      <c r="B44" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1">
         <v>3</v>
       </c>
-      <c r="B42" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="1">
-        <v>4</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="2"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="1">
-        <v>5</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F44" s="9"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="1">
-        <v>6</v>
-      </c>
       <c r="B45" s="13" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="1">
         <v>1</v>
       </c>
-      <c r="B46" s="11" t="s">
-        <v>166</v>
+      <c r="B46" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="1">
         <v>2</v>
       </c>
-      <c r="B47" s="11" t="s">
-        <v>166</v>
+      <c r="B47" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="1">
         <v>3</v>
       </c>
-      <c r="B48" s="11" t="s">
-        <v>166</v>
+      <c r="B48" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="1">
+        <v>4</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="1">
         <v>1</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C49" s="1" t="s">
+      <c r="B50" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="1">
+        <v>2</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="1">
+        <v>1</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="1">
+        <v>2</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="1">
+        <v>1</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="1">
+        <v>2</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F55" s="9"/>
+      <c r="G55" s="2"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="1">
+        <v>3</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F56" s="9"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="1">
+        <v>4</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1">
+      <c r="B58" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="1">
+        <v>6</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="1">
+        <v>1</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="1">
         <v>2</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1">
+      <c r="B61" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="1">
         <v>3</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="1">
+      <c r="B62" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="1">
+        <v>1</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="1">
+        <v>2</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1">
+        <v>3</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1">
         <v>4</v>
       </c>
-      <c r="B52" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="1"/>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="1"/>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="1"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="1"/>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="1"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="1"/>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="1"/>
-      <c r="C57" s="1"/>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="1"/>
-      <c r="C58" s="1"/>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="1"/>
-      <c r="C59" s="1"/>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="1"/>
-      <c r="C60" s="1"/>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="1"/>
-      <c r="C61" s="1"/>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="1"/>
-      <c r="C62" s="1"/>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="1"/>
-      <c r="C63" s="1"/>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="1"/>
-      <c r="C64" s="1"/>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="1"/>
-      <c r="C65" s="1"/>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="1"/>
-      <c r="C66" s="1"/>
+      <c r="B66" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="1"/>
+      <c r="B67" s="11"/>
       <c r="C67" s="1"/>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="1"/>
+      <c r="B68" s="11"/>
       <c r="C68" s="1"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1"/>
+      <c r="B69" s="11"/>
       <c r="C69" s="1"/>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="1"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="1"/>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="1"/>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1"/>
+      <c r="C72" s="1"/>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="1"/>
+      <c r="C73" s="1"/>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="1"/>
+      <c r="C74" s="1"/>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1"/>
+      <c r="C75" s="1"/>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1"/>
+      <c r="C76" s="1"/>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1"/>
+      <c r="C77" s="1"/>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1"/>
+      <c r="C78" s="1"/>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1"/>
+      <c r="C79" s="1"/>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1"/>
+      <c r="C80" s="1"/>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1"/>
+      <c r="C81" s="1"/>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="1"/>
+      <c r="C82" s="1"/>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="1"/>
+      <c r="C83" s="1"/>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="1"/>
+      <c r="C84" s="1"/>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I16:I17" xr:uid="{2665461F-3737-5C48-86C3-985860BED678}">
-      <formula1>$I$2:$I$1017</formula1>
+      <formula1>$I$2:$I$1029</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2065,7 +2828,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -2079,13 +2842,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2094,19 +2857,19 @@
         <v>SynergeElement_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2130,7 +2893,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5FDDF60-689E-184E-934A-907BC1C56072}">
           <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1017</xm:f>
+            <xm:f>Enum!$I$2:$I$1029</xm:f>
           </x14:formula1>
           <xm:sqref>B5:B6</xm:sqref>
         </x14:dataValidation>
@@ -2142,13 +2905,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4766A74-1CE1-8948-A88A-472E2BC79D97}">
-  <dimension ref="A1:AF19"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="19.28515625" customWidth="1"/>
     <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -2174,10 +2937,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>0</v>
@@ -2186,19 +2949,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>9</v>
@@ -2228,34 +2991,34 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="19" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -2283,18 +3046,18 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="Q3" s="9"/>
       <c r="S3" s="9"/>
@@ -2308,14 +3071,14 @@
     </row>
     <row r="5" spans="1:32">
       <c r="A5" s="7" t="s">
-        <v>152</v>
+        <v>2</v>
       </c>
       <c r="S5" s="13"/>
       <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="S6" s="13"/>
       <c r="T6" s="1"/>
@@ -2323,16 +3086,16 @@
     <row r="7" spans="1:32">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
-        <v>Skill_Human_Projectile_1</v>
+        <v>Skill_Projectile_Human_1</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="E7" s="9">
         <v>1</v>
@@ -2345,255 +3108,320 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="S7" s="13"/>
       <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:32">
-      <c r="A8" s="7" t="s">
-        <v>2</v>
+      <c r="A8" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B8:F8)</f>
+        <v>Skill_Projectile_Bow_1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>140</v>
       </c>
       <c r="S8" s="13"/>
       <c r="T8" s="1"/>
     </row>
     <row r="9" spans="1:32">
       <c r="A9" s="7" t="s">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="S9" s="13"/>
       <c r="T9" s="1"/>
     </row>
     <row r="10" spans="1:32">
       <c r="A10" s="7" t="s">
-        <v>153</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="S10" s="13"/>
+      <c r="T10" s="1"/>
     </row>
     <row r="11" spans="1:32">
-      <c r="A11" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
-        <v>Skill_Projectile_Hit_1</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" s="9">
-        <v>1</v>
-      </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9">
-        <v>0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" t="s">
-        <v>129</v>
-      </c>
-      <c r="N11">
-        <v>0.6</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="P11" s="11" t="s">
-        <v>189</v>
+      <c r="A11" s="7" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:32">
       <c r="A12" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B12:F12)</f>
-        <v>Skill_Human_MeleeAttack_1</v>
+        <v>Skill_Projectile_Hit_1</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E12" s="9">
         <v>1</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="9">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="J12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K12" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" t="s">
+        <v>122</v>
+      </c>
+      <c r="N12">
+        <v>0.6</v>
+      </c>
+      <c r="O12" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="M12" t="s">
-        <v>129</v>
-      </c>
-      <c r="N12">
+      <c r="P12" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
+      <c r="A13" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B13:F13)</f>
+        <v>Skill_Human_MeleeAttack_1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="M13" t="s">
+        <v>122</v>
+      </c>
+      <c r="N13">
         <v>0.1</v>
       </c>
-      <c r="O12" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32">
-      <c r="A13" s="7" t="s">
-        <v>2</v>
+      <c r="O13" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:32">
       <c r="A14" s="7" t="s">
-        <v>155</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:32">
       <c r="A15" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
+      <c r="A16" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B17:F17)</f>
+        <v>Skill_Stat_1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" t="s">
+        <v>58</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" t="s">
+        <v>123</v>
+      </c>
+      <c r="N17">
+        <v>0.1</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="P17" s="11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="16" spans="1:32">
-      <c r="A16" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B16:F16)</f>
-        <v>Skill_Stat_1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9">
+    <row r="18" spans="1:16">
+      <c r="A18" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="24"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="19" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B21:F21)</f>
+        <v>Skill_Human_AddBuff_1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" s="9">
         <v>1</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9">
+      <c r="F21" s="9"/>
+      <c r="G21" s="9">
         <v>0</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H21" s="9">
         <v>1</v>
       </c>
-      <c r="I16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J16" t="s">
-        <v>65</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L16" s="2"/>
-      <c r="M16" t="s">
-        <v>130</v>
-      </c>
-      <c r="N16">
+      <c r="I21" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" t="s">
+        <v>123</v>
+      </c>
+      <c r="N21">
         <v>0.1</v>
       </c>
-      <c r="O16" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="P16" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B19:F19)</f>
-        <v>Skill_Human_AddBuff_1</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9">
-        <v>0</v>
-      </c>
-      <c r="H19" s="9">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" t="s">
-        <v>65</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L19" s="2"/>
-      <c r="M19" t="s">
-        <v>130</v>
-      </c>
-      <c r="N19">
-        <v>0.1</v>
-      </c>
-      <c r="O19" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="P19" s="11" t="s">
-        <v>170</v>
+      <c r="O21" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12" xr:uid="{27A11A15-E75D-9B40-BA34-50931BED73C4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L13" xr:uid="{27A11A15-E75D-9B40-BA34-50931BED73C4}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -2603,6 +3431,282 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{144C7A59-A31B-3B4B-8194-C1B482CAFDC6}">
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="8"/>
+      <c r="B1" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="8"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B3:E3)</f>
+        <v>Skin_Human_1</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="22">
+        <v>1</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B4:E4)</f>
+        <v>Skin_Dog_1</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="22">
+        <v>1</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B5:E5)</f>
+        <v>Skin_Eagle_1</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="22">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B6:E6)</f>
+        <v>Skin_Snake_1</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="22">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>183</v>
+      </c>
+      <c r="M6" t="s">
+        <v>185</v>
+      </c>
+      <c r="N6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="22"/>
+      <c r="L7" t="s">
+        <v>187</v>
+      </c>
+      <c r="M7" t="s">
+        <v>186</v>
+      </c>
+      <c r="N7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="L8" t="s">
+        <v>188</v>
+      </c>
+      <c r="M8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="L9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M9" t="s">
+        <v>191</v>
+      </c>
+      <c r="N9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="L10" t="s">
+        <v>192</v>
+      </c>
+      <c r="M10" t="s">
+        <v>194</v>
+      </c>
+      <c r="N10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="L11" t="s">
+        <v>195</v>
+      </c>
+      <c r="M11" t="s">
+        <v>194</v>
+      </c>
+      <c r="N11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="L12" t="s">
+        <v>197</v>
+      </c>
+      <c r="M12" t="s">
+        <v>194</v>
+      </c>
+      <c r="N12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="C13" s="9"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="C16" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C8E724-28BD-8649-A64E-E00F04A859F7}">
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
@@ -2629,7 +3733,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>1</v>
@@ -2644,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>9</v>
@@ -2657,25 +3761,25 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2701,16 +3805,16 @@
         <v>1</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="L3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2738,7 +3842,9 @@
     </row>
     <row r="8" spans="1:12">
       <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="G8" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
@@ -2750,7 +3856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7280A486-F06C-3245-9C19-439155A4666B}">
   <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
@@ -2800,19 +3906,19 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
@@ -2828,25 +3934,25 @@
         <v>Projectile_Human</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -2942,7 +4048,7 @@
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>0</v>
@@ -2955,10 +4061,10 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2970,7 +4076,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="7" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -2981,17 +4087,17 @@
         <v>AI_Flow_DefaultDetectionRange</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G5" s="9">
         <v>6</v>
@@ -3003,16 +4109,16 @@
         <v>AI_Flow_DefaultAttackRange</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G6" s="9">
         <v>1.5</v>
@@ -3024,16 +4130,16 @@
         <v>AI_Flow_TargetLostRangeOffset</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F7" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G7" s="9">
         <v>2</v>
@@ -3045,16 +4151,16 @@
         <v>AI_Flow_FoolowDistanceRatio</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G8" s="9">
         <v>0.9</v>
@@ -3106,13 +4212,13 @@
         <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -3127,16 +4233,16 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -3152,19 +4258,19 @@
         <v>Spawner_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G3" s="17">
         <v>100100</v>
@@ -3300,30 +4406,31 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A933480A-994B-A74A-B07D-EEB09A80B87F}">
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="21.7109375" customWidth="1"/>
-    <col min="13" max="13" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="21.7109375" customWidth="1"/>
+    <col min="14" max="14" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5" t="s">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>0</v>
@@ -3334,94 +4441,100 @@
       <c r="H1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>15</v>
+      <c r="I1" s="5" t="s">
+        <v>0</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="O1" s="5" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="R1" s="5"/>
+        <v>149</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>151</v>
+      </c>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
-    </row>
-    <row r="2" spans="1:23">
+      <c r="X1" s="5"/>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="R2" s="6"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="6"/>
+        <v>150</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="S2" s="6"/>
+      <c r="T2" s="14"/>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
-    </row>
-    <row r="3" spans="1:23">
+      <c r="X2" s="6"/>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
         <v>Player_Human</v>
@@ -3430,49 +4543,53 @@
         <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="9">
+        <v>46</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,"Skin",C3,"1")</f>
+        <v>Skin_Human_1</v>
+      </c>
+      <c r="E3" s="9">
         <v>100</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>115</v>
-      </c>
       <c r="F3" s="9" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="N3" s="9">
+        <v>106</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="9">
         <v>100</v>
       </c>
-      <c r="O3" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
+      <c r="P3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="R3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
         <v>Player_Dog</v>
@@ -3481,49 +4598,53 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="9">
+        <v>68</v>
+      </c>
+      <c r="D4" s="9" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,"Skin",C4,"1")</f>
+        <v>Skin_Dog_1</v>
+      </c>
+      <c r="E4" s="9">
         <v>100</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>115</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="N4" s="9">
+        <v>106</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="O4" s="9">
         <v>100</v>
       </c>
-      <c r="O4" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
+      <c r="P4" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="R4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
         <v>Player_Eagle</v>
@@ -3532,49 +4653,53 @@
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="9">
+        <v>69</v>
+      </c>
+      <c r="D5" s="9" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,"Skin",C5,"1")</f>
+        <v>Skin_Eagle_1</v>
+      </c>
+      <c r="E5" s="9">
         <v>100</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>115</v>
-      </c>
       <c r="F5" s="9" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="N5" s="9">
+        <v>106</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="O5" s="9">
         <v>100</v>
       </c>
-      <c r="O5" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
+      <c r="P5" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="R5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6,C6)</f>
         <v>Player_Snake</v>
@@ -3583,49 +4708,53 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="9">
+        <v>70</v>
+      </c>
+      <c r="D6" s="9" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,"Skin",C6,"1")</f>
+        <v>Skin_Snake_1</v>
+      </c>
+      <c r="E6" s="9">
         <v>100</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>115</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="N6" s="9">
+        <v>106</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" s="9">
         <v>100</v>
       </c>
-      <c r="O6" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
+      <c r="P6" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="R6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -3635,215 +4764,241 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="11"/>
+      <c r="I7" s="9"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
-      <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="1:23">
+      <c r="L7" s="11"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" spans="1:24">
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:23">
+      <c r="H8" s="9"/>
+      <c r="L8" s="9"/>
+    </row>
+    <row r="9" spans="1:24">
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="K9" s="9"/>
-    </row>
-    <row r="10" spans="1:23">
+      <c r="H9" s="9"/>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" spans="1:24">
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" spans="1:23">
+      <c r="H10" s="9"/>
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" spans="1:24">
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
-      <c r="K11" s="9"/>
-    </row>
-    <row r="12" spans="1:23">
+      <c r="H11" s="9"/>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="1:24">
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="4"/>
-      <c r="K12" s="9"/>
-    </row>
-    <row r="13" spans="1:23">
+      <c r="H12" s="9"/>
+      <c r="I12" s="4"/>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" spans="1:24">
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="K13" s="9"/>
-    </row>
-    <row r="14" spans="1:23">
+      <c r="H13" s="9"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="1:24">
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="3"/>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:23">
+      <c r="H14" s="9"/>
+      <c r="I14" s="3"/>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="1:24">
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="4"/>
-      <c r="K15" s="9"/>
-    </row>
-    <row r="16" spans="1:23">
+      <c r="H15" s="9"/>
+      <c r="I15" s="4"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:24">
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="4"/>
-      <c r="K16" s="9"/>
-    </row>
-    <row r="17" spans="3:11">
+      <c r="H16" s="9"/>
+      <c r="I16" s="4"/>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="3:12">
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="K17" s="9"/>
-    </row>
-    <row r="18" spans="3:11">
+      <c r="I17" s="9"/>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="3:12">
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-      <c r="K18" s="9"/>
-    </row>
-    <row r="19" spans="3:11">
+      <c r="H18" s="9"/>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" spans="3:12">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="K19" s="9"/>
-    </row>
-    <row r="20" spans="3:11">
+      <c r="H19" s="9"/>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" spans="3:12">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-      <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="3:11">
+      <c r="H20" s="9"/>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" spans="3:12">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
-      <c r="K21" s="9"/>
-    </row>
-    <row r="22" spans="3:11">
+      <c r="H21" s="9"/>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" spans="3:12">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
-      <c r="K22" s="9"/>
-    </row>
-    <row r="23" spans="3:11">
+      <c r="H22" s="9"/>
+      <c r="L22" s="9"/>
+    </row>
+    <row r="23" spans="3:12">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="K23" s="9"/>
-    </row>
-    <row r="24" spans="3:11">
+      <c r="H23" s="9"/>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" spans="3:12">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
-      <c r="K24" s="9"/>
-    </row>
-    <row r="25" spans="3:11">
+      <c r="H24" s="9"/>
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" spans="3:12">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="K25" s="9"/>
-    </row>
-    <row r="26" spans="3:11">
+      <c r="H25" s="9"/>
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" spans="3:12">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
-      <c r="K26" s="9"/>
-    </row>
-    <row r="27" spans="3:11">
+      <c r="H26" s="9"/>
+      <c r="L26" s="9"/>
+    </row>
+    <row r="27" spans="3:12">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="K27" s="9"/>
-    </row>
-    <row r="28" spans="3:11">
+      <c r="H27" s="9"/>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="3:12">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="K28" s="9"/>
-    </row>
-    <row r="29" spans="3:11">
+      <c r="H28" s="9"/>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="3:12">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="K29" s="9"/>
-    </row>
-    <row r="30" spans="3:11">
+      <c r="H29" s="9"/>
+      <c r="L29" s="9"/>
+    </row>
+    <row r="30" spans="3:12">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
-      <c r="K30" s="9"/>
-    </row>
-    <row r="31" spans="3:11">
+      <c r="H30" s="9"/>
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" spans="3:12">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
-      <c r="K31" s="9"/>
-    </row>
-    <row r="32" spans="3:11">
+      <c r="H31" s="9"/>
+      <c r="L31" s="9"/>
+    </row>
+    <row r="32" spans="3:12">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="K32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="L32" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3853,9 +5008,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FBA1699A-C505-8C41-9338-26277C216689}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1017</xm:f>
+            <xm:f>Enum!$H$2:$H$1029</xm:f>
           </x14:formula1>
-          <xm:sqref>R3:R7</xm:sqref>
+          <xm:sqref>S3:S7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3865,54 +5020,57 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA670E5-D6A8-8742-AF98-6CB0AA05A8B1}">
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:Y178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>0</v>
+      <c r="G1" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
@@ -3921,376 +5079,4817 @@
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="J2" s="8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="N2" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
-      <c r="R2" s="14"/>
+      <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
+      <c r="U2" s="14"/>
       <c r="V2" s="6"/>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B3,C3)</f>
-        <v>Item_WoodSword</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="11" t="s">
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+    </row>
+    <row r="3" spans="1:25" ht="32" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B4:F4)</f>
+        <v>Item_RHand_Bow</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="2"/>
+      <c r="H4" t="s">
+        <v>257</v>
+      </c>
+      <c r="I4" t="s">
+        <v>257</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="M4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B5:F5)</f>
+        <v>Item_RHand_Bow</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="2"/>
+      <c r="H5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I5" t="s">
+        <v>258</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="M5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B6:F6)</f>
+        <v>Item_RHand_Bow</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="2"/>
+      <c r="H6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I6" t="s">
+        <v>259</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="M6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
+        <v>Item_RHand_Bow</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="H7" t="s">
+        <v>260</v>
+      </c>
+      <c r="I7" t="s">
+        <v>260</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="M7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B8:F8)</f>
+        <v>Item_RHand_Bow</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="H8" t="s">
+        <v>261</v>
+      </c>
+      <c r="I8" t="s">
+        <v>261</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="M8" t="s">
+        <v>11</v>
+      </c>
+      <c r="N8">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B9:F9)</f>
+        <v>Item_RHand_Bow</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>212</v>
+      </c>
+      <c r="D9" t="s">
+        <v>209</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="H9" t="s">
+        <v>262</v>
+      </c>
+      <c r="I9" t="s">
+        <v>262</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="M9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N9">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B10:F10)</f>
+        <v>Item_RHand_Bow</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="H10" t="s">
+        <v>263</v>
+      </c>
+      <c r="I10" t="s">
+        <v>263</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="M10" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
+        <v>Item_RHand_Bow</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D11" t="s">
+        <v>209</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="H11" t="s">
+        <v>264</v>
+      </c>
+      <c r="I11" t="s">
+        <v>264</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="M11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N11">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="9"/>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B13:F13)</f>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" t="s">
+        <v>247</v>
+      </c>
+      <c r="I13" t="s">
+        <v>247</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L13" s="11"/>
+      <c r="M13" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B14:F14)</f>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D14" t="s">
+        <v>210</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" t="s">
+        <v>248</v>
+      </c>
+      <c r="I14" t="s">
+        <v>248</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L14" s="11"/>
+      <c r="M14" t="s">
+        <v>11</v>
+      </c>
+      <c r="N14">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" s="7" t="str">
+        <f t="shared" ref="A15:A22" si="0">_xlfn.TEXTJOIN("_",TRUE,B15:F15)</f>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>212</v>
+      </c>
+      <c r="D15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" t="s">
+        <v>249</v>
+      </c>
+      <c r="I15" t="s">
+        <v>249</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L15" s="11"/>
+      <c r="M15" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" t="s">
+        <v>250</v>
+      </c>
+      <c r="I16" t="s">
+        <v>250</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L16" s="11"/>
+      <c r="M16" t="s">
+        <v>11</v>
+      </c>
+      <c r="N16">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D17" t="s">
+        <v>210</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" t="s">
+        <v>251</v>
+      </c>
+      <c r="I17" t="s">
+        <v>251</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L17" s="11"/>
+      <c r="M17" t="s">
+        <v>11</v>
+      </c>
+      <c r="N17">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>212</v>
+      </c>
+      <c r="D18" t="s">
+        <v>210</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" t="s">
+        <v>252</v>
+      </c>
+      <c r="I18" t="s">
+        <v>252</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="M18" t="s">
+        <v>11</v>
+      </c>
+      <c r="N18">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>212</v>
+      </c>
+      <c r="D19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" t="s">
+        <v>253</v>
+      </c>
+      <c r="I19" t="s">
+        <v>253</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L19" s="11"/>
+      <c r="M19" t="s">
+        <v>11</v>
+      </c>
+      <c r="N19">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>212</v>
+      </c>
+      <c r="D20" t="s">
+        <v>210</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" t="s">
+        <v>254</v>
+      </c>
+      <c r="I20" t="s">
+        <v>254</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L20" s="11"/>
+      <c r="M20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N20">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>212</v>
+      </c>
+      <c r="D21" t="s">
+        <v>210</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" t="s">
+        <v>255</v>
+      </c>
+      <c r="I21" t="s">
+        <v>255</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L21" s="11"/>
+      <c r="M21" t="s">
+        <v>11</v>
+      </c>
+      <c r="N21">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Item_RHand_Shield</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>212</v>
+      </c>
+      <c r="D22" t="s">
+        <v>210</v>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" t="s">
+        <v>256</v>
+      </c>
+      <c r="I22" t="s">
+        <v>256</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L22" s="11"/>
+      <c r="M22" t="s">
+        <v>11</v>
+      </c>
+      <c r="N22">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="9"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="7" t="str">
+        <f t="shared" ref="A24" si="1">_xlfn.TEXTJOIN("_",TRUE,B24:F24)</f>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>213</v>
+      </c>
+      <c r="D24" t="s">
+        <v>211</v>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L24" s="11"/>
+      <c r="M24" t="s">
+        <v>11</v>
+      </c>
+      <c r="N24">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="7" t="str">
+        <f t="shared" ref="A25:A41" si="2">_xlfn.TEXTJOIN("_",TRUE,B25:F25)</f>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>213</v>
+      </c>
+      <c r="D25" t="s">
+        <v>211</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L25" s="11"/>
+      <c r="M25" t="s">
+        <v>11</v>
+      </c>
+      <c r="N25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>213</v>
+      </c>
+      <c r="D26" t="s">
+        <v>211</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L26" s="11"/>
+      <c r="M26" t="s">
+        <v>11</v>
+      </c>
+      <c r="N26">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>213</v>
+      </c>
+      <c r="D27" t="s">
+        <v>211</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L27" s="11"/>
+      <c r="M27" t="s">
+        <v>11</v>
+      </c>
+      <c r="N27">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D28" t="s">
+        <v>211</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L28" s="11"/>
+      <c r="M28" t="s">
+        <v>11</v>
+      </c>
+      <c r="N28">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>213</v>
+      </c>
+      <c r="D29" t="s">
+        <v>211</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L29" s="11"/>
+      <c r="M29" t="s">
+        <v>11</v>
+      </c>
+      <c r="N29">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>213</v>
+      </c>
+      <c r="D30" t="s">
+        <v>211</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L30" s="11"/>
+      <c r="M30" t="s">
+        <v>11</v>
+      </c>
+      <c r="N30">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>213</v>
+      </c>
+      <c r="D31" t="s">
+        <v>211</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L31" s="11"/>
+      <c r="M31" t="s">
+        <v>11</v>
+      </c>
+      <c r="N31">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>213</v>
+      </c>
+      <c r="D32" t="s">
+        <v>211</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L32" s="11"/>
+      <c r="M32" t="s">
+        <v>11</v>
+      </c>
+      <c r="N32">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>213</v>
+      </c>
+      <c r="D33" t="s">
+        <v>211</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L33" s="11"/>
+      <c r="M33" t="s">
+        <v>11</v>
+      </c>
+      <c r="N33">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>213</v>
+      </c>
+      <c r="D34" t="s">
+        <v>211</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L34" s="11"/>
+      <c r="M34" t="s">
+        <v>11</v>
+      </c>
+      <c r="N34">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>213</v>
+      </c>
+      <c r="D35" t="s">
+        <v>211</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L35" s="11"/>
+      <c r="M35" t="s">
+        <v>11</v>
+      </c>
+      <c r="N35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>213</v>
+      </c>
+      <c r="D36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L36" s="11"/>
+      <c r="M36" t="s">
+        <v>11</v>
+      </c>
+      <c r="N36">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" t="s">
+        <v>211</v>
+      </c>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L37" s="11"/>
+      <c r="M37" t="s">
+        <v>11</v>
+      </c>
+      <c r="N37">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>213</v>
+      </c>
+      <c r="D38" t="s">
+        <v>211</v>
+      </c>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L38" s="11"/>
+      <c r="M38" t="s">
+        <v>11</v>
+      </c>
+      <c r="N38">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>213</v>
+      </c>
+      <c r="D39" t="s">
+        <v>211</v>
+      </c>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L39" s="11"/>
+      <c r="M39" t="s">
+        <v>11</v>
+      </c>
+      <c r="N39">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>213</v>
+      </c>
+      <c r="D40" t="s">
+        <v>211</v>
+      </c>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L40" s="11"/>
+      <c r="M40" t="s">
+        <v>11</v>
+      </c>
+      <c r="N40">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>Item_LHand_Sword</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>213</v>
+      </c>
+      <c r="D41" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L41" s="11"/>
+      <c r="M41" t="s">
+        <v>11</v>
+      </c>
+      <c r="N41">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="9"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="7" t="str">
+        <f t="shared" ref="A43:A47" si="3">_xlfn.TEXTJOIN("_",TRUE,B43:F43)</f>
+        <v>Item_LHand_Staff</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>213</v>
+      </c>
+      <c r="D43" t="s">
+        <v>217</v>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="I43" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L43" s="11"/>
+      <c r="M43" t="s">
+        <v>11</v>
+      </c>
+      <c r="N43">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Item_LHand_Staff</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>213</v>
+      </c>
+      <c r="D44" t="s">
+        <v>217</v>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="I44" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L44" s="11"/>
+      <c r="M44" t="s">
+        <v>11</v>
+      </c>
+      <c r="N44">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Item_LHand_Staff</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>213</v>
+      </c>
+      <c r="D45" t="s">
+        <v>217</v>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="I45" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L45" s="11"/>
+      <c r="M45" t="s">
+        <v>11</v>
+      </c>
+      <c r="N45">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Item_LHand_Staff</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" t="s">
+        <v>217</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="I46" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L46" s="11"/>
+      <c r="M46" t="s">
+        <v>11</v>
+      </c>
+      <c r="N46">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>Item_LHand_Staff</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>213</v>
+      </c>
+      <c r="D47" t="s">
+        <v>217</v>
+      </c>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="I47" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L47" s="11"/>
+      <c r="M47" t="s">
+        <v>11</v>
+      </c>
+      <c r="N47">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="9"/>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="7" t="str">
+        <f t="shared" ref="A49:A75" si="4">_xlfn.TEXTJOIN("_",TRUE,B49:F49)</f>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>214</v>
+      </c>
+      <c r="D49" t="s">
+        <v>214</v>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L49" s="11"/>
+      <c r="M49" t="s">
+        <v>11</v>
+      </c>
+      <c r="N49">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>214</v>
+      </c>
+      <c r="D50" t="s">
+        <v>214</v>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L50" s="11"/>
+      <c r="M50" t="s">
+        <v>11</v>
+      </c>
+      <c r="N50">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>214</v>
+      </c>
+      <c r="D51" t="s">
+        <v>214</v>
+      </c>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L51" s="11"/>
+      <c r="M51" t="s">
+        <v>11</v>
+      </c>
+      <c r="N51">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>214</v>
+      </c>
+      <c r="D52" t="s">
+        <v>214</v>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L52" s="11"/>
+      <c r="M52" t="s">
+        <v>11</v>
+      </c>
+      <c r="N52">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>214</v>
+      </c>
+      <c r="D53" t="s">
+        <v>214</v>
+      </c>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L53" s="11"/>
+      <c r="M53" t="s">
+        <v>11</v>
+      </c>
+      <c r="N53">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D54" t="s">
+        <v>214</v>
+      </c>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L54" s="11"/>
+      <c r="M54" t="s">
+        <v>11</v>
+      </c>
+      <c r="N54">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>214</v>
+      </c>
+      <c r="D55" t="s">
+        <v>214</v>
+      </c>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L55" s="11"/>
+      <c r="M55" t="s">
+        <v>11</v>
+      </c>
+      <c r="N55">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>214</v>
+      </c>
+      <c r="D56" t="s">
+        <v>214</v>
+      </c>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L56" s="11"/>
+      <c r="M56" t="s">
+        <v>11</v>
+      </c>
+      <c r="N56">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>214</v>
+      </c>
+      <c r="D57" t="s">
+        <v>214</v>
+      </c>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L57" s="11"/>
+      <c r="M57" t="s">
+        <v>11</v>
+      </c>
+      <c r="N57">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>214</v>
+      </c>
+      <c r="D58" t="s">
+        <v>214</v>
+      </c>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L58" s="11"/>
+      <c r="M58" t="s">
+        <v>11</v>
+      </c>
+      <c r="N58">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>214</v>
+      </c>
+      <c r="D59" t="s">
+        <v>214</v>
+      </c>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L59" s="11"/>
+      <c r="M59" t="s">
+        <v>11</v>
+      </c>
+      <c r="N59">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>214</v>
+      </c>
+      <c r="D60" t="s">
+        <v>214</v>
+      </c>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L60" s="11"/>
+      <c r="M60" t="s">
+        <v>11</v>
+      </c>
+      <c r="N60">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>214</v>
+      </c>
+      <c r="D61" t="s">
+        <v>214</v>
+      </c>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L61" s="11"/>
+      <c r="M61" t="s">
+        <v>11</v>
+      </c>
+      <c r="N61">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>214</v>
+      </c>
+      <c r="D62" t="s">
+        <v>214</v>
+      </c>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L62" s="11"/>
+      <c r="M62" t="s">
+        <v>11</v>
+      </c>
+      <c r="N62">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>214</v>
+      </c>
+      <c r="D63" t="s">
+        <v>214</v>
+      </c>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L63" s="11"/>
+      <c r="M63" t="s">
+        <v>11</v>
+      </c>
+      <c r="N63">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>214</v>
+      </c>
+      <c r="D64" t="s">
+        <v>214</v>
+      </c>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L64" s="11"/>
+      <c r="M64" t="s">
+        <v>11</v>
+      </c>
+      <c r="N64">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>214</v>
+      </c>
+      <c r="D65" t="s">
+        <v>214</v>
+      </c>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L65" s="11"/>
+      <c r="M65" t="s">
+        <v>11</v>
+      </c>
+      <c r="N65">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" t="s">
+        <v>214</v>
+      </c>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L66" s="11"/>
+      <c r="M66" t="s">
+        <v>11</v>
+      </c>
+      <c r="N66">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>214</v>
+      </c>
+      <c r="D67" t="s">
+        <v>214</v>
+      </c>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L67" s="11"/>
+      <c r="M67" t="s">
+        <v>11</v>
+      </c>
+      <c r="N67">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>214</v>
+      </c>
+      <c r="D68" t="s">
+        <v>214</v>
+      </c>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L68" s="11"/>
+      <c r="M68" t="s">
+        <v>11</v>
+      </c>
+      <c r="N68">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>214</v>
+      </c>
+      <c r="D69" t="s">
+        <v>214</v>
+      </c>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L69" s="11"/>
+      <c r="M69" t="s">
+        <v>11</v>
+      </c>
+      <c r="N69">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>214</v>
+      </c>
+      <c r="D70" t="s">
+        <v>214</v>
+      </c>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L70" s="11"/>
+      <c r="M70" t="s">
+        <v>11</v>
+      </c>
+      <c r="N70">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>214</v>
+      </c>
+      <c r="D71" t="s">
+        <v>214</v>
+      </c>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L71" s="11"/>
+      <c r="M71" t="s">
+        <v>11</v>
+      </c>
+      <c r="N71">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>214</v>
+      </c>
+      <c r="D72" t="s">
+        <v>214</v>
+      </c>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L72" s="11"/>
+      <c r="M72" t="s">
+        <v>11</v>
+      </c>
+      <c r="N72">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>214</v>
+      </c>
+      <c r="D73" t="s">
+        <v>214</v>
+      </c>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L73" s="11"/>
+      <c r="M73" t="s">
+        <v>11</v>
+      </c>
+      <c r="N73">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" t="s">
+        <v>214</v>
+      </c>
+      <c r="D74" t="s">
+        <v>214</v>
+      </c>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L74" s="11"/>
+      <c r="M74" t="s">
+        <v>11</v>
+      </c>
+      <c r="N74">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>214</v>
+      </c>
+      <c r="D75" t="s">
+        <v>214</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L75" s="11"/>
+      <c r="M75" t="s">
+        <v>11</v>
+      </c>
+      <c r="N75">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="A76" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B76:F76)</f>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>214</v>
+      </c>
+      <c r="D76" t="s">
+        <v>214</v>
+      </c>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L76" s="11"/>
+      <c r="M76" t="s">
+        <v>11</v>
+      </c>
+      <c r="N76">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B77:F77)</f>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>214</v>
+      </c>
+      <c r="D77" t="s">
+        <v>214</v>
+      </c>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L77" s="11"/>
+      <c r="M77" t="s">
+        <v>11</v>
+      </c>
+      <c r="N77">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
+      <c r="A78" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B78:F78)</f>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>214</v>
+      </c>
+      <c r="D78" t="s">
+        <v>214</v>
+      </c>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="H78" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L78" s="11"/>
+      <c r="M78" t="s">
+        <v>11</v>
+      </c>
+      <c r="N78">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B79:F79)</f>
+        <v>Item_Top_Top</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>214</v>
+      </c>
+      <c r="D79" t="s">
+        <v>214</v>
+      </c>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L79" s="11"/>
+      <c r="M79" t="s">
+        <v>11</v>
+      </c>
+      <c r="N79">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
+      <c r="A80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="L80" s="1"/>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81" s="7" t="str">
+        <f t="shared" ref="A81" si="5">_xlfn.TEXTJOIN("_",TRUE,B81:F81)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>216</v>
+      </c>
+      <c r="D81" t="s">
+        <v>216</v>
+      </c>
+      <c r="H81" t="s">
+        <v>296</v>
+      </c>
+      <c r="I81" t="s">
+        <v>296</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L81" s="11"/>
+      <c r="M81" t="s">
+        <v>11</v>
+      </c>
+      <c r="N81">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B82:F82)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>216</v>
+      </c>
+      <c r="D82" t="s">
+        <v>216</v>
+      </c>
+      <c r="H82" t="s">
+        <v>297</v>
+      </c>
+      <c r="I82" t="s">
+        <v>297</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L82" s="11"/>
+      <c r="M82" t="s">
+        <v>11</v>
+      </c>
+      <c r="N82">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B83:F83)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>216</v>
+      </c>
+      <c r="D83" t="s">
+        <v>216</v>
+      </c>
+      <c r="H83" t="s">
+        <v>298</v>
+      </c>
+      <c r="I83" t="s">
+        <v>298</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L83" s="11"/>
+      <c r="M83" t="s">
+        <v>11</v>
+      </c>
+      <c r="N83">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B84:F84)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>216</v>
+      </c>
+      <c r="D84" t="s">
+        <v>216</v>
+      </c>
+      <c r="H84" t="s">
+        <v>299</v>
+      </c>
+      <c r="I84" t="s">
+        <v>299</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L84" s="11"/>
+      <c r="M84" t="s">
+        <v>11</v>
+      </c>
+      <c r="N84">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B85:F85)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
+        <v>216</v>
+      </c>
+      <c r="D85" t="s">
+        <v>216</v>
+      </c>
+      <c r="H85" t="s">
+        <v>300</v>
+      </c>
+      <c r="I85" t="s">
+        <v>300</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L85" s="11"/>
+      <c r="M85" t="s">
+        <v>11</v>
+      </c>
+      <c r="N85">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86" s="7" t="str">
+        <f t="shared" ref="A86" si="6">_xlfn.TEXTJOIN("_",TRUE,B86:F86)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>216</v>
+      </c>
+      <c r="D86" t="s">
+        <v>216</v>
+      </c>
+      <c r="H86" t="s">
+        <v>301</v>
+      </c>
+      <c r="I86" t="s">
+        <v>301</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L86" s="11"/>
+      <c r="M86" t="s">
+        <v>11</v>
+      </c>
+      <c r="N86">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B87:F87)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" t="s">
+        <v>216</v>
+      </c>
+      <c r="D87" t="s">
+        <v>216</v>
+      </c>
+      <c r="H87" t="s">
+        <v>302</v>
+      </c>
+      <c r="I87" t="s">
+        <v>302</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L87" s="11"/>
+      <c r="M87" t="s">
+        <v>11</v>
+      </c>
+      <c r="N87">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
+      <c r="A88" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B88:F88)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
+        <v>216</v>
+      </c>
+      <c r="D88" t="s">
+        <v>216</v>
+      </c>
+      <c r="H88" t="s">
+        <v>303</v>
+      </c>
+      <c r="I88" t="s">
+        <v>303</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L88" s="11"/>
+      <c r="M88" t="s">
+        <v>11</v>
+      </c>
+      <c r="N88">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
+      <c r="A89" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B89:F89)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>216</v>
+      </c>
+      <c r="D89" t="s">
+        <v>216</v>
+      </c>
+      <c r="H89" t="s">
+        <v>304</v>
+      </c>
+      <c r="I89" t="s">
+        <v>304</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L89" s="11"/>
+      <c r="M89" t="s">
+        <v>11</v>
+      </c>
+      <c r="N89">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="A90" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B90:F90)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
+        <v>216</v>
+      </c>
+      <c r="D90" t="s">
+        <v>216</v>
+      </c>
+      <c r="H90" t="s">
+        <v>305</v>
+      </c>
+      <c r="I90" t="s">
+        <v>305</v>
+      </c>
+      <c r="J90" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L90" s="11"/>
+      <c r="M90" t="s">
+        <v>11</v>
+      </c>
+      <c r="N90">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91" s="7" t="str">
+        <f t="shared" ref="A91" si="7">_xlfn.TEXTJOIN("_",TRUE,B91:F91)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" t="s">
+        <v>216</v>
+      </c>
+      <c r="D91" t="s">
+        <v>216</v>
+      </c>
+      <c r="H91" t="s">
+        <v>306</v>
+      </c>
+      <c r="I91" t="s">
+        <v>306</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L91" s="11"/>
+      <c r="M91" t="s">
+        <v>11</v>
+      </c>
+      <c r="N91">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
+      <c r="A92" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B92:F92)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>216</v>
+      </c>
+      <c r="D92" t="s">
+        <v>216</v>
+      </c>
+      <c r="H92" t="s">
+        <v>307</v>
+      </c>
+      <c r="I92" t="s">
+        <v>307</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K92" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L92" s="11"/>
+      <c r="M92" t="s">
+        <v>11</v>
+      </c>
+      <c r="N92">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
+      <c r="A93" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B93:F93)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" t="s">
+        <v>216</v>
+      </c>
+      <c r="D93" t="s">
+        <v>216</v>
+      </c>
+      <c r="H93" t="s">
+        <v>308</v>
+      </c>
+      <c r="I93" t="s">
+        <v>308</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K93" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L93" s="11"/>
+      <c r="M93" t="s">
+        <v>11</v>
+      </c>
+      <c r="N93">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
+      <c r="A94" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B94:F94)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" t="s">
+        <v>216</v>
+      </c>
+      <c r="D94" t="s">
+        <v>216</v>
+      </c>
+      <c r="H94" t="s">
+        <v>309</v>
+      </c>
+      <c r="I94" t="s">
+        <v>309</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K94" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L94" s="11"/>
+      <c r="M94" t="s">
+        <v>11</v>
+      </c>
+      <c r="N94">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
+      <c r="A95" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B95:F95)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" t="s">
+        <v>216</v>
+      </c>
+      <c r="D95" t="s">
+        <v>216</v>
+      </c>
+      <c r="H95" t="s">
+        <v>310</v>
+      </c>
+      <c r="I95" t="s">
+        <v>310</v>
+      </c>
+      <c r="J95" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K95" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L95" s="11"/>
+      <c r="M95" t="s">
+        <v>11</v>
+      </c>
+      <c r="N95">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
+      <c r="A96" s="7" t="str">
+        <f t="shared" ref="A96" si="8">_xlfn.TEXTJOIN("_",TRUE,B96:F96)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" t="s">
+        <v>216</v>
+      </c>
+      <c r="D96" t="s">
+        <v>216</v>
+      </c>
+      <c r="H96" t="s">
+        <v>311</v>
+      </c>
+      <c r="I96" t="s">
+        <v>311</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K96" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L96" s="11"/>
+      <c r="M96" t="s">
+        <v>11</v>
+      </c>
+      <c r="N96">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
+      <c r="A97" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B97:F97)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" t="s">
+        <v>216</v>
+      </c>
+      <c r="D97" t="s">
+        <v>216</v>
+      </c>
+      <c r="H97" t="s">
+        <v>312</v>
+      </c>
+      <c r="I97" t="s">
+        <v>312</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K97" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L97" s="11"/>
+      <c r="M97" t="s">
+        <v>11</v>
+      </c>
+      <c r="N97">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
+      <c r="A98" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B98:F98)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" t="s">
+        <v>216</v>
+      </c>
+      <c r="D98" t="s">
+        <v>216</v>
+      </c>
+      <c r="H98" t="s">
+        <v>313</v>
+      </c>
+      <c r="I98" t="s">
+        <v>313</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K98" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L98" s="11"/>
+      <c r="M98" t="s">
+        <v>11</v>
+      </c>
+      <c r="N98">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
+      <c r="A99" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B99:F99)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B99" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" t="s">
+        <v>216</v>
+      </c>
+      <c r="D99" t="s">
+        <v>216</v>
+      </c>
+      <c r="H99" t="s">
+        <v>314</v>
+      </c>
+      <c r="I99" t="s">
+        <v>314</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K99" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L99" s="11"/>
+      <c r="M99" t="s">
+        <v>11</v>
+      </c>
+      <c r="N99">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
+      <c r="A100" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B100:F100)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" t="s">
+        <v>216</v>
+      </c>
+      <c r="D100" t="s">
+        <v>216</v>
+      </c>
+      <c r="H100" t="s">
+        <v>315</v>
+      </c>
+      <c r="I100" t="s">
+        <v>315</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K100" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L100" s="11"/>
+      <c r="M100" t="s">
+        <v>11</v>
+      </c>
+      <c r="N100">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
+      <c r="A101" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B101:F101)</f>
+        <v>Item_Pants_Pants</v>
+      </c>
+      <c r="B101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" t="s">
+        <v>216</v>
+      </c>
+      <c r="D101" t="s">
+        <v>216</v>
+      </c>
+      <c r="H101" t="s">
+        <v>316</v>
+      </c>
+      <c r="I101" t="s">
+        <v>316</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K101" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L101" s="11"/>
+      <c r="M101" t="s">
+        <v>11</v>
+      </c>
+      <c r="N101">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="A102" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
+      <c r="A103" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,B103:F103)</f>
+        <v>Item_Cape_Cape</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>218</v>
+      </c>
+      <c r="D103" t="s">
+        <v>218</v>
+      </c>
+      <c r="H103" t="s">
+        <v>317</v>
+      </c>
+      <c r="I103" t="s">
+        <v>317</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K103" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L103" s="11"/>
+      <c r="M103" t="s">
+        <v>11</v>
+      </c>
+      <c r="N103">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
+      <c r="A104" s="7" t="str">
+        <f t="shared" ref="A104:A108" si="9">_xlfn.TEXTJOIN("_",TRUE,B104:F104)</f>
+        <v>Item_Cape_Cape</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" t="s">
+        <v>218</v>
+      </c>
+      <c r="D104" t="s">
+        <v>218</v>
+      </c>
+      <c r="H104" t="s">
+        <v>318</v>
+      </c>
+      <c r="I104" t="s">
+        <v>318</v>
+      </c>
+      <c r="J104" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K104" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L104" s="11"/>
+      <c r="M104" t="s">
+        <v>11</v>
+      </c>
+      <c r="N104">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
+      <c r="A105" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Item_Cape_Cape</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>218</v>
+      </c>
+      <c r="D105" t="s">
+        <v>218</v>
+      </c>
+      <c r="H105" t="s">
+        <v>319</v>
+      </c>
+      <c r="I105" t="s">
+        <v>319</v>
+      </c>
+      <c r="J105" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K105" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L105" s="11"/>
+      <c r="M105" t="s">
+        <v>11</v>
+      </c>
+      <c r="N105">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
+      <c r="A106" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Item_Cape_Cape</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>218</v>
+      </c>
+      <c r="D106" t="s">
+        <v>218</v>
+      </c>
+      <c r="H106" t="s">
+        <v>320</v>
+      </c>
+      <c r="I106" t="s">
+        <v>320</v>
+      </c>
+      <c r="J106" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K106" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L106" s="11"/>
+      <c r="M106" t="s">
+        <v>11</v>
+      </c>
+      <c r="N106">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
+      <c r="A107" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Item_Cape_Cape</v>
+      </c>
+      <c r="B107" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" t="s">
+        <v>218</v>
+      </c>
+      <c r="D107" t="s">
+        <v>218</v>
+      </c>
+      <c r="H107" t="s">
+        <v>321</v>
+      </c>
+      <c r="I107" t="s">
+        <v>321</v>
+      </c>
+      <c r="J107" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K107" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L107" s="11"/>
+      <c r="M107" t="s">
+        <v>11</v>
+      </c>
+      <c r="N107">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
+      <c r="A108" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>Item_Cape_Cape</v>
+      </c>
+      <c r="B108" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" t="s">
+        <v>218</v>
+      </c>
+      <c r="D108" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" t="s">
+        <v>322</v>
+      </c>
+      <c r="I108" t="s">
+        <v>322</v>
+      </c>
+      <c r="J108" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K108" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L108" s="11"/>
+      <c r="M108" t="s">
+        <v>11</v>
+      </c>
+      <c r="N108">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
+      <c r="A109" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
+      <c r="A110" s="7" t="str">
+        <f t="shared" ref="A110" si="10">_xlfn.TEXTJOIN("_",TRUE,B110:F110)</f>
+        <v>Item_FaceAcc_FaceAcc</v>
+      </c>
+      <c r="B110" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110" t="s">
+        <v>219</v>
+      </c>
+      <c r="D110" t="s">
+        <v>219</v>
+      </c>
+      <c r="H110" t="s">
+        <v>323</v>
+      </c>
+      <c r="I110" t="s">
+        <v>323</v>
+      </c>
+      <c r="J110" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K110" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L110" s="11"/>
+      <c r="M110" t="s">
+        <v>11</v>
+      </c>
+      <c r="N110">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
+      <c r="A111" s="7" t="str">
+        <f t="shared" ref="A111:A116" si="11">_xlfn.TEXTJOIN("_",TRUE,B111:F111)</f>
+        <v>Item_FaceAcc_FaceAcc</v>
+      </c>
+      <c r="B111" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" t="s">
+        <v>219</v>
+      </c>
+      <c r="D111" t="s">
+        <v>219</v>
+      </c>
+      <c r="H111" t="s">
+        <v>324</v>
+      </c>
+      <c r="I111" t="s">
+        <v>324</v>
+      </c>
+      <c r="J111" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K111" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L111" s="11"/>
+      <c r="M111" t="s">
+        <v>11</v>
+      </c>
+      <c r="N111">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
+      <c r="A112" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Item_FaceAcc_FaceAcc</v>
+      </c>
+      <c r="B112" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" t="s">
+        <v>219</v>
+      </c>
+      <c r="D112" t="s">
+        <v>219</v>
+      </c>
+      <c r="H112" t="s">
+        <v>325</v>
+      </c>
+      <c r="I112" t="s">
+        <v>325</v>
+      </c>
+      <c r="J112" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K112" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L112" s="11"/>
+      <c r="M112" t="s">
+        <v>11</v>
+      </c>
+      <c r="N112">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
+      <c r="A113" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Item_FaceAcc_FaceAcc</v>
+      </c>
+      <c r="B113" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" t="s">
+        <v>219</v>
+      </c>
+      <c r="D113" t="s">
+        <v>219</v>
+      </c>
+      <c r="H113" t="s">
+        <v>326</v>
+      </c>
+      <c r="I113" t="s">
+        <v>326</v>
+      </c>
+      <c r="J113" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K113" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L113" s="11"/>
+      <c r="M113" t="s">
+        <v>11</v>
+      </c>
+      <c r="N113">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14">
+      <c r="A114" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Item_FaceAcc_FaceAcc</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" t="s">
+        <v>219</v>
+      </c>
+      <c r="D114" t="s">
+        <v>219</v>
+      </c>
+      <c r="H114" t="s">
+        <v>327</v>
+      </c>
+      <c r="I114" t="s">
+        <v>327</v>
+      </c>
+      <c r="J114" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K114" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L114" s="11"/>
+      <c r="M114" t="s">
+        <v>11</v>
+      </c>
+      <c r="N114">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
+      <c r="A115" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Item_FaceAcc_FaceAcc</v>
+      </c>
+      <c r="B115" t="s">
+        <v>26</v>
+      </c>
+      <c r="C115" t="s">
+        <v>219</v>
+      </c>
+      <c r="D115" t="s">
+        <v>219</v>
+      </c>
+      <c r="H115" t="s">
+        <v>328</v>
+      </c>
+      <c r="I115" t="s">
+        <v>328</v>
+      </c>
+      <c r="J115" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K115" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L115" s="11"/>
+      <c r="M115" t="s">
+        <v>11</v>
+      </c>
+      <c r="N115">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14">
+      <c r="A116" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>Item_FaceAcc_FaceAcc</v>
+      </c>
+      <c r="B116" t="s">
+        <v>26</v>
+      </c>
+      <c r="C116" t="s">
+        <v>219</v>
+      </c>
+      <c r="D116" t="s">
+        <v>219</v>
+      </c>
+      <c r="H116" t="s">
+        <v>329</v>
+      </c>
+      <c r="I116" t="s">
+        <v>329</v>
+      </c>
+      <c r="J116" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K116" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L116" s="11"/>
+      <c r="M116" t="s">
+        <v>11</v>
+      </c>
+      <c r="N116">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
+      <c r="A117" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
+      <c r="A118" s="7" t="str">
+        <f t="shared" ref="A118:A122" si="12">_xlfn.TEXTJOIN("_",TRUE,B118:F118)</f>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B118" t="s">
+        <v>26</v>
+      </c>
+      <c r="C118" t="s">
+        <v>220</v>
+      </c>
+      <c r="D118" t="s">
+        <v>215</v>
+      </c>
+      <c r="H118" t="s">
+        <v>330</v>
+      </c>
+      <c r="I118" t="s">
+        <v>330</v>
+      </c>
+      <c r="J118" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K118" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L118" s="11"/>
+      <c r="M118" t="s">
+        <v>11</v>
+      </c>
+      <c r="N118">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
+      <c r="A119" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B119" t="s">
+        <v>26</v>
+      </c>
+      <c r="C119" t="s">
+        <v>220</v>
+      </c>
+      <c r="D119" t="s">
+        <v>215</v>
+      </c>
+      <c r="H119" t="s">
+        <v>331</v>
+      </c>
+      <c r="I119" t="s">
+        <v>331</v>
+      </c>
+      <c r="J119" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K119" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L119" s="11"/>
+      <c r="M119" t="s">
+        <v>11</v>
+      </c>
+      <c r="N119">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14">
+      <c r="A120" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B120" t="s">
+        <v>26</v>
+      </c>
+      <c r="C120" t="s">
+        <v>220</v>
+      </c>
+      <c r="D120" t="s">
+        <v>215</v>
+      </c>
+      <c r="H120" t="s">
+        <v>332</v>
+      </c>
+      <c r="I120" t="s">
+        <v>332</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K120" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L120" s="11"/>
+      <c r="M120" t="s">
+        <v>11</v>
+      </c>
+      <c r="N120">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
+      <c r="A121" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" t="s">
+        <v>220</v>
+      </c>
+      <c r="D121" t="s">
+        <v>215</v>
+      </c>
+      <c r="H121" t="s">
+        <v>333</v>
+      </c>
+      <c r="I121" t="s">
+        <v>333</v>
+      </c>
+      <c r="J121" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K121" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L121" s="11"/>
+      <c r="M121" t="s">
+        <v>11</v>
+      </c>
+      <c r="N121">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14">
+      <c r="A122" s="7" t="str">
+        <f t="shared" si="12"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B122" t="s">
+        <v>26</v>
+      </c>
+      <c r="C122" t="s">
+        <v>220</v>
+      </c>
+      <c r="D122" t="s">
+        <v>215</v>
+      </c>
+      <c r="H122" t="s">
+        <v>334</v>
+      </c>
+      <c r="I122" t="s">
+        <v>334</v>
+      </c>
+      <c r="J122" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K122" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L122" s="11"/>
+      <c r="M122" t="s">
+        <v>11</v>
+      </c>
+      <c r="N122">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14">
+      <c r="A123" s="7" t="str">
+        <f t="shared" ref="A123:A142" si="13">_xlfn.TEXTJOIN("_",TRUE,B123:F123)</f>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" t="s">
+        <v>220</v>
+      </c>
+      <c r="D123" t="s">
+        <v>215</v>
+      </c>
+      <c r="H123" t="s">
+        <v>335</v>
+      </c>
+      <c r="I123" t="s">
+        <v>335</v>
+      </c>
+      <c r="J123" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K123" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L123" s="11"/>
+      <c r="M123" t="s">
+        <v>11</v>
+      </c>
+      <c r="N123">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14">
+      <c r="A124" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B124" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" t="s">
+        <v>220</v>
+      </c>
+      <c r="D124" t="s">
+        <v>215</v>
+      </c>
+      <c r="H124" t="s">
+        <v>336</v>
+      </c>
+      <c r="I124" t="s">
+        <v>336</v>
+      </c>
+      <c r="J124" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K124" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L124" s="11"/>
+      <c r="M124" t="s">
+        <v>11</v>
+      </c>
+      <c r="N124">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14">
+      <c r="A125" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" t="s">
+        <v>220</v>
+      </c>
+      <c r="D125" t="s">
+        <v>215</v>
+      </c>
+      <c r="H125" t="s">
+        <v>337</v>
+      </c>
+      <c r="I125" t="s">
+        <v>337</v>
+      </c>
+      <c r="J125" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K125" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L125" s="11"/>
+      <c r="M125" t="s">
+        <v>11</v>
+      </c>
+      <c r="N125">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14">
+      <c r="A126" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B126" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" t="s">
+        <v>220</v>
+      </c>
+      <c r="D126" t="s">
+        <v>215</v>
+      </c>
+      <c r="H126" t="s">
+        <v>338</v>
+      </c>
+      <c r="I126" t="s">
+        <v>338</v>
+      </c>
+      <c r="J126" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K126" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L126" s="11"/>
+      <c r="M126" t="s">
+        <v>11</v>
+      </c>
+      <c r="N126">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
+      <c r="A127" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B127" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" t="s">
+        <v>220</v>
+      </c>
+      <c r="D127" t="s">
+        <v>215</v>
+      </c>
+      <c r="H127" t="s">
+        <v>339</v>
+      </c>
+      <c r="I127" t="s">
+        <v>339</v>
+      </c>
+      <c r="J127" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K127" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L127" s="11"/>
+      <c r="M127" t="s">
+        <v>11</v>
+      </c>
+      <c r="N127">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14">
+      <c r="A128" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B128" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" t="s">
+        <v>220</v>
+      </c>
+      <c r="D128" t="s">
+        <v>215</v>
+      </c>
+      <c r="H128" t="s">
+        <v>340</v>
+      </c>
+      <c r="I128" t="s">
+        <v>340</v>
+      </c>
+      <c r="J128" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K128" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L128" s="11"/>
+      <c r="M128" t="s">
+        <v>11</v>
+      </c>
+      <c r="N128">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B129" t="s">
+        <v>26</v>
+      </c>
+      <c r="C129" t="s">
+        <v>220</v>
+      </c>
+      <c r="D129" t="s">
+        <v>215</v>
+      </c>
+      <c r="H129" t="s">
+        <v>341</v>
+      </c>
+      <c r="I129" t="s">
+        <v>341</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K129" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L129" s="11"/>
+      <c r="M129" t="s">
+        <v>11</v>
+      </c>
+      <c r="N129">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14">
+      <c r="A130" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B130" t="s">
+        <v>26</v>
+      </c>
+      <c r="C130" t="s">
+        <v>220</v>
+      </c>
+      <c r="D130" t="s">
+        <v>215</v>
+      </c>
+      <c r="H130" t="s">
+        <v>342</v>
+      </c>
+      <c r="I130" t="s">
+        <v>342</v>
+      </c>
+      <c r="J130" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K130" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L130" s="11"/>
+      <c r="M130" t="s">
+        <v>11</v>
+      </c>
+      <c r="N130">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
+      <c r="A131" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B131" t="s">
+        <v>26</v>
+      </c>
+      <c r="C131" t="s">
+        <v>220</v>
+      </c>
+      <c r="D131" t="s">
+        <v>215</v>
+      </c>
+      <c r="H131" t="s">
+        <v>343</v>
+      </c>
+      <c r="I131" t="s">
+        <v>343</v>
+      </c>
+      <c r="J131" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K131" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L131" s="11"/>
+      <c r="M131" t="s">
+        <v>11</v>
+      </c>
+      <c r="N131">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14">
+      <c r="A132" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B132" t="s">
+        <v>26</v>
+      </c>
+      <c r="C132" t="s">
+        <v>220</v>
+      </c>
+      <c r="D132" t="s">
+        <v>215</v>
+      </c>
+      <c r="H132" t="s">
+        <v>344</v>
+      </c>
+      <c r="I132" t="s">
+        <v>344</v>
+      </c>
+      <c r="J132" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K132" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L132" s="11"/>
+      <c r="M132" t="s">
+        <v>11</v>
+      </c>
+      <c r="N132">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14">
+      <c r="A133" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133" t="s">
+        <v>220</v>
+      </c>
+      <c r="D133" t="s">
+        <v>215</v>
+      </c>
+      <c r="H133" t="s">
+        <v>345</v>
+      </c>
+      <c r="I133" t="s">
+        <v>345</v>
+      </c>
+      <c r="J133" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K133" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L133" s="11"/>
+      <c r="M133" t="s">
+        <v>11</v>
+      </c>
+      <c r="N133">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14">
+      <c r="A134" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B134" t="s">
+        <v>26</v>
+      </c>
+      <c r="C134" t="s">
+        <v>220</v>
+      </c>
+      <c r="D134" t="s">
+        <v>215</v>
+      </c>
+      <c r="H134" t="s">
+        <v>346</v>
+      </c>
+      <c r="I134" t="s">
+        <v>346</v>
+      </c>
+      <c r="J134" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K134" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L134" s="11"/>
+      <c r="M134" t="s">
+        <v>11</v>
+      </c>
+      <c r="N134">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14">
+      <c r="A135" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B135" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135" t="s">
+        <v>220</v>
+      </c>
+      <c r="D135" t="s">
+        <v>215</v>
+      </c>
+      <c r="H135" t="s">
+        <v>347</v>
+      </c>
+      <c r="I135" t="s">
+        <v>347</v>
+      </c>
+      <c r="J135" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K135" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L135" s="11"/>
+      <c r="M135" t="s">
+        <v>11</v>
+      </c>
+      <c r="N135">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14">
+      <c r="A136" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B136" t="s">
+        <v>26</v>
+      </c>
+      <c r="C136" t="s">
+        <v>220</v>
+      </c>
+      <c r="D136" t="s">
+        <v>215</v>
+      </c>
+      <c r="H136" t="s">
+        <v>348</v>
+      </c>
+      <c r="I136" t="s">
+        <v>348</v>
+      </c>
+      <c r="J136" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K136" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L136" s="11"/>
+      <c r="M136" t="s">
+        <v>11</v>
+      </c>
+      <c r="N136">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14">
+      <c r="A137" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_HairAcc_Hat</v>
+      </c>
+      <c r="B137" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137" t="s">
+        <v>220</v>
+      </c>
+      <c r="D137" t="s">
+        <v>215</v>
+      </c>
+      <c r="H137" t="s">
+        <v>349</v>
+      </c>
+      <c r="I137" t="s">
+        <v>349</v>
+      </c>
+      <c r="J137" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="K137" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="L137" s="11"/>
+      <c r="M137" t="s">
+        <v>11</v>
+      </c>
+      <c r="N137">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14">
+      <c r="A138" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C138" s="9"/>
+      <c r="D138" s="9"/>
+      <c r="E138" s="9"/>
+      <c r="F138" s="9"/>
+      <c r="G138" s="9"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="L138" s="11"/>
+      <c r="M138" s="11"/>
+    </row>
+    <row r="139" spans="1:14">
+      <c r="A139" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_Player_Player_Human</v>
+      </c>
+      <c r="B139" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F139" s="9"/>
+      <c r="G139" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H139" t="s">
+        <v>59</v>
+      </c>
+      <c r="I139" t="s">
+        <v>113</v>
+      </c>
+      <c r="J139" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K139" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="L139" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="M139" t="s">
+        <v>11</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14">
+      <c r="A140" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_Player_Player_Dog</v>
+      </c>
+      <c r="B140" t="s">
+        <v>26</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F140" s="9"/>
+      <c r="G140" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H140" t="s">
+        <v>59</v>
+      </c>
+      <c r="I140" t="s">
         <v>114</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="L3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3">
+      <c r="J140" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K140" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="L140" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="M140" t="s">
+        <v>11</v>
+      </c>
+      <c r="N140">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B4,C4)</f>
-        <v>Item_WoodStaff</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="L4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4">
+    <row r="141" spans="1:14">
+      <c r="A141" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_Player_Player_Eagle</v>
+      </c>
+      <c r="B141" t="s">
+        <v>26</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F141" s="9"/>
+      <c r="G141" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H141" t="s">
+        <v>59</v>
+      </c>
+      <c r="I141" t="s">
+        <v>115</v>
+      </c>
+      <c r="J141" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K141" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="L141" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="M141" t="s">
+        <v>11</v>
+      </c>
+      <c r="N141">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B5,C5)</f>
-        <v>Item_WoodBow</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="L5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5">
+    <row r="142" spans="1:14">
+      <c r="A142" s="7" t="str">
+        <f t="shared" si="13"/>
+        <v>Item_Player_Player_Snake</v>
+      </c>
+      <c r="B142" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F142" s="9"/>
+      <c r="G142" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H142" t="s">
+        <v>59</v>
+      </c>
+      <c r="I142" t="s">
+        <v>116</v>
+      </c>
+      <c r="J142" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K142" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="L142" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="M142" t="s">
+        <v>11</v>
+      </c>
+      <c r="N142">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="1"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B7,C7)</f>
-        <v>Item_Human</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="L7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B8,C8)</f>
-        <v>Item_Dog</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" t="s">
-        <v>121</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="L8" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B9,C9)</f>
-        <v>Item_Eagle</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="L9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B10,C10)</f>
-        <v>Item_Snake</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" t="s">
-        <v>123</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="L10" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" spans="1:22">
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" spans="1:22">
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:22">
-      <c r="I14" s="1"/>
+    <row r="177" spans="3:12">
+      <c r="C177" s="9"/>
+      <c r="D177" s="9"/>
+      <c r="E177" s="9"/>
+      <c r="F177" s="9"/>
+      <c r="G177" s="9"/>
+      <c r="H177" s="9"/>
+      <c r="L177" s="1"/>
+    </row>
+    <row r="178" spans="3:12">
+      <c r="L178" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6" xr:uid="{17B1ACDF-E711-444F-BA32-32976EC6EADF}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B59ECF9-BEB9-264A-A494-976028F5B748}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1017</xm:f>
+            <xm:f>Enum!$H$2:$H$1029</xm:f>
           </x14:formula1>
-          <xm:sqref>P3:P7 K6</xm:sqref>
+          <xm:sqref>N138 S4:S73</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4320,7 +9919,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -4338,7 +9937,7 @@
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -4353,23 +9952,23 @@
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="6" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -4385,22 +9984,22 @@
         <v>FactionRelation_Hero</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9" t="str">
@@ -4415,22 +10014,22 @@
         <v>FactionRelation_Faction2</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="str">
@@ -4445,22 +10044,22 @@
         <v>FactionRelation_Faction3</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="9" t="str">
@@ -4475,22 +10074,22 @@
         <v>FactionRelation_Faction4</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="J6" s="9" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,E6:H6)</f>
@@ -4547,7 +10146,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D3DBA599-4157-B940-AFCF-2F7B820F1087}">
           <x14:formula1>
-            <xm:f>Enum!$H$2:$H$1017</xm:f>
+            <xm:f>Enum!$H$2:$H$1029</xm:f>
           </x14:formula1>
           <xm:sqref>L6:M6 Q3:Q7</xm:sqref>
         </x14:dataValidation>
@@ -4571,7 +10170,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>0</v>
@@ -4587,13 +10186,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4602,19 +10201,19 @@
         <v>Grade_Common</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4623,19 +10222,19 @@
         <v>Grade_Uncommon</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -4646,19 +10245,19 @@
         <v>Grade_Rare</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -4669,19 +10268,19 @@
         <v>Grade_Epic</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -4692,19 +10291,19 @@
         <v>Grade_Unique</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -4715,19 +10314,19 @@
         <v>Grade_Legend</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4755,7 +10354,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -4769,13 +10368,13 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4784,19 +10383,19 @@
         <v>SynergeBiome_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4831,7 +10430,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F0F1FFA4-2FD9-9C45-A6EF-56B810B8EE53}">
           <x14:formula1>
-            <xm:f>Enum!$I$2:$I$1017</xm:f>
+            <xm:f>Enum!$I$2:$I$1029</xm:f>
           </x14:formula1>
           <xm:sqref>C5:C6</xm:sqref>
         </x14:dataValidation>

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48BD764-9FA3-8E43-8B93-A4D806DF4CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CDDA2B-2992-2B4C-B841-ED8D4C665BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="10" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="356">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -364,22 +364,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Item_Human</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Dog</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Eagle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Snake</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Spawner</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -614,99 +598,95 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>duration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxStack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Projectile Example</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Attack Example</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 사용 가능 범위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// Stat Example</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BiomeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biomeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ElementType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elementType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApplyStat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Str,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatModifier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GrantSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseSkillOnEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffEffectType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffEffectType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffEffectParam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synergeBuffKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Skill_Human_Projectile_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>duration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxStack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>// Projectile Example</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>// Attack Example</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 사용 가능 범위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>// Stat Example</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BiomeType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>biomeType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ElementType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>elementType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ApplyStat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Str,5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatModifier</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GrantSkill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseSkillOnEnd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffEffectType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buffEffectType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buffEffectParam</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>synergeBuffKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddBuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_Human_Projectile_1</t>
   </si>
   <si>
     <t>float</t>
@@ -1364,6 +1344,22 @@
   </si>
   <si>
     <t>Str,Dex,Int,Physical,Magical</t>
+  </si>
+  <si>
+    <t>Item_Player_Player_Human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Player_Player_Dog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Player_Player_Eagle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Player_Player_Snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2021,7 +2017,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2032,7 +2028,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2241,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>47</v>
@@ -2253,7 +2249,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
@@ -2265,10 +2261,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E26" s="12"/>
     </row>
@@ -2277,10 +2273,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2288,10 +2284,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2299,10 +2295,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2310,10 +2306,10 @@
         <v>7</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2321,10 +2317,10 @@
         <v>8</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C31" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2332,10 +2328,10 @@
         <v>9</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C32" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2346,7 +2342,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2357,7 +2353,7 @@
         <v>25</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2368,7 +2364,7 @@
         <v>25</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2379,7 +2375,7 @@
         <v>25</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2390,7 +2386,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2401,7 +2397,7 @@
         <v>25</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2412,7 +2408,7 @@
         <v>25</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2423,7 +2419,7 @@
         <v>25</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2434,7 +2430,7 @@
         <v>25</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2453,10 +2449,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2464,10 +2460,10 @@
         <v>2</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2475,10 +2471,10 @@
         <v>3</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2486,10 +2482,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -2497,10 +2493,10 @@
         <v>2</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -2508,10 +2504,10 @@
         <v>3</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2519,10 +2515,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2530,10 +2526,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2541,10 +2537,10 @@
         <v>2</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2552,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>24</v>
@@ -2563,10 +2559,10 @@
         <v>2</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2574,10 +2570,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2585,10 +2581,10 @@
         <v>2</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="2"/>
@@ -2600,10 +2596,10 @@
         <v>3</v>
       </c>
       <c r="B56" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="F56" s="9"/>
       <c r="J56" s="11"/>
@@ -2614,10 +2610,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2625,10 +2621,10 @@
         <v>5</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2636,10 +2632,10 @@
         <v>6</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2647,10 +2643,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2658,10 +2654,10 @@
         <v>2</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2669,10 +2665,10 @@
         <v>3</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -2680,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>5</v>
@@ -2691,10 +2687,10 @@
         <v>2</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2702,10 +2698,10 @@
         <v>3</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -2713,10 +2709,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -2848,7 +2844,7 @@
         <v>52</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2869,7 +2865,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2937,7 +2933,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>71</v>
@@ -2949,19 +2945,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>9</v>
@@ -2991,10 +2987,10 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="19" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>29</v>
@@ -3003,22 +2999,22 @@
         <v>30</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M2" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="N2" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>125</v>
-      </c>
       <c r="P2" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -3046,18 +3042,18 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Q3" s="9"/>
       <c r="S3" s="9"/>
@@ -3078,7 +3074,7 @@
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="7" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="S6" s="13"/>
       <c r="T6" s="1"/>
@@ -3092,7 +3088,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>46</v>
@@ -3114,17 +3110,17 @@
         <v>57</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s">
         <v>24</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="S7" s="13"/>
       <c r="T7" s="1"/>
@@ -3138,10 +3134,10 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E8" s="9">
         <v>1</v>
@@ -3160,17 +3156,17 @@
         <v>57</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s">
         <v>24</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="S8" s="13"/>
       <c r="T8" s="1"/>
@@ -3191,7 +3187,7 @@
     </row>
     <row r="11" spans="1:32">
       <c r="A11" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:32">
@@ -3203,10 +3199,10 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E12" s="9">
         <v>1</v>
@@ -3225,20 +3221,20 @@
         <v>58</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N12">
         <v>0.6</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:32">
@@ -3253,7 +3249,7 @@
         <v>46</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E13" s="9">
         <v>1</v>
@@ -3272,19 +3268,19 @@
         <v>57</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N13">
         <v>0.1</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -3299,7 +3295,7 @@
     </row>
     <row r="16" spans="1:32">
       <c r="A16" s="7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3311,7 +3307,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9">
@@ -3331,20 +3327,20 @@
         <v>58</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="N17">
         <v>0.1</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3368,7 +3364,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="19" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3383,7 +3379,7 @@
         <v>46</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E21" s="9">
         <v>1</v>
@@ -3402,20 +3398,20 @@
         <v>58</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="N21">
         <v>0.1</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="P21" s="11" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -3441,16 +3437,16 @@
     <row r="1" spans="1:14">
       <c r="A1" s="8"/>
       <c r="B1" s="20" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>0</v>
@@ -3487,13 +3483,13 @@
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
       <c r="F2" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="G2" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="G2" s="21" t="s">
-        <v>206</v>
-      </c>
       <c r="H2" s="21" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -3502,7 +3498,7 @@
         <v>Skin_Human_1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>46</v>
@@ -3512,13 +3508,13 @@
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="11" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -3527,7 +3523,7 @@
         <v>Skin_Dog_1</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>68</v>
@@ -3537,13 +3533,13 @@
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="22" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -3552,7 +3548,7 @@
         <v>Skin_Eagle_1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>69</v>
@@ -3562,13 +3558,13 @@
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -3577,7 +3573,7 @@
         <v>Skin_Snake_1</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>70</v>
@@ -3587,25 +3583,25 @@
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="22" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M6" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="N6" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3617,13 +3613,13 @@
       <c r="F7" s="11"/>
       <c r="G7" s="22"/>
       <c r="L7" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="M7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="N7" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3635,57 +3631,57 @@
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
       <c r="L8" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="N8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="L9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="M9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="L10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="M10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="N10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="L11" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="M11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="N11" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="L12" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="M12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="N12" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3748,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>9</v>
@@ -3761,13 +3757,13 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>29</v>
@@ -3776,10 +3772,10 @@
         <v>30</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -3805,16 +3801,16 @@
         <v>1</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="L3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3843,7 +3839,7 @@
     <row r="8" spans="1:12">
       <c r="F8" s="9"/>
       <c r="G8" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -3906,7 +3902,7 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>29</v>
@@ -3934,7 +3930,7 @@
         <v>Projectile_Human</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>46</v>
@@ -3943,16 +3939,16 @@
         <v>1</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -4048,7 +4044,7 @@
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>0</v>
@@ -4061,10 +4057,10 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4076,7 +4072,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -4087,17 +4083,17 @@
         <v>AI_Flow_DefaultDetectionRange</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G5" s="9">
         <v>6</v>
@@ -4109,16 +4105,16 @@
         <v>AI_Flow_DefaultAttackRange</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G6" s="9">
         <v>1.5</v>
@@ -4130,16 +4126,16 @@
         <v>AI_Flow_TargetLostRangeOffset</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G7" s="9">
         <v>2</v>
@@ -4151,16 +4147,16 @@
         <v>AI_Flow_FoolowDistanceRatio</v>
       </c>
       <c r="B8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" t="s">
         <v>174</v>
       </c>
-      <c r="C8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" t="s">
-        <v>179</v>
-      </c>
       <c r="F8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G8" s="9">
         <v>0.9</v>
@@ -4218,7 +4214,7 @@
         <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
@@ -4236,13 +4232,13 @@
         <v>74</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -4258,19 +4254,19 @@
         <v>Spawner_Test</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G3" s="17">
         <v>100100</v>
@@ -4463,13 +4459,13 @@
         <v>71</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
@@ -4483,10 +4479,10 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>29</v>
@@ -4519,13 +4515,13 @@
         <v>73</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="S2" s="6"/>
       <c r="T2" s="14"/>
@@ -4553,22 +4549,22 @@
         <v>100</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>75</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L3" s="11" t="s">
         <v>56</v>
@@ -4577,13 +4573,13 @@
         <v>20</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="O3" s="9">
         <v>100</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="R3" t="s">
         <v>42</v>
@@ -4608,22 +4604,22 @@
         <v>100</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>76</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>48</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L4" s="11" t="s">
         <v>56</v>
@@ -4632,13 +4628,13 @@
         <v>21</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="O4" s="9">
         <v>100</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="R4" t="s">
         <v>42</v>
@@ -4663,22 +4659,22 @@
         <v>100</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>77</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>48</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L5" s="11" t="s">
         <v>56</v>
@@ -4687,13 +4683,13 @@
         <v>21</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="O5" s="9">
         <v>100</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="R5" t="s">
         <v>42</v>
@@ -4718,22 +4714,22 @@
         <v>100</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>78</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>48</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>56</v>
@@ -4742,13 +4738,13 @@
         <v>21</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="O6" s="9">
         <v>100</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="R6" t="s">
         <v>42</v>
@@ -5036,7 +5032,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>25</v>
@@ -5087,7 +5083,7 @@
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>27</v>
@@ -5098,7 +5094,7 @@
         <v>22</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>30</v>
@@ -5116,7 +5112,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -5135,7 +5131,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -5144,7 +5140,7 @@
       <c r="G3" s="25"/>
       <c r="H3" s="23"/>
       <c r="I3" s="23" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
@@ -5166,33 +5162,36 @@
     <row r="4" spans="1:25">
       <c r="A4" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B4:F4)</f>
-        <v>Item_RHand_Bow</v>
+        <v>Item_RHand_Bow_1</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>209</v>
+        <v>204</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="2"/>
       <c r="H4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="M4" t="s">
         <v>11</v>
@@ -5204,33 +5203,36 @@
     <row r="5" spans="1:25">
       <c r="A5" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B5:F5)</f>
-        <v>Item_RHand_Bow</v>
+        <v>Item_RHand_Bow_2</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D5" t="s">
-        <v>209</v>
+        <v>204</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="2"/>
       <c r="H5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="M5" t="s">
         <v>11</v>
@@ -5242,33 +5244,36 @@
     <row r="6" spans="1:25">
       <c r="A6" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B6:F6)</f>
-        <v>Item_RHand_Bow</v>
+        <v>Item_RHand_Bow_3</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>204</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="2"/>
       <c r="H6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="M6" t="s">
         <v>11</v>
@@ -5280,32 +5285,35 @@
     <row r="7" spans="1:25">
       <c r="A7" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
-        <v>Item_RHand_Bow</v>
+        <v>Item_RHand_Bow_4</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
+        <v>204</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
       </c>
       <c r="F7" s="9"/>
       <c r="H7" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="I7" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="M7" t="s">
         <v>11</v>
@@ -5317,32 +5325,35 @@
     <row r="8" spans="1:25">
       <c r="A8" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B8:F8)</f>
-        <v>Item_RHand_Bow</v>
+        <v>Item_RHand_Bow_5</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>204</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
       </c>
       <c r="F8" s="9"/>
       <c r="H8" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I8" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="M8" t="s">
         <v>11</v>
@@ -5354,32 +5365,35 @@
     <row r="9" spans="1:25">
       <c r="A9" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B9:F9)</f>
-        <v>Item_RHand_Bow</v>
+        <v>Item_RHand_Bow_6</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D9" t="s">
-        <v>209</v>
+        <v>204</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
       </c>
       <c r="F9" s="9"/>
       <c r="H9" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I9" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="M9" t="s">
         <v>11</v>
@@ -5391,32 +5405,35 @@
     <row r="10" spans="1:25">
       <c r="A10" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B10:F10)</f>
-        <v>Item_RHand_Bow</v>
+        <v>Item_RHand_Bow_7</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D10" t="s">
-        <v>209</v>
+        <v>204</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
       </c>
       <c r="F10" s="9"/>
       <c r="H10" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I10" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="M10" t="s">
         <v>11</v>
@@ -5428,32 +5445,35 @@
     <row r="11" spans="1:25">
       <c r="A11" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
-        <v>Item_RHand_Bow</v>
+        <v>Item_RHand_Bow_8</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>209</v>
+        <v>204</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
       </c>
       <c r="F11" s="9"/>
       <c r="H11" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="I11" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="M11" t="s">
         <v>11</v>
@@ -5477,30 +5497,33 @@
     <row r="13" spans="1:25">
       <c r="A13" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B13:F13)</f>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_1</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D13" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I13" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" t="s">
@@ -5513,30 +5536,33 @@
     <row r="14" spans="1:25">
       <c r="A14" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B14:F14)</f>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_2</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D14" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I14" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L14" s="11"/>
       <c r="M14" t="s">
@@ -5549,30 +5575,33 @@
     <row r="15" spans="1:25">
       <c r="A15" s="7" t="str">
         <f t="shared" ref="A15:A22" si="0">_xlfn.TEXTJOIN("_",TRUE,B15:F15)</f>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_3</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D15" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I15" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L15" s="11"/>
       <c r="M15" t="s">
@@ -5585,30 +5614,33 @@
     <row r="16" spans="1:25">
       <c r="A16" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_4</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D16" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L16" s="11"/>
       <c r="M16" t="s">
@@ -5621,30 +5653,33 @@
     <row r="17" spans="1:14">
       <c r="A17" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_5</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D17" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I17" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L17" s="11"/>
       <c r="M17" t="s">
@@ -5657,30 +5692,33 @@
     <row r="18" spans="1:14">
       <c r="A18" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_6</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D18" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E18">
+        <v>6</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I18" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L18" s="11"/>
       <c r="M18" t="s">
@@ -5693,30 +5731,33 @@
     <row r="19" spans="1:14">
       <c r="A19" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_7</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D19" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E19">
+        <v>7</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="I19" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L19" s="11"/>
       <c r="M19" t="s">
@@ -5729,30 +5770,33 @@
     <row r="20" spans="1:14">
       <c r="A20" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_8</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D20" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E20">
+        <v>8</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I20" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L20" s="11"/>
       <c r="M20" t="s">
@@ -5765,30 +5809,33 @@
     <row r="21" spans="1:14">
       <c r="A21" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_9</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D21" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E21">
+        <v>9</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I21" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L21" s="11"/>
       <c r="M21" t="s">
@@ -5801,30 +5848,33 @@
     <row r="22" spans="1:14">
       <c r="A22" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>Item_RHand_Shield</v>
+        <v>Item_RHand_Shield_10</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D22" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I22" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L22" s="11"/>
       <c r="M22" t="s">
@@ -5849,30 +5899,33 @@
     <row r="24" spans="1:14">
       <c r="A24" s="7" t="str">
         <f t="shared" ref="A24" si="1">_xlfn.TEXTJOIN("_",TRUE,B24:F24)</f>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_1</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D24" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L24" s="11"/>
       <c r="M24" t="s">
@@ -5885,30 +5938,33 @@
     <row r="25" spans="1:14">
       <c r="A25" s="7" t="str">
         <f t="shared" ref="A25:A41" si="2">_xlfn.TEXTJOIN("_",TRUE,B25:F25)</f>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_2</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D25" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L25" s="11"/>
       <c r="M25" t="s">
@@ -5921,30 +5977,33 @@
     <row r="26" spans="1:14">
       <c r="A26" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_3</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D26" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L26" s="11"/>
       <c r="M26" t="s">
@@ -5957,30 +6016,33 @@
     <row r="27" spans="1:14">
       <c r="A27" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_4</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D27" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L27" s="11"/>
       <c r="M27" t="s">
@@ -5993,30 +6055,33 @@
     <row r="28" spans="1:14">
       <c r="A28" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_5</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D28" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E28">
+        <v>5</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L28" s="11"/>
       <c r="M28" t="s">
@@ -6029,30 +6094,33 @@
     <row r="29" spans="1:14">
       <c r="A29" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_6</v>
       </c>
       <c r="B29" t="s">
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D29" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L29" s="11"/>
       <c r="M29" t="s">
@@ -6065,30 +6133,33 @@
     <row r="30" spans="1:14">
       <c r="A30" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_7</v>
       </c>
       <c r="B30" t="s">
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D30" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E30">
+        <v>7</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L30" s="11"/>
       <c r="M30" t="s">
@@ -6101,30 +6172,33 @@
     <row r="31" spans="1:14">
       <c r="A31" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_8</v>
       </c>
       <c r="B31" t="s">
         <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D31" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E31">
+        <v>8</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L31" s="11"/>
       <c r="M31" t="s">
@@ -6137,30 +6211,33 @@
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_9</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D32" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E32">
+        <v>9</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L32" s="11"/>
       <c r="M32" t="s">
@@ -6173,30 +6250,33 @@
     <row r="33" spans="1:14">
       <c r="A33" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_10</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D33" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L33" s="11"/>
       <c r="M33" t="s">
@@ -6209,30 +6289,33 @@
     <row r="34" spans="1:14">
       <c r="A34" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_11</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D34" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E34">
+        <v>11</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L34" s="11"/>
       <c r="M34" t="s">
@@ -6245,30 +6328,33 @@
     <row r="35" spans="1:14">
       <c r="A35" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_12</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D35" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E35">
+        <v>12</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L35" s="11"/>
       <c r="M35" t="s">
@@ -6281,30 +6367,33 @@
     <row r="36" spans="1:14">
       <c r="A36" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_13</v>
       </c>
       <c r="B36" t="s">
         <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D36" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E36">
+        <v>13</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L36" s="11"/>
       <c r="M36" t="s">
@@ -6317,30 +6406,33 @@
     <row r="37" spans="1:14">
       <c r="A37" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_14</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D37" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E37">
+        <v>14</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L37" s="11"/>
       <c r="M37" t="s">
@@ -6353,30 +6445,33 @@
     <row r="38" spans="1:14">
       <c r="A38" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_15</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D38" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E38">
+        <v>15</v>
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L38" s="11"/>
       <c r="M38" t="s">
@@ -6389,30 +6484,33 @@
     <row r="39" spans="1:14">
       <c r="A39" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_16</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D39" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E39">
+        <v>16</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L39" s="11"/>
       <c r="M39" t="s">
@@ -6425,30 +6523,33 @@
     <row r="40" spans="1:14">
       <c r="A40" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_17</v>
       </c>
       <c r="B40" t="s">
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D40" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E40">
+        <v>17</v>
       </c>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L40" s="11"/>
       <c r="M40" t="s">
@@ -6461,30 +6562,33 @@
     <row r="41" spans="1:14">
       <c r="A41" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>Item_LHand_Sword</v>
+        <v>Item_LHand_Sword_18</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D41" t="s">
-        <v>211</v>
+        <v>206</v>
+      </c>
+      <c r="E41">
+        <v>18</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L41" s="11"/>
       <c r="M41" t="s">
@@ -6509,30 +6613,33 @@
     <row r="43" spans="1:14">
       <c r="A43" s="7" t="str">
         <f t="shared" ref="A43:A47" si="3">_xlfn.TEXTJOIN("_",TRUE,B43:F43)</f>
-        <v>Item_LHand_Staff</v>
+        <v>Item_LHand_Staff_1</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D43" t="s">
-        <v>217</v>
+        <v>212</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="9"/>
       <c r="H43" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L43" s="11"/>
       <c r="M43" t="s">
@@ -6545,30 +6652,33 @@
     <row r="44" spans="1:14">
       <c r="A44" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>Item_LHand_Staff</v>
+        <v>Item_LHand_Staff_2</v>
       </c>
       <c r="B44" t="s">
         <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D44" t="s">
-        <v>217</v>
+        <v>212</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="22" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L44" s="11"/>
       <c r="M44" t="s">
@@ -6581,30 +6691,33 @@
     <row r="45" spans="1:14">
       <c r="A45" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>Item_LHand_Staff</v>
+        <v>Item_LHand_Staff_3</v>
       </c>
       <c r="B45" t="s">
         <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D45" t="s">
-        <v>217</v>
+        <v>212</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
       </c>
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="22" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L45" s="11"/>
       <c r="M45" t="s">
@@ -6617,30 +6730,33 @@
     <row r="46" spans="1:14">
       <c r="A46" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>Item_LHand_Staff</v>
+        <v>Item_LHand_Staff_4</v>
       </c>
       <c r="B46" t="s">
         <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D46" t="s">
-        <v>217</v>
+        <v>212</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
       </c>
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
       <c r="H46" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L46" s="11"/>
       <c r="M46" t="s">
@@ -6653,30 +6769,33 @@
     <row r="47" spans="1:14">
       <c r="A47" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>Item_LHand_Staff</v>
+        <v>Item_LHand_Staff_5</v>
       </c>
       <c r="B47" t="s">
         <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D47" t="s">
-        <v>217</v>
+        <v>212</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
       </c>
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
       <c r="H47" s="22" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L47" s="11"/>
       <c r="M47" t="s">
@@ -6701,30 +6820,33 @@
     <row r="49" spans="1:14">
       <c r="A49" s="7" t="str">
         <f t="shared" ref="A49:A75" si="4">_xlfn.TEXTJOIN("_",TRUE,B49:F49)</f>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_1</v>
       </c>
       <c r="B49" t="s">
         <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D49" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L49" s="11"/>
       <c r="M49" t="s">
@@ -6737,30 +6859,33 @@
     <row r="50" spans="1:14">
       <c r="A50" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_2</v>
       </c>
       <c r="B50" t="s">
         <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D50" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
       </c>
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L50" s="11"/>
       <c r="M50" t="s">
@@ -6773,30 +6898,33 @@
     <row r="51" spans="1:14">
       <c r="A51" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_3</v>
       </c>
       <c r="B51" t="s">
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D51" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
       </c>
       <c r="F51" s="9"/>
       <c r="G51" s="9"/>
       <c r="H51" s="9" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L51" s="11"/>
       <c r="M51" t="s">
@@ -6809,30 +6937,33 @@
     <row r="52" spans="1:14">
       <c r="A52" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_4</v>
       </c>
       <c r="B52" t="s">
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D52" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E52">
+        <v>4</v>
       </c>
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
       <c r="H52" s="9" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L52" s="11"/>
       <c r="M52" t="s">
@@ -6845,30 +6976,33 @@
     <row r="53" spans="1:14">
       <c r="A53" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_5</v>
       </c>
       <c r="B53" t="s">
         <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D53" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E53">
+        <v>5</v>
       </c>
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L53" s="11"/>
       <c r="M53" t="s">
@@ -6881,30 +7015,33 @@
     <row r="54" spans="1:14">
       <c r="A54" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_6</v>
       </c>
       <c r="B54" t="s">
         <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D54" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E54">
+        <v>6</v>
       </c>
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
       <c r="H54" s="9" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L54" s="11"/>
       <c r="M54" t="s">
@@ -6917,30 +7054,33 @@
     <row r="55" spans="1:14">
       <c r="A55" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_7</v>
       </c>
       <c r="B55" t="s">
         <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D55" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E55">
+        <v>7</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="9" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L55" s="11"/>
       <c r="M55" t="s">
@@ -6953,30 +7093,33 @@
     <row r="56" spans="1:14">
       <c r="A56" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_8</v>
       </c>
       <c r="B56" t="s">
         <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D56" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E56">
+        <v>8</v>
       </c>
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L56" s="11"/>
       <c r="M56" t="s">
@@ -6989,30 +7132,33 @@
     <row r="57" spans="1:14">
       <c r="A57" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_9</v>
       </c>
       <c r="B57" t="s">
         <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D57" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E57">
+        <v>9</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="9"/>
       <c r="H57" s="9" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L57" s="11"/>
       <c r="M57" t="s">
@@ -7025,30 +7171,33 @@
     <row r="58" spans="1:14">
       <c r="A58" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_10</v>
       </c>
       <c r="B58" t="s">
         <v>26</v>
       </c>
       <c r="C58" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D58" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E58">
+        <v>10</v>
       </c>
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
       <c r="H58" s="9" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L58" s="11"/>
       <c r="M58" t="s">
@@ -7061,30 +7210,33 @@
     <row r="59" spans="1:14">
       <c r="A59" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_11</v>
       </c>
       <c r="B59" t="s">
         <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D59" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E59">
+        <v>11</v>
       </c>
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
       <c r="H59" s="9" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L59" s="11"/>
       <c r="M59" t="s">
@@ -7097,30 +7249,33 @@
     <row r="60" spans="1:14">
       <c r="A60" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_12</v>
       </c>
       <c r="B60" t="s">
         <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D60" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E60">
+        <v>12</v>
       </c>
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L60" s="11"/>
       <c r="M60" t="s">
@@ -7133,30 +7288,33 @@
     <row r="61" spans="1:14">
       <c r="A61" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_13</v>
       </c>
       <c r="B61" t="s">
         <v>26</v>
       </c>
       <c r="C61" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D61" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E61">
+        <v>13</v>
       </c>
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L61" s="11"/>
       <c r="M61" t="s">
@@ -7169,30 +7327,33 @@
     <row r="62" spans="1:14">
       <c r="A62" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_14</v>
       </c>
       <c r="B62" t="s">
         <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D62" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E62">
+        <v>14</v>
       </c>
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
       <c r="H62" s="9" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" t="s">
@@ -7205,30 +7366,33 @@
     <row r="63" spans="1:14">
       <c r="A63" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_15</v>
       </c>
       <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D63" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E63">
+        <v>15</v>
       </c>
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L63" s="11"/>
       <c r="M63" t="s">
@@ -7241,30 +7405,33 @@
     <row r="64" spans="1:14">
       <c r="A64" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_16</v>
       </c>
       <c r="B64" t="s">
         <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D64" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E64">
+        <v>16</v>
       </c>
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
       <c r="H64" s="9" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L64" s="11"/>
       <c r="M64" t="s">
@@ -7277,30 +7444,33 @@
     <row r="65" spans="1:14">
       <c r="A65" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_17</v>
       </c>
       <c r="B65" t="s">
         <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D65" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E65">
+        <v>17</v>
       </c>
       <c r="F65" s="9"/>
       <c r="G65" s="9"/>
       <c r="H65" s="9" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L65" s="11"/>
       <c r="M65" t="s">
@@ -7313,30 +7483,33 @@
     <row r="66" spans="1:14">
       <c r="A66" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_18</v>
       </c>
       <c r="B66" t="s">
         <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D66" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E66">
+        <v>18</v>
       </c>
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="9" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L66" s="11"/>
       <c r="M66" t="s">
@@ -7349,30 +7522,33 @@
     <row r="67" spans="1:14">
       <c r="A67" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_19</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D67" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E67">
+        <v>19</v>
       </c>
       <c r="F67" s="9"/>
       <c r="G67" s="9"/>
       <c r="H67" s="9" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L67" s="11"/>
       <c r="M67" t="s">
@@ -7385,30 +7561,33 @@
     <row r="68" spans="1:14">
       <c r="A68" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_20</v>
       </c>
       <c r="B68" t="s">
         <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D68" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E68">
+        <v>20</v>
       </c>
       <c r="F68" s="9"/>
       <c r="G68" s="9"/>
       <c r="H68" s="9" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L68" s="11"/>
       <c r="M68" t="s">
@@ -7421,30 +7600,33 @@
     <row r="69" spans="1:14">
       <c r="A69" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_21</v>
       </c>
       <c r="B69" t="s">
         <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D69" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E69">
+        <v>21</v>
       </c>
       <c r="F69" s="9"/>
       <c r="G69" s="9"/>
       <c r="H69" s="9" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L69" s="11"/>
       <c r="M69" t="s">
@@ -7457,30 +7639,33 @@
     <row r="70" spans="1:14">
       <c r="A70" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_22</v>
       </c>
       <c r="B70" t="s">
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D70" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E70">
+        <v>22</v>
       </c>
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="9" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L70" s="11"/>
       <c r="M70" t="s">
@@ -7493,30 +7678,33 @@
     <row r="71" spans="1:14">
       <c r="A71" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_23</v>
       </c>
       <c r="B71" t="s">
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D71" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E71">
+        <v>23</v>
       </c>
       <c r="F71" s="9"/>
       <c r="G71" s="9"/>
       <c r="H71" s="9" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K71" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L71" s="11"/>
       <c r="M71" t="s">
@@ -7529,31 +7717,33 @@
     <row r="72" spans="1:14">
       <c r="A72" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_24</v>
       </c>
       <c r="B72" t="s">
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D72" t="s">
-        <v>214</v>
-      </c>
-      <c r="E72" s="9"/>
+        <v>209</v>
+      </c>
+      <c r="E72">
+        <v>24</v>
+      </c>
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
       <c r="H72" s="9" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K72" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L72" s="11"/>
       <c r="M72" t="s">
@@ -7566,31 +7756,33 @@
     <row r="73" spans="1:14">
       <c r="A73" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_25</v>
       </c>
       <c r="B73" t="s">
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D73" t="s">
-        <v>214</v>
-      </c>
-      <c r="E73" s="9"/>
+        <v>209</v>
+      </c>
+      <c r="E73">
+        <v>25</v>
+      </c>
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
       <c r="H73" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L73" s="11"/>
       <c r="M73" t="s">
@@ -7603,31 +7795,33 @@
     <row r="74" spans="1:14">
       <c r="A74" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_26</v>
       </c>
       <c r="B74" t="s">
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D74" t="s">
-        <v>214</v>
-      </c>
-      <c r="E74" s="9"/>
+        <v>209</v>
+      </c>
+      <c r="E74">
+        <v>26</v>
+      </c>
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L74" s="11"/>
       <c r="M74" t="s">
@@ -7640,31 +7834,33 @@
     <row r="75" spans="1:14">
       <c r="A75" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_27</v>
       </c>
       <c r="B75" t="s">
         <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D75" t="s">
-        <v>214</v>
-      </c>
-      <c r="E75" s="9"/>
+        <v>209</v>
+      </c>
+      <c r="E75">
+        <v>27</v>
+      </c>
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
       <c r="H75" s="9" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K75" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L75" s="11"/>
       <c r="M75" t="s">
@@ -7677,31 +7873,33 @@
     <row r="76" spans="1:14">
       <c r="A76" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B76:F76)</f>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_28</v>
       </c>
       <c r="B76" t="s">
         <v>26</v>
       </c>
       <c r="C76" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D76" t="s">
-        <v>214</v>
-      </c>
-      <c r="E76" s="9"/>
+        <v>209</v>
+      </c>
+      <c r="E76">
+        <v>28</v>
+      </c>
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="9" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L76" s="11"/>
       <c r="M76" t="s">
@@ -7714,31 +7912,33 @@
     <row r="77" spans="1:14">
       <c r="A77" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B77:F77)</f>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_29</v>
       </c>
       <c r="B77" t="s">
         <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D77" t="s">
-        <v>214</v>
-      </c>
-      <c r="E77" s="9"/>
+        <v>209</v>
+      </c>
+      <c r="E77">
+        <v>29</v>
+      </c>
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L77" s="11"/>
       <c r="M77" t="s">
@@ -7751,30 +7951,32 @@
     <row r="78" spans="1:14">
       <c r="A78" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B78:F78)</f>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_30</v>
       </c>
       <c r="B78" t="s">
         <v>26</v>
       </c>
       <c r="C78" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D78" t="s">
-        <v>214</v>
-      </c>
-      <c r="E78" s="9"/>
+        <v>209</v>
+      </c>
+      <c r="E78">
+        <v>30</v>
+      </c>
       <c r="F78" s="9"/>
       <c r="H78" s="9" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L78" s="11"/>
       <c r="M78" t="s">
@@ -7787,31 +7989,33 @@
     <row r="79" spans="1:14">
       <c r="A79" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B79:F79)</f>
-        <v>Item_Top_Top</v>
+        <v>Item_Top_Top_31</v>
       </c>
       <c r="B79" t="s">
         <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D79" t="s">
-        <v>214</v>
-      </c>
-      <c r="E79" s="9"/>
+        <v>209</v>
+      </c>
+      <c r="E79">
+        <v>31</v>
+      </c>
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L79" s="11"/>
       <c r="M79" t="s">
@@ -7833,28 +8037,31 @@
     <row r="81" spans="1:14">
       <c r="A81" s="7" t="str">
         <f t="shared" ref="A81" si="5">_xlfn.TEXTJOIN("_",TRUE,B81:F81)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_1</v>
       </c>
       <c r="B81" t="s">
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D81" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I81" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L81" s="11"/>
       <c r="M81" t="s">
@@ -7867,28 +8074,31 @@
     <row r="82" spans="1:14">
       <c r="A82" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B82:F82)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_2</v>
       </c>
       <c r="B82" t="s">
         <v>26</v>
       </c>
       <c r="C82" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D82" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
       </c>
       <c r="H82" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="I82" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L82" s="11"/>
       <c r="M82" t="s">
@@ -7901,28 +8111,31 @@
     <row r="83" spans="1:14">
       <c r="A83" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B83:F83)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_3</v>
       </c>
       <c r="B83" t="s">
         <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D83" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E83">
+        <v>3</v>
       </c>
       <c r="H83" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I83" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L83" s="11"/>
       <c r="M83" t="s">
@@ -7935,28 +8148,31 @@
     <row r="84" spans="1:14">
       <c r="A84" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B84:F84)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_4</v>
       </c>
       <c r="B84" t="s">
         <v>26</v>
       </c>
       <c r="C84" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D84" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E84">
+        <v>4</v>
       </c>
       <c r="H84" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="I84" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L84" s="11"/>
       <c r="M84" t="s">
@@ -7969,28 +8185,31 @@
     <row r="85" spans="1:14">
       <c r="A85" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B85:F85)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_5</v>
       </c>
       <c r="B85" t="s">
         <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D85" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E85">
+        <v>5</v>
       </c>
       <c r="H85" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I85" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L85" s="11"/>
       <c r="M85" t="s">
@@ -8003,28 +8222,31 @@
     <row r="86" spans="1:14">
       <c r="A86" s="7" t="str">
         <f t="shared" ref="A86" si="6">_xlfn.TEXTJOIN("_",TRUE,B86:F86)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_6</v>
       </c>
       <c r="B86" t="s">
         <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D86" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E86">
+        <v>6</v>
       </c>
       <c r="H86" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="I86" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L86" s="11"/>
       <c r="M86" t="s">
@@ -8037,28 +8259,31 @@
     <row r="87" spans="1:14">
       <c r="A87" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B87:F87)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_7</v>
       </c>
       <c r="B87" t="s">
         <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D87" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E87">
+        <v>7</v>
       </c>
       <c r="H87" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="I87" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K87" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L87" s="11"/>
       <c r="M87" t="s">
@@ -8071,28 +8296,31 @@
     <row r="88" spans="1:14">
       <c r="A88" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B88:F88)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_8</v>
       </c>
       <c r="B88" t="s">
         <v>26</v>
       </c>
       <c r="C88" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D88" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E88">
+        <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I88" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L88" s="11"/>
       <c r="M88" t="s">
@@ -8105,28 +8333,31 @@
     <row r="89" spans="1:14">
       <c r="A89" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B89:F89)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_9</v>
       </c>
       <c r="B89" t="s">
         <v>26</v>
       </c>
       <c r="C89" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D89" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E89">
+        <v>9</v>
       </c>
       <c r="H89" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="I89" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K89" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L89" s="11"/>
       <c r="M89" t="s">
@@ -8139,28 +8370,31 @@
     <row r="90" spans="1:14">
       <c r="A90" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B90:F90)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_10</v>
       </c>
       <c r="B90" t="s">
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D90" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E90">
+        <v>10</v>
       </c>
       <c r="H90" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I90" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K90" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L90" s="11"/>
       <c r="M90" t="s">
@@ -8173,28 +8407,31 @@
     <row r="91" spans="1:14">
       <c r="A91" s="7" t="str">
         <f t="shared" ref="A91" si="7">_xlfn.TEXTJOIN("_",TRUE,B91:F91)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_11</v>
       </c>
       <c r="B91" t="s">
         <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D91" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E91">
+        <v>11</v>
       </c>
       <c r="H91" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I91" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K91" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L91" s="11"/>
       <c r="M91" t="s">
@@ -8207,28 +8444,31 @@
     <row r="92" spans="1:14">
       <c r="A92" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B92:F92)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_12</v>
       </c>
       <c r="B92" t="s">
         <v>26</v>
       </c>
       <c r="C92" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D92" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E92">
+        <v>12</v>
       </c>
       <c r="H92" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I92" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K92" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L92" s="11"/>
       <c r="M92" t="s">
@@ -8241,28 +8481,31 @@
     <row r="93" spans="1:14">
       <c r="A93" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B93:F93)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_13</v>
       </c>
       <c r="B93" t="s">
         <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D93" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E93">
+        <v>13</v>
       </c>
       <c r="H93" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I93" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K93" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L93" s="11"/>
       <c r="M93" t="s">
@@ -8275,28 +8518,31 @@
     <row r="94" spans="1:14">
       <c r="A94" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B94:F94)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_14</v>
       </c>
       <c r="B94" t="s">
         <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D94" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E94">
+        <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I94" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="J94" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K94" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L94" s="11"/>
       <c r="M94" t="s">
@@ -8309,28 +8555,31 @@
     <row r="95" spans="1:14">
       <c r="A95" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B95:F95)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_15</v>
       </c>
       <c r="B95" t="s">
         <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D95" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E95">
+        <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="I95" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K95" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L95" s="11"/>
       <c r="M95" t="s">
@@ -8343,28 +8592,31 @@
     <row r="96" spans="1:14">
       <c r="A96" s="7" t="str">
         <f t="shared" ref="A96" si="8">_xlfn.TEXTJOIN("_",TRUE,B96:F96)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_16</v>
       </c>
       <c r="B96" t="s">
         <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D96" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E96">
+        <v>16</v>
       </c>
       <c r="H96" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="I96" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K96" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L96" s="11"/>
       <c r="M96" t="s">
@@ -8377,28 +8629,31 @@
     <row r="97" spans="1:14">
       <c r="A97" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B97:F97)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_17</v>
       </c>
       <c r="B97" t="s">
         <v>26</v>
       </c>
       <c r="C97" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D97" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E97">
+        <v>17</v>
       </c>
       <c r="H97" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I97" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="J97" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K97" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L97" s="11"/>
       <c r="M97" t="s">
@@ -8411,28 +8666,31 @@
     <row r="98" spans="1:14">
       <c r="A98" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B98:F98)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_18</v>
       </c>
       <c r="B98" t="s">
         <v>26</v>
       </c>
       <c r="C98" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D98" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E98">
+        <v>18</v>
       </c>
       <c r="H98" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I98" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="J98" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K98" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L98" s="11"/>
       <c r="M98" t="s">
@@ -8445,28 +8703,31 @@
     <row r="99" spans="1:14">
       <c r="A99" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B99:F99)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_19</v>
       </c>
       <c r="B99" t="s">
         <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D99" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E99">
+        <v>19</v>
       </c>
       <c r="H99" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I99" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="J99" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K99" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L99" s="11"/>
       <c r="M99" t="s">
@@ -8479,28 +8740,31 @@
     <row r="100" spans="1:14">
       <c r="A100" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B100:F100)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_20</v>
       </c>
       <c r="B100" t="s">
         <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D100" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E100">
+        <v>20</v>
       </c>
       <c r="H100" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I100" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J100" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K100" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L100" s="11"/>
       <c r="M100" t="s">
@@ -8513,28 +8777,31 @@
     <row r="101" spans="1:14">
       <c r="A101" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B101:F101)</f>
-        <v>Item_Pants_Pants</v>
+        <v>Item_Pants_Pants_21</v>
       </c>
       <c r="B101" t="s">
         <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D101" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="E101">
+        <v>21</v>
       </c>
       <c r="H101" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="I101" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="J101" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K101" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L101" s="11"/>
       <c r="M101" t="s">
@@ -8552,28 +8819,31 @@
     <row r="103" spans="1:14">
       <c r="A103" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B103:F103)</f>
-        <v>Item_Cape_Cape</v>
+        <v>Item_Cape_Cape_1</v>
       </c>
       <c r="B103" t="s">
         <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D103" t="s">
-        <v>218</v>
+        <v>213</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="I103" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="J103" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K103" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L103" s="11"/>
       <c r="M103" t="s">
@@ -8586,28 +8856,31 @@
     <row r="104" spans="1:14">
       <c r="A104" s="7" t="str">
         <f t="shared" ref="A104:A108" si="9">_xlfn.TEXTJOIN("_",TRUE,B104:F104)</f>
-        <v>Item_Cape_Cape</v>
+        <v>Item_Cape_Cape_2</v>
       </c>
       <c r="B104" t="s">
         <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D104" t="s">
-        <v>218</v>
+        <v>213</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
       </c>
       <c r="H104" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I104" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L104" s="11"/>
       <c r="M104" t="s">
@@ -8620,28 +8893,31 @@
     <row r="105" spans="1:14">
       <c r="A105" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>Item_Cape_Cape</v>
+        <v>Item_Cape_Cape_3</v>
       </c>
       <c r="B105" t="s">
         <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D105" t="s">
-        <v>218</v>
+        <v>213</v>
+      </c>
+      <c r="E105">
+        <v>3</v>
       </c>
       <c r="H105" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I105" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K105" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L105" s="11"/>
       <c r="M105" t="s">
@@ -8654,28 +8930,31 @@
     <row r="106" spans="1:14">
       <c r="A106" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>Item_Cape_Cape</v>
+        <v>Item_Cape_Cape_4</v>
       </c>
       <c r="B106" t="s">
         <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D106" t="s">
-        <v>218</v>
+        <v>213</v>
+      </c>
+      <c r="E106">
+        <v>4</v>
       </c>
       <c r="H106" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I106" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="J106" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K106" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L106" s="11"/>
       <c r="M106" t="s">
@@ -8688,28 +8967,31 @@
     <row r="107" spans="1:14">
       <c r="A107" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>Item_Cape_Cape</v>
+        <v>Item_Cape_Cape_5</v>
       </c>
       <c r="B107" t="s">
         <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D107" t="s">
-        <v>218</v>
+        <v>213</v>
+      </c>
+      <c r="E107">
+        <v>5</v>
       </c>
       <c r="H107" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="I107" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="J107" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K107" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L107" s="11"/>
       <c r="M107" t="s">
@@ -8722,28 +9004,31 @@
     <row r="108" spans="1:14">
       <c r="A108" s="7" t="str">
         <f t="shared" si="9"/>
-        <v>Item_Cape_Cape</v>
+        <v>Item_Cape_Cape_6</v>
       </c>
       <c r="B108" t="s">
         <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D108" t="s">
-        <v>218</v>
+        <v>213</v>
+      </c>
+      <c r="E108">
+        <v>6</v>
       </c>
       <c r="H108" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I108" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="J108" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K108" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L108" s="11"/>
       <c r="M108" t="s">
@@ -8761,28 +9046,31 @@
     <row r="110" spans="1:14">
       <c r="A110" s="7" t="str">
         <f t="shared" ref="A110" si="10">_xlfn.TEXTJOIN("_",TRUE,B110:F110)</f>
-        <v>Item_FaceAcc_FaceAcc</v>
+        <v>Item_FaceAcc_FaceAcc_1</v>
       </c>
       <c r="B110" t="s">
         <v>26</v>
       </c>
       <c r="C110" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
       </c>
       <c r="H110" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="I110" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="J110" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K110" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L110" s="11"/>
       <c r="M110" t="s">
@@ -8795,28 +9083,31 @@
     <row r="111" spans="1:14">
       <c r="A111" s="7" t="str">
         <f t="shared" ref="A111:A116" si="11">_xlfn.TEXTJOIN("_",TRUE,B111:F111)</f>
-        <v>Item_FaceAcc_FaceAcc</v>
+        <v>Item_FaceAcc_FaceAcc_2</v>
       </c>
       <c r="B111" t="s">
         <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D111" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="E111">
+        <v>2</v>
       </c>
       <c r="H111" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="I111" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J111" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K111" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L111" s="11"/>
       <c r="M111" t="s">
@@ -8829,28 +9120,31 @@
     <row r="112" spans="1:14">
       <c r="A112" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>Item_FaceAcc_FaceAcc</v>
+        <v>Item_FaceAcc_FaceAcc_3</v>
       </c>
       <c r="B112" t="s">
         <v>26</v>
       </c>
       <c r="C112" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D112" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="E112">
+        <v>3</v>
       </c>
       <c r="H112" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="I112" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K112" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L112" s="11"/>
       <c r="M112" t="s">
@@ -8863,28 +9157,31 @@
     <row r="113" spans="1:14">
       <c r="A113" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>Item_FaceAcc_FaceAcc</v>
+        <v>Item_FaceAcc_FaceAcc_4</v>
       </c>
       <c r="B113" t="s">
         <v>26</v>
       </c>
       <c r="C113" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D113" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="E113">
+        <v>4</v>
       </c>
       <c r="H113" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I113" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="J113" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K113" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L113" s="11"/>
       <c r="M113" t="s">
@@ -8897,28 +9194,31 @@
     <row r="114" spans="1:14">
       <c r="A114" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>Item_FaceAcc_FaceAcc</v>
+        <v>Item_FaceAcc_FaceAcc_5</v>
       </c>
       <c r="B114" t="s">
         <v>26</v>
       </c>
       <c r="C114" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D114" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="E114">
+        <v>5</v>
       </c>
       <c r="H114" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="I114" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="J114" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K114" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L114" s="11"/>
       <c r="M114" t="s">
@@ -8931,28 +9231,31 @@
     <row r="115" spans="1:14">
       <c r="A115" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>Item_FaceAcc_FaceAcc</v>
+        <v>Item_FaceAcc_FaceAcc_6</v>
       </c>
       <c r="B115" t="s">
         <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D115" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="E115">
+        <v>6</v>
       </c>
       <c r="H115" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I115" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="J115" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K115" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L115" s="11"/>
       <c r="M115" t="s">
@@ -8965,28 +9268,31 @@
     <row r="116" spans="1:14">
       <c r="A116" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>Item_FaceAcc_FaceAcc</v>
+        <v>Item_FaceAcc_FaceAcc_7</v>
       </c>
       <c r="B116" t="s">
         <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D116" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="E116">
+        <v>7</v>
       </c>
       <c r="H116" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I116" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="J116" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K116" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L116" s="11"/>
       <c r="M116" t="s">
@@ -9004,28 +9310,31 @@
     <row r="118" spans="1:14">
       <c r="A118" s="7" t="str">
         <f t="shared" ref="A118:A122" si="12">_xlfn.TEXTJOIN("_",TRUE,B118:F118)</f>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_1</v>
       </c>
       <c r="B118" t="s">
         <v>26</v>
       </c>
       <c r="C118" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D118" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
       </c>
       <c r="H118" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I118" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K118" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L118" s="11"/>
       <c r="M118" t="s">
@@ -9038,28 +9347,31 @@
     <row r="119" spans="1:14">
       <c r="A119" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_2</v>
       </c>
       <c r="B119" t="s">
         <v>26</v>
       </c>
       <c r="C119" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D119" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E119">
+        <v>2</v>
       </c>
       <c r="H119" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="I119" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="J119" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K119" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L119" s="11"/>
       <c r="M119" t="s">
@@ -9072,28 +9384,31 @@
     <row r="120" spans="1:14">
       <c r="A120" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_3</v>
       </c>
       <c r="B120" t="s">
         <v>26</v>
       </c>
       <c r="C120" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D120" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E120">
+        <v>3</v>
       </c>
       <c r="H120" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I120" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="J120" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K120" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L120" s="11"/>
       <c r="M120" t="s">
@@ -9106,28 +9421,31 @@
     <row r="121" spans="1:14">
       <c r="A121" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_4</v>
       </c>
       <c r="B121" t="s">
         <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D121" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E121">
+        <v>4</v>
       </c>
       <c r="H121" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I121" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J121" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K121" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L121" s="11"/>
       <c r="M121" t="s">
@@ -9140,28 +9458,31 @@
     <row r="122" spans="1:14">
       <c r="A122" s="7" t="str">
         <f t="shared" si="12"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_5</v>
       </c>
       <c r="B122" t="s">
         <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D122" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E122">
+        <v>5</v>
       </c>
       <c r="H122" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I122" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K122" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L122" s="11"/>
       <c r="M122" t="s">
@@ -9174,28 +9495,31 @@
     <row r="123" spans="1:14">
       <c r="A123" s="7" t="str">
         <f t="shared" ref="A123:A142" si="13">_xlfn.TEXTJOIN("_",TRUE,B123:F123)</f>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_6</v>
       </c>
       <c r="B123" t="s">
         <v>26</v>
       </c>
       <c r="C123" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D123" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E123">
+        <v>6</v>
       </c>
       <c r="H123" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="I123" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="J123" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K123" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L123" s="11"/>
       <c r="M123" t="s">
@@ -9208,28 +9532,31 @@
     <row r="124" spans="1:14">
       <c r="A124" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_7</v>
       </c>
       <c r="B124" t="s">
         <v>26</v>
       </c>
       <c r="C124" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D124" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E124">
+        <v>7</v>
       </c>
       <c r="H124" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I124" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J124" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K124" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L124" s="11"/>
       <c r="M124" t="s">
@@ -9242,28 +9569,31 @@
     <row r="125" spans="1:14">
       <c r="A125" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_8</v>
       </c>
       <c r="B125" t="s">
         <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D125" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E125">
+        <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I125" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="J125" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K125" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L125" s="11"/>
       <c r="M125" t="s">
@@ -9276,28 +9606,31 @@
     <row r="126" spans="1:14">
       <c r="A126" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_9</v>
       </c>
       <c r="B126" t="s">
         <v>26</v>
       </c>
       <c r="C126" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D126" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E126">
+        <v>9</v>
       </c>
       <c r="H126" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I126" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J126" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K126" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L126" s="11"/>
       <c r="M126" t="s">
@@ -9310,28 +9643,31 @@
     <row r="127" spans="1:14">
       <c r="A127" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_10</v>
       </c>
       <c r="B127" t="s">
         <v>26</v>
       </c>
       <c r="C127" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D127" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E127">
+        <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I127" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J127" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K127" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L127" s="11"/>
       <c r="M127" t="s">
@@ -9344,28 +9680,31 @@
     <row r="128" spans="1:14">
       <c r="A128" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_11</v>
       </c>
       <c r="B128" t="s">
         <v>26</v>
       </c>
       <c r="C128" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D128" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E128">
+        <v>11</v>
       </c>
       <c r="H128" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I128" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J128" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K128" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L128" s="11"/>
       <c r="M128" t="s">
@@ -9378,28 +9717,31 @@
     <row r="129" spans="1:14">
       <c r="A129" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_12</v>
       </c>
       <c r="B129" t="s">
         <v>26</v>
       </c>
       <c r="C129" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D129" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E129">
+        <v>12</v>
       </c>
       <c r="H129" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I129" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="J129" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K129" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L129" s="11"/>
       <c r="M129" t="s">
@@ -9412,28 +9754,31 @@
     <row r="130" spans="1:14">
       <c r="A130" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_13</v>
       </c>
       <c r="B130" t="s">
         <v>26</v>
       </c>
       <c r="C130" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D130" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E130">
+        <v>13</v>
       </c>
       <c r="H130" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I130" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K130" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L130" s="11"/>
       <c r="M130" t="s">
@@ -9446,28 +9791,31 @@
     <row r="131" spans="1:14">
       <c r="A131" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_14</v>
       </c>
       <c r="B131" t="s">
         <v>26</v>
       </c>
       <c r="C131" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D131" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E131">
+        <v>14</v>
       </c>
       <c r="H131" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I131" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J131" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K131" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L131" s="11"/>
       <c r="M131" t="s">
@@ -9480,28 +9828,31 @@
     <row r="132" spans="1:14">
       <c r="A132" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_15</v>
       </c>
       <c r="B132" t="s">
         <v>26</v>
       </c>
       <c r="C132" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D132" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E132">
+        <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="I132" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K132" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L132" s="11"/>
       <c r="M132" t="s">
@@ -9514,28 +9865,31 @@
     <row r="133" spans="1:14">
       <c r="A133" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_16</v>
       </c>
       <c r="B133" t="s">
         <v>26</v>
       </c>
       <c r="C133" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D133" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E133">
+        <v>16</v>
       </c>
       <c r="H133" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I133" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J133" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K133" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L133" s="11"/>
       <c r="M133" t="s">
@@ -9548,28 +9902,31 @@
     <row r="134" spans="1:14">
       <c r="A134" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_17</v>
       </c>
       <c r="B134" t="s">
         <v>26</v>
       </c>
       <c r="C134" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D134" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E134">
+        <v>17</v>
       </c>
       <c r="H134" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I134" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="J134" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K134" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L134" s="11"/>
       <c r="M134" t="s">
@@ -9582,28 +9939,31 @@
     <row r="135" spans="1:14">
       <c r="A135" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_18</v>
       </c>
       <c r="B135" t="s">
         <v>26</v>
       </c>
       <c r="C135" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D135" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E135">
+        <v>18</v>
       </c>
       <c r="H135" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="I135" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J135" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K135" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L135" s="11"/>
       <c r="M135" t="s">
@@ -9616,28 +9976,31 @@
     <row r="136" spans="1:14">
       <c r="A136" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_19</v>
       </c>
       <c r="B136" t="s">
         <v>26</v>
       </c>
       <c r="C136" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D136" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E136">
+        <v>19</v>
       </c>
       <c r="H136" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="I136" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J136" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K136" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L136" s="11"/>
       <c r="M136" t="s">
@@ -9650,28 +10013,31 @@
     <row r="137" spans="1:14">
       <c r="A137" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>Item_HairAcc_Hat</v>
+        <v>Item_HairAcc_Hat_20</v>
       </c>
       <c r="B137" t="s">
         <v>26</v>
       </c>
       <c r="C137" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D137" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="E137">
+        <v>20</v>
       </c>
       <c r="H137" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I137" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="J137" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K137" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L137" s="11"/>
       <c r="M137" t="s">
@@ -9720,16 +10086,16 @@
         <v>59</v>
       </c>
       <c r="I139" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J139" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K139" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L139" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M139" t="s">
         <v>11</v>
@@ -9763,16 +10129,16 @@
         <v>59</v>
       </c>
       <c r="I140" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J140" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K140" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L140" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M140" t="s">
         <v>11</v>
@@ -9806,16 +10172,16 @@
         <v>59</v>
       </c>
       <c r="I141" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J141" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K141" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L141" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M141" t="s">
         <v>11</v>
@@ -9849,16 +10215,16 @@
         <v>59</v>
       </c>
       <c r="I142" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J142" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K142" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L142" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M142" t="s">
         <v>11</v>
@@ -9882,6 +10248,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
@@ -9919,7 +10286,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -9937,7 +10304,7 @@
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -9952,23 +10319,23 @@
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -9984,22 +10351,22 @@
         <v>FactionRelation_Hero</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="9" t="str">
@@ -10014,22 +10381,22 @@
         <v>FactionRelation_Faction2</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="str">
@@ -10044,22 +10411,22 @@
         <v>FactionRelation_Faction3</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="9" t="str">
@@ -10074,22 +10441,22 @@
         <v>FactionRelation_Faction4</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="J6" s="9" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,E6:H6)</f>
@@ -10374,7 +10741,7 @@
         <v>52</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:6">

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CDDA2B-2992-2B4C-B841-ED8D4C665BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D54EDB-A066-9B4F-A1C9-493C8265BD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="-20" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="11" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="361">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -832,22 +832,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>body_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>body_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>body_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>body_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hairKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1359,6 +1343,41 @@
   </si>
   <si>
     <t>Item_Player_Player_Snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Body/Body_0</t>
+  </si>
+  <si>
+    <t>Pixem/Parts/Body/Body_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Body/Body_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Body/Body_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Hair/Hair_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Hair/Hair_9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Hair/Hair_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Hair/Hair_13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/Face/Face_4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2237,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>47</v>
@@ -2249,7 +2268,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
@@ -2261,10 +2280,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E26" s="12"/>
     </row>
@@ -2273,10 +2292,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2284,10 +2303,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2295,10 +2314,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2306,10 +2325,10 @@
         <v>7</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C30" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2317,10 +2336,10 @@
         <v>8</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C31" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2328,10 +2347,10 @@
         <v>9</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C32" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2342,7 +2361,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2353,7 +2372,7 @@
         <v>25</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2364,7 +2383,7 @@
         <v>25</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2375,7 +2394,7 @@
         <v>25</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2386,7 +2405,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2397,7 +2416,7 @@
         <v>25</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2408,7 +2427,7 @@
         <v>25</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2419,7 +2438,7 @@
         <v>25</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2430,7 +2449,7 @@
         <v>25</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -3137,7 +3156,7 @@
         <v>113</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E8" s="9">
         <v>1</v>
@@ -3364,7 +3383,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="19" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3432,6 +3451,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -3486,10 +3508,10 @@
         <v>196</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -3508,13 +3530,13 @@
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="11" t="s">
-        <v>197</v>
+        <v>352</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>180</v>
+        <v>356</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>179</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -3533,13 +3555,13 @@
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="22" t="s">
-        <v>198</v>
+        <v>353</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>181</v>
+        <v>357</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>179</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -3558,13 +3580,13 @@
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11" t="s">
-        <v>199</v>
+        <v>354</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>184</v>
+        <v>358</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>179</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -3583,13 +3605,13 @@
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="22" t="s">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>186</v>
+        <v>359</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>179</v>
+        <v>360</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -4479,7 +4501,7 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>176</v>
@@ -4573,7 +4595,7 @@
         <v>20</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="O3" s="9">
         <v>100</v>
@@ -4628,7 +4650,7 @@
         <v>21</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="O4" s="9">
         <v>100</v>
@@ -4683,7 +4705,7 @@
         <v>21</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="O5" s="9">
         <v>100</v>
@@ -4738,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="O6" s="9">
         <v>100</v>
@@ -5032,7 +5054,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>25</v>
@@ -5083,7 +5105,7 @@
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>27</v>
@@ -5094,7 +5116,7 @@
         <v>22</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>30</v>
@@ -5131,7 +5153,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -5140,7 +5162,7 @@
       <c r="G3" s="25"/>
       <c r="H3" s="23"/>
       <c r="I3" s="23" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
@@ -5168,10 +5190,10 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -5179,19 +5201,19 @@
       <c r="F4" s="9"/>
       <c r="G4" s="2"/>
       <c r="H4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M4" t="s">
         <v>11</v>
@@ -5209,10 +5231,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D5" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -5220,19 +5242,19 @@
       <c r="F5" s="9"/>
       <c r="G5" s="2"/>
       <c r="H5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M5" t="s">
         <v>11</v>
@@ -5250,10 +5272,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5261,19 +5283,19 @@
       <c r="F6" s="9"/>
       <c r="G6" s="2"/>
       <c r="H6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M6" t="s">
         <v>11</v>
@@ -5291,29 +5313,29 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7" s="9"/>
       <c r="H7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M7" t="s">
         <v>11</v>
@@ -5331,29 +5353,29 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E8">
         <v>5</v>
       </c>
       <c r="F8" s="9"/>
       <c r="H8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M8" t="s">
         <v>11</v>
@@ -5371,29 +5393,29 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D9" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
       <c r="F9" s="9"/>
       <c r="H9" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I9" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M9" t="s">
         <v>11</v>
@@ -5411,29 +5433,29 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E10">
         <v>7</v>
       </c>
       <c r="F10" s="9"/>
       <c r="H10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M10" t="s">
         <v>11</v>
@@ -5451,29 +5473,29 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D11" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="F11" s="9"/>
       <c r="H11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M11" t="s">
         <v>11</v>
@@ -5503,10 +5525,10 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5514,16 +5536,16 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I13" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" t="s">
@@ -5542,10 +5564,10 @@
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D14" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -5553,16 +5575,16 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I14" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L14" s="11"/>
       <c r="M14" t="s">
@@ -5581,10 +5603,10 @@
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D15" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -5592,16 +5614,16 @@
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I15" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L15" s="11"/>
       <c r="M15" t="s">
@@ -5620,10 +5642,10 @@
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D16" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -5631,16 +5653,16 @@
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L16" s="11"/>
       <c r="M16" t="s">
@@ -5659,10 +5681,10 @@
         <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D17" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -5670,16 +5692,16 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I17" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L17" s="11"/>
       <c r="M17" t="s">
@@ -5698,10 +5720,10 @@
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D18" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -5709,16 +5731,16 @@
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I18" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L18" s="11"/>
       <c r="M18" t="s">
@@ -5737,10 +5759,10 @@
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E19">
         <v>7</v>
@@ -5748,16 +5770,16 @@
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I19" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L19" s="11"/>
       <c r="M19" t="s">
@@ -5776,10 +5798,10 @@
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -5787,16 +5809,16 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I20" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L20" s="11"/>
       <c r="M20" t="s">
@@ -5815,10 +5837,10 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D21" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E21">
         <v>9</v>
@@ -5826,16 +5848,16 @@
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I21" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L21" s="11"/>
       <c r="M21" t="s">
@@ -5854,10 +5876,10 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D22" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -5865,16 +5887,16 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I22" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L22" s="11"/>
       <c r="M22" t="s">
@@ -5905,10 +5927,10 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D24" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -5916,16 +5938,16 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L24" s="11"/>
       <c r="M24" t="s">
@@ -5944,10 +5966,10 @@
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D25" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -5955,16 +5977,16 @@
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L25" s="11"/>
       <c r="M25" t="s">
@@ -5983,10 +6005,10 @@
         <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D26" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -5994,16 +6016,16 @@
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L26" s="11"/>
       <c r="M26" t="s">
@@ -6022,10 +6044,10 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D27" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -6033,16 +6055,16 @@
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L27" s="11"/>
       <c r="M27" t="s">
@@ -6061,10 +6083,10 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D28" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -6072,16 +6094,16 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L28" s="11"/>
       <c r="M28" t="s">
@@ -6100,10 +6122,10 @@
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D29" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -6111,16 +6133,16 @@
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L29" s="11"/>
       <c r="M29" t="s">
@@ -6139,10 +6161,10 @@
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D30" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E30">
         <v>7</v>
@@ -6150,16 +6172,16 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L30" s="11"/>
       <c r="M30" t="s">
@@ -6178,10 +6200,10 @@
         <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D31" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E31">
         <v>8</v>
@@ -6189,16 +6211,16 @@
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L31" s="11"/>
       <c r="M31" t="s">
@@ -6217,10 +6239,10 @@
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D32" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E32">
         <v>9</v>
@@ -6228,16 +6250,16 @@
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L32" s="11"/>
       <c r="M32" t="s">
@@ -6256,10 +6278,10 @@
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D33" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E33">
         <v>10</v>
@@ -6267,16 +6289,16 @@
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L33" s="11"/>
       <c r="M33" t="s">
@@ -6295,10 +6317,10 @@
         <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D34" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E34">
         <v>11</v>
@@ -6306,16 +6328,16 @@
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L34" s="11"/>
       <c r="M34" t="s">
@@ -6334,10 +6356,10 @@
         <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D35" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -6345,16 +6367,16 @@
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L35" s="11"/>
       <c r="M35" t="s">
@@ -6373,10 +6395,10 @@
         <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D36" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E36">
         <v>13</v>
@@ -6384,16 +6406,16 @@
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L36" s="11"/>
       <c r="M36" t="s">
@@ -6412,10 +6434,10 @@
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D37" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E37">
         <v>14</v>
@@ -6423,16 +6445,16 @@
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L37" s="11"/>
       <c r="M37" t="s">
@@ -6451,10 +6473,10 @@
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D38" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E38">
         <v>15</v>
@@ -6462,16 +6484,16 @@
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L38" s="11"/>
       <c r="M38" t="s">
@@ -6490,10 +6512,10 @@
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D39" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E39">
         <v>16</v>
@@ -6501,16 +6523,16 @@
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L39" s="11"/>
       <c r="M39" t="s">
@@ -6529,10 +6551,10 @@
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D40" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E40">
         <v>17</v>
@@ -6540,16 +6562,16 @@
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L40" s="11"/>
       <c r="M40" t="s">
@@ -6568,10 +6590,10 @@
         <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D41" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E41">
         <v>18</v>
@@ -6579,16 +6601,16 @@
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L41" s="11"/>
       <c r="M41" t="s">
@@ -6619,10 +6641,10 @@
         <v>26</v>
       </c>
       <c r="C43" t="s">
+        <v>204</v>
+      </c>
+      <c r="D43" t="s">
         <v>208</v>
-      </c>
-      <c r="D43" t="s">
-        <v>212</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -6630,16 +6652,16 @@
       <c r="F43" s="9"/>
       <c r="G43" s="9"/>
       <c r="H43" s="22" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L43" s="11"/>
       <c r="M43" t="s">
@@ -6658,10 +6680,10 @@
         <v>26</v>
       </c>
       <c r="C44" t="s">
+        <v>204</v>
+      </c>
+      <c r="D44" t="s">
         <v>208</v>
-      </c>
-      <c r="D44" t="s">
-        <v>212</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -6669,16 +6691,16 @@
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="22" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L44" s="11"/>
       <c r="M44" t="s">
@@ -6697,10 +6719,10 @@
         <v>26</v>
       </c>
       <c r="C45" t="s">
+        <v>204</v>
+      </c>
+      <c r="D45" t="s">
         <v>208</v>
-      </c>
-      <c r="D45" t="s">
-        <v>212</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -6708,16 +6730,16 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="22" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L45" s="11"/>
       <c r="M45" t="s">
@@ -6736,10 +6758,10 @@
         <v>26</v>
       </c>
       <c r="C46" t="s">
+        <v>204</v>
+      </c>
+      <c r="D46" t="s">
         <v>208</v>
-      </c>
-      <c r="D46" t="s">
-        <v>212</v>
       </c>
       <c r="E46">
         <v>4</v>
@@ -6747,16 +6769,16 @@
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
       <c r="H46" s="22" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L46" s="11"/>
       <c r="M46" t="s">
@@ -6775,10 +6797,10 @@
         <v>26</v>
       </c>
       <c r="C47" t="s">
+        <v>204</v>
+      </c>
+      <c r="D47" t="s">
         <v>208</v>
-      </c>
-      <c r="D47" t="s">
-        <v>212</v>
       </c>
       <c r="E47">
         <v>5</v>
@@ -6786,16 +6808,16 @@
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
       <c r="H47" s="22" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L47" s="11"/>
       <c r="M47" t="s">
@@ -6826,10 +6848,10 @@
         <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D49" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -6837,16 +6859,16 @@
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L49" s="11"/>
       <c r="M49" t="s">
@@ -6865,10 +6887,10 @@
         <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D50" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E50">
         <v>2</v>
@@ -6876,16 +6898,16 @@
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L50" s="11"/>
       <c r="M50" t="s">
@@ -6904,10 +6926,10 @@
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D51" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -6915,16 +6937,16 @@
       <c r="F51" s="9"/>
       <c r="G51" s="9"/>
       <c r="H51" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L51" s="11"/>
       <c r="M51" t="s">
@@ -6943,10 +6965,10 @@
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D52" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E52">
         <v>4</v>
@@ -6954,16 +6976,16 @@
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
       <c r="H52" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L52" s="11"/>
       <c r="M52" t="s">
@@ -6982,10 +7004,10 @@
         <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D53" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E53">
         <v>5</v>
@@ -6993,16 +7015,16 @@
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L53" s="11"/>
       <c r="M53" t="s">
@@ -7021,10 +7043,10 @@
         <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D54" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E54">
         <v>6</v>
@@ -7032,16 +7054,16 @@
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
       <c r="H54" s="9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L54" s="11"/>
       <c r="M54" t="s">
@@ -7060,10 +7082,10 @@
         <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D55" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E55">
         <v>7</v>
@@ -7071,16 +7093,16 @@
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L55" s="11"/>
       <c r="M55" t="s">
@@ -7099,10 +7121,10 @@
         <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D56" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E56">
         <v>8</v>
@@ -7110,16 +7132,16 @@
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L56" s="11"/>
       <c r="M56" t="s">
@@ -7138,10 +7160,10 @@
         <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D57" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E57">
         <v>9</v>
@@ -7149,16 +7171,16 @@
       <c r="F57" s="9"/>
       <c r="G57" s="9"/>
       <c r="H57" s="9" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L57" s="11"/>
       <c r="M57" t="s">
@@ -7177,10 +7199,10 @@
         <v>26</v>
       </c>
       <c r="C58" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D58" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E58">
         <v>10</v>
@@ -7188,16 +7210,16 @@
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
       <c r="H58" s="9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L58" s="11"/>
       <c r="M58" t="s">
@@ -7216,10 +7238,10 @@
         <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D59" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E59">
         <v>11</v>
@@ -7227,16 +7249,16 @@
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
       <c r="H59" s="9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L59" s="11"/>
       <c r="M59" t="s">
@@ -7255,10 +7277,10 @@
         <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D60" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E60">
         <v>12</v>
@@ -7266,16 +7288,16 @@
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L60" s="11"/>
       <c r="M60" t="s">
@@ -7294,10 +7316,10 @@
         <v>26</v>
       </c>
       <c r="C61" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D61" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E61">
         <v>13</v>
@@ -7305,16 +7327,16 @@
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L61" s="11"/>
       <c r="M61" t="s">
@@ -7333,10 +7355,10 @@
         <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D62" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E62">
         <v>14</v>
@@ -7344,16 +7366,16 @@
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
       <c r="H62" s="9" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" t="s">
@@ -7372,10 +7394,10 @@
         <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D63" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E63">
         <v>15</v>
@@ -7383,16 +7405,16 @@
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L63" s="11"/>
       <c r="M63" t="s">
@@ -7411,10 +7433,10 @@
         <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D64" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E64">
         <v>16</v>
@@ -7422,16 +7444,16 @@
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
       <c r="H64" s="9" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L64" s="11"/>
       <c r="M64" t="s">
@@ -7450,10 +7472,10 @@
         <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D65" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E65">
         <v>17</v>
@@ -7461,16 +7483,16 @@
       <c r="F65" s="9"/>
       <c r="G65" s="9"/>
       <c r="H65" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L65" s="11"/>
       <c r="M65" t="s">
@@ -7489,10 +7511,10 @@
         <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D66" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E66">
         <v>18</v>
@@ -7500,16 +7522,16 @@
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="9" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L66" s="11"/>
       <c r="M66" t="s">
@@ -7528,10 +7550,10 @@
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D67" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E67">
         <v>19</v>
@@ -7539,16 +7561,16 @@
       <c r="F67" s="9"/>
       <c r="G67" s="9"/>
       <c r="H67" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L67" s="11"/>
       <c r="M67" t="s">
@@ -7567,10 +7589,10 @@
         <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D68" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E68">
         <v>20</v>
@@ -7578,16 +7600,16 @@
       <c r="F68" s="9"/>
       <c r="G68" s="9"/>
       <c r="H68" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L68" s="11"/>
       <c r="M68" t="s">
@@ -7606,10 +7628,10 @@
         <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D69" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E69">
         <v>21</v>
@@ -7617,16 +7639,16 @@
       <c r="F69" s="9"/>
       <c r="G69" s="9"/>
       <c r="H69" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L69" s="11"/>
       <c r="M69" t="s">
@@ -7645,10 +7667,10 @@
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D70" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E70">
         <v>22</v>
@@ -7656,16 +7678,16 @@
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="9" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L70" s="11"/>
       <c r="M70" t="s">
@@ -7684,10 +7706,10 @@
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D71" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E71">
         <v>23</v>
@@ -7695,16 +7717,16 @@
       <c r="F71" s="9"/>
       <c r="G71" s="9"/>
       <c r="H71" s="9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K71" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L71" s="11"/>
       <c r="M71" t="s">
@@ -7723,10 +7745,10 @@
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D72" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E72">
         <v>24</v>
@@ -7734,16 +7756,16 @@
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
       <c r="H72" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K72" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L72" s="11"/>
       <c r="M72" t="s">
@@ -7762,10 +7784,10 @@
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D73" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E73">
         <v>25</v>
@@ -7773,16 +7795,16 @@
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
       <c r="H73" s="9" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L73" s="11"/>
       <c r="M73" t="s">
@@ -7801,10 +7823,10 @@
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D74" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E74">
         <v>26</v>
@@ -7812,16 +7834,16 @@
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L74" s="11"/>
       <c r="M74" t="s">
@@ -7840,10 +7862,10 @@
         <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D75" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E75">
         <v>27</v>
@@ -7851,16 +7873,16 @@
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
       <c r="H75" s="9" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K75" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L75" s="11"/>
       <c r="M75" t="s">
@@ -7879,10 +7901,10 @@
         <v>26</v>
       </c>
       <c r="C76" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D76" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E76">
         <v>28</v>
@@ -7890,16 +7912,16 @@
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="9" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L76" s="11"/>
       <c r="M76" t="s">
@@ -7918,10 +7940,10 @@
         <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D77" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E77">
         <v>29</v>
@@ -7929,16 +7951,16 @@
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L77" s="11"/>
       <c r="M77" t="s">
@@ -7957,26 +7979,26 @@
         <v>26</v>
       </c>
       <c r="C78" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D78" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E78">
         <v>30</v>
       </c>
       <c r="F78" s="9"/>
       <c r="H78" s="9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L78" s="11"/>
       <c r="M78" t="s">
@@ -7995,10 +8017,10 @@
         <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D79" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E79">
         <v>31</v>
@@ -8006,16 +8028,16 @@
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L79" s="11"/>
       <c r="M79" t="s">
@@ -8043,25 +8065,25 @@
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D81" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="I81" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L81" s="11"/>
       <c r="M81" t="s">
@@ -8080,25 +8102,25 @@
         <v>26</v>
       </c>
       <c r="C82" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D82" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E82">
         <v>2</v>
       </c>
       <c r="H82" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I82" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L82" s="11"/>
       <c r="M82" t="s">
@@ -8117,25 +8139,25 @@
         <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D83" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
       <c r="H83" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I83" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L83" s="11"/>
       <c r="M83" t="s">
@@ -8154,25 +8176,25 @@
         <v>26</v>
       </c>
       <c r="C84" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D84" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E84">
         <v>4</v>
       </c>
       <c r="H84" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I84" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L84" s="11"/>
       <c r="M84" t="s">
@@ -8191,25 +8213,25 @@
         <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D85" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E85">
         <v>5</v>
       </c>
       <c r="H85" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I85" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L85" s="11"/>
       <c r="M85" t="s">
@@ -8228,25 +8250,25 @@
         <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D86" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E86">
         <v>6</v>
       </c>
       <c r="H86" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I86" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L86" s="11"/>
       <c r="M86" t="s">
@@ -8265,25 +8287,25 @@
         <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D87" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E87">
         <v>7</v>
       </c>
       <c r="H87" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="I87" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K87" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L87" s="11"/>
       <c r="M87" t="s">
@@ -8302,25 +8324,25 @@
         <v>26</v>
       </c>
       <c r="C88" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D88" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E88">
         <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I88" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L88" s="11"/>
       <c r="M88" t="s">
@@ -8339,25 +8361,25 @@
         <v>26</v>
       </c>
       <c r="C89" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D89" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E89">
         <v>9</v>
       </c>
       <c r="H89" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="I89" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K89" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L89" s="11"/>
       <c r="M89" t="s">
@@ -8376,25 +8398,25 @@
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D90" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E90">
         <v>10</v>
       </c>
       <c r="H90" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I90" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K90" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L90" s="11"/>
       <c r="M90" t="s">
@@ -8413,25 +8435,25 @@
         <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D91" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E91">
         <v>11</v>
       </c>
       <c r="H91" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I91" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K91" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L91" s="11"/>
       <c r="M91" t="s">
@@ -8450,25 +8472,25 @@
         <v>26</v>
       </c>
       <c r="C92" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D92" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E92">
         <v>12</v>
       </c>
       <c r="H92" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I92" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K92" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L92" s="11"/>
       <c r="M92" t="s">
@@ -8487,25 +8509,25 @@
         <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D93" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E93">
         <v>13</v>
       </c>
       <c r="H93" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I93" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K93" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L93" s="11"/>
       <c r="M93" t="s">
@@ -8524,25 +8546,25 @@
         <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D94" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E94">
         <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I94" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J94" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K94" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L94" s="11"/>
       <c r="M94" t="s">
@@ -8561,25 +8583,25 @@
         <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D95" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E95">
         <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I95" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K95" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L95" s="11"/>
       <c r="M95" t="s">
@@ -8598,25 +8620,25 @@
         <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D96" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E96">
         <v>16</v>
       </c>
       <c r="H96" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="I96" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K96" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L96" s="11"/>
       <c r="M96" t="s">
@@ -8635,25 +8657,25 @@
         <v>26</v>
       </c>
       <c r="C97" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D97" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E97">
         <v>17</v>
       </c>
       <c r="H97" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I97" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="J97" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K97" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L97" s="11"/>
       <c r="M97" t="s">
@@ -8672,25 +8694,25 @@
         <v>26</v>
       </c>
       <c r="C98" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D98" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E98">
         <v>18</v>
       </c>
       <c r="H98" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I98" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J98" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K98" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L98" s="11"/>
       <c r="M98" t="s">
@@ -8709,25 +8731,25 @@
         <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D99" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E99">
         <v>19</v>
       </c>
       <c r="H99" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="I99" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J99" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K99" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L99" s="11"/>
       <c r="M99" t="s">
@@ -8746,25 +8768,25 @@
         <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D100" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E100">
         <v>20</v>
       </c>
       <c r="H100" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I100" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J100" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K100" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L100" s="11"/>
       <c r="M100" t="s">
@@ -8783,25 +8805,25 @@
         <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D101" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E101">
         <v>21</v>
       </c>
       <c r="H101" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I101" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J101" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K101" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L101" s="11"/>
       <c r="M101" t="s">
@@ -8825,25 +8847,25 @@
         <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D103" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E103">
         <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="I103" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="J103" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K103" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L103" s="11"/>
       <c r="M103" t="s">
@@ -8862,25 +8884,25 @@
         <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D104" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E104">
         <v>2</v>
       </c>
       <c r="H104" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I104" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L104" s="11"/>
       <c r="M104" t="s">
@@ -8899,25 +8921,25 @@
         <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D105" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E105">
         <v>3</v>
       </c>
       <c r="H105" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I105" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K105" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L105" s="11"/>
       <c r="M105" t="s">
@@ -8936,25 +8958,25 @@
         <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D106" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E106">
         <v>4</v>
       </c>
       <c r="H106" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I106" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J106" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K106" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L106" s="11"/>
       <c r="M106" t="s">
@@ -8973,25 +8995,25 @@
         <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D107" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E107">
         <v>5</v>
       </c>
       <c r="H107" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I107" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J107" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K107" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L107" s="11"/>
       <c r="M107" t="s">
@@ -9010,25 +9032,25 @@
         <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D108" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E108">
         <v>6</v>
       </c>
       <c r="H108" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I108" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J108" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K108" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L108" s="11"/>
       <c r="M108" t="s">
@@ -9052,25 +9074,25 @@
         <v>26</v>
       </c>
       <c r="C110" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D110" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E110">
         <v>1</v>
       </c>
       <c r="H110" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I110" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J110" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K110" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L110" s="11"/>
       <c r="M110" t="s">
@@ -9089,25 +9111,25 @@
         <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D111" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E111">
         <v>2</v>
       </c>
       <c r="H111" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I111" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J111" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K111" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L111" s="11"/>
       <c r="M111" t="s">
@@ -9126,25 +9148,25 @@
         <v>26</v>
       </c>
       <c r="C112" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D112" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E112">
         <v>3</v>
       </c>
       <c r="H112" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I112" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K112" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L112" s="11"/>
       <c r="M112" t="s">
@@ -9163,25 +9185,25 @@
         <v>26</v>
       </c>
       <c r="C113" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D113" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E113">
         <v>4</v>
       </c>
       <c r="H113" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I113" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J113" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K113" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L113" s="11"/>
       <c r="M113" t="s">
@@ -9200,25 +9222,25 @@
         <v>26</v>
       </c>
       <c r="C114" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D114" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E114">
         <v>5</v>
       </c>
       <c r="H114" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I114" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J114" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K114" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L114" s="11"/>
       <c r="M114" t="s">
@@ -9237,25 +9259,25 @@
         <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D115" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E115">
         <v>6</v>
       </c>
       <c r="H115" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I115" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J115" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K115" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L115" s="11"/>
       <c r="M115" t="s">
@@ -9274,25 +9296,25 @@
         <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D116" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E116">
         <v>7</v>
       </c>
       <c r="H116" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I116" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J116" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K116" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L116" s="11"/>
       <c r="M116" t="s">
@@ -9316,25 +9338,25 @@
         <v>26</v>
       </c>
       <c r="C118" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D118" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E118">
         <v>1</v>
       </c>
       <c r="H118" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I118" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K118" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L118" s="11"/>
       <c r="M118" t="s">
@@ -9353,25 +9375,25 @@
         <v>26</v>
       </c>
       <c r="C119" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D119" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E119">
         <v>2</v>
       </c>
       <c r="H119" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I119" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J119" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K119" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L119" s="11"/>
       <c r="M119" t="s">
@@ -9390,25 +9412,25 @@
         <v>26</v>
       </c>
       <c r="C120" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D120" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E120">
         <v>3</v>
       </c>
       <c r="H120" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I120" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J120" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K120" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L120" s="11"/>
       <c r="M120" t="s">
@@ -9427,25 +9449,25 @@
         <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D121" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E121">
         <v>4</v>
       </c>
       <c r="H121" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I121" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J121" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K121" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L121" s="11"/>
       <c r="M121" t="s">
@@ -9464,25 +9486,25 @@
         <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D122" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E122">
         <v>5</v>
       </c>
       <c r="H122" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I122" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K122" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L122" s="11"/>
       <c r="M122" t="s">
@@ -9501,25 +9523,25 @@
         <v>26</v>
       </c>
       <c r="C123" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D123" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E123">
         <v>6</v>
       </c>
       <c r="H123" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I123" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="J123" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K123" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L123" s="11"/>
       <c r="M123" t="s">
@@ -9538,25 +9560,25 @@
         <v>26</v>
       </c>
       <c r="C124" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D124" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E124">
         <v>7</v>
       </c>
       <c r="H124" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I124" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J124" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K124" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L124" s="11"/>
       <c r="M124" t="s">
@@ -9575,25 +9597,25 @@
         <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D125" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I125" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="J125" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K125" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L125" s="11"/>
       <c r="M125" t="s">
@@ -9612,25 +9634,25 @@
         <v>26</v>
       </c>
       <c r="C126" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D126" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E126">
         <v>9</v>
       </c>
       <c r="H126" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I126" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J126" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K126" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L126" s="11"/>
       <c r="M126" t="s">
@@ -9649,25 +9671,25 @@
         <v>26</v>
       </c>
       <c r="C127" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D127" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E127">
         <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="I127" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="J127" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K127" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L127" s="11"/>
       <c r="M127" t="s">
@@ -9686,25 +9708,25 @@
         <v>26</v>
       </c>
       <c r="C128" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D128" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E128">
         <v>11</v>
       </c>
       <c r="H128" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I128" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="J128" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K128" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L128" s="11"/>
       <c r="M128" t="s">
@@ -9723,25 +9745,25 @@
         <v>26</v>
       </c>
       <c r="C129" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D129" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E129">
         <v>12</v>
       </c>
       <c r="H129" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I129" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="J129" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K129" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L129" s="11"/>
       <c r="M129" t="s">
@@ -9760,25 +9782,25 @@
         <v>26</v>
       </c>
       <c r="C130" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D130" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E130">
         <v>13</v>
       </c>
       <c r="H130" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="I130" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K130" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L130" s="11"/>
       <c r="M130" t="s">
@@ -9797,25 +9819,25 @@
         <v>26</v>
       </c>
       <c r="C131" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D131" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E131">
         <v>14</v>
       </c>
       <c r="H131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="J131" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K131" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L131" s="11"/>
       <c r="M131" t="s">
@@ -9834,25 +9856,25 @@
         <v>26</v>
       </c>
       <c r="C132" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D132" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E132">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="I132" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K132" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L132" s="11"/>
       <c r="M132" t="s">
@@ -9871,25 +9893,25 @@
         <v>26</v>
       </c>
       <c r="C133" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D133" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E133">
         <v>16</v>
       </c>
       <c r="H133" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I133" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J133" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K133" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L133" s="11"/>
       <c r="M133" t="s">
@@ -9908,25 +9930,25 @@
         <v>26</v>
       </c>
       <c r="C134" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D134" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E134">
         <v>17</v>
       </c>
       <c r="H134" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I134" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="J134" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K134" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L134" s="11"/>
       <c r="M134" t="s">
@@ -9945,25 +9967,25 @@
         <v>26</v>
       </c>
       <c r="C135" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D135" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E135">
         <v>18</v>
       </c>
       <c r="H135" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I135" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="J135" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K135" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L135" s="11"/>
       <c r="M135" t="s">
@@ -9982,25 +10004,25 @@
         <v>26</v>
       </c>
       <c r="C136" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D136" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E136">
         <v>19</v>
       </c>
       <c r="H136" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="I136" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J136" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K136" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L136" s="11"/>
       <c r="M136" t="s">
@@ -10019,25 +10041,25 @@
         <v>26</v>
       </c>
       <c r="C137" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D137" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E137">
         <v>20</v>
       </c>
       <c r="H137" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I137" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="J137" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K137" s="11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L137" s="11"/>
       <c r="M137" t="s">

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/infy_mac/Unity/FactoryProject/Generated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D54EDB-A066-9B4F-A1C9-493C8265BD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC086C2-9E78-A142-B961-67665D962EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="11" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
+    <workbookView xWindow="51200" yWindow="620" windowWidth="51200" windowHeight="26600" xr2:uid="{940BCB5D-19EC-984D-9BAE-40F19189B649}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="357">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -484,22 +484,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>icon_item_human</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_dog</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_eagle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_snake</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Projectile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -856,14 +840,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RHand</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LHand</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Top</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1236,14 +1212,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Pixem/Parts/FaceAcc_1/FaceAcc2_10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pixem/Parts/FaceAcc_1/FaceAcc2_12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Pixem/Parts/HairAcc/HairAcc_0</t>
   </si>
   <si>
@@ -1378,6 +1346,22 @@
   </si>
   <si>
     <t>Pixem/Parts/Face/Face_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/FaceAcc_2/FaceAcc2_10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pixem/Parts/FaceAcc_2/FaceAcc2_12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainWeapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SubWeapon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1587,7 +1571,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1652,15 +1636,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2256,7 +2231,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>47</v>
@@ -2268,7 +2243,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
@@ -2280,10 +2255,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="E26" s="12"/>
     </row>
@@ -2292,10 +2267,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>204</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2303,10 +2278,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2314,10 +2289,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2325,10 +2300,10 @@
         <v>7</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2336,10 +2311,10 @@
         <v>8</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C31" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2347,10 +2322,10 @@
         <v>9</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C32" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2361,7 +2336,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2372,7 +2347,7 @@
         <v>25</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2383,7 +2358,7 @@
         <v>25</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2394,7 +2369,7 @@
         <v>25</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2405,7 +2380,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2416,7 +2391,7 @@
         <v>25</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2427,7 +2402,7 @@
         <v>25</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2438,7 +2413,7 @@
         <v>25</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2449,7 +2424,7 @@
         <v>25</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2545,10 +2520,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2556,10 +2531,10 @@
         <v>2</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2567,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>24</v>
@@ -2578,10 +2553,10 @@
         <v>2</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2589,10 +2564,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2600,10 +2575,10 @@
         <v>2</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="2"/>
@@ -2615,10 +2590,10 @@
         <v>3</v>
       </c>
       <c r="B56" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="F56" s="9"/>
       <c r="J56" s="11"/>
@@ -2629,10 +2604,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2640,10 +2615,10 @@
         <v>5</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2651,10 +2626,10 @@
         <v>6</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2662,10 +2637,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2673,10 +2648,10 @@
         <v>2</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2684,10 +2659,10 @@
         <v>3</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -2695,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>5</v>
@@ -2706,10 +2681,10 @@
         <v>2</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2717,10 +2692,10 @@
         <v>3</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -2728,10 +2703,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -2863,7 +2838,7 @@
         <v>52</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2884,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2952,7 +2927,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>71</v>
@@ -2964,19 +2939,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>9</v>
@@ -3006,10 +2981,10 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="19" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>29</v>
@@ -3018,22 +2993,22 @@
         <v>30</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M2" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="N2" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>121</v>
-      </c>
       <c r="P2" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -3061,18 +3036,18 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="Q3" s="9"/>
       <c r="S3" s="9"/>
@@ -3093,7 +3068,7 @@
     </row>
     <row r="6" spans="1:32">
       <c r="A6" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="S6" s="13"/>
       <c r="T6" s="1"/>
@@ -3107,7 +3082,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>46</v>
@@ -3129,17 +3104,17 @@
         <v>57</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s">
         <v>24</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="S7" s="13"/>
       <c r="T7" s="1"/>
@@ -3153,10 +3128,10 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E8" s="9">
         <v>1</v>
@@ -3175,17 +3150,17 @@
         <v>57</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s">
         <v>24</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="S8" s="13"/>
       <c r="T8" s="1"/>
@@ -3206,7 +3181,7 @@
     </row>
     <row r="11" spans="1:32">
       <c r="A11" s="7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:32">
@@ -3218,10 +3193,10 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E12" s="9">
         <v>1</v>
@@ -3240,20 +3215,20 @@
         <v>58</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N12">
         <v>0.6</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:32">
@@ -3268,7 +3243,7 @@
         <v>46</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E13" s="9">
         <v>1</v>
@@ -3287,19 +3262,19 @@
         <v>57</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N13">
         <v>0.1</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -3314,7 +3289,7 @@
     </row>
     <row r="16" spans="1:32">
       <c r="A16" s="7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3326,7 +3301,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9">
@@ -3346,20 +3321,20 @@
         <v>58</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N17">
         <v>0.1</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3372,7 +3347,6 @@
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="24"/>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
     </row>
@@ -3383,7 +3357,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="19" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3398,7 +3372,7 @@
         <v>46</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E21" s="9">
         <v>1</v>
@@ -3417,20 +3391,20 @@
         <v>58</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N21">
         <v>0.1</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="P21" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -3459,16 +3433,16 @@
     <row r="1" spans="1:14">
       <c r="A1" s="8"/>
       <c r="B1" s="20" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>0</v>
@@ -3479,22 +3453,22 @@
       <c r="H1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="18" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3505,13 +3479,13 @@
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
       <c r="F2" s="21" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -3520,7 +3494,7 @@
         <v>Skin_Human_1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>46</v>
@@ -3530,13 +3504,13 @@
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>352</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -3545,7 +3519,7 @@
         <v>Skin_Dog_1</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>68</v>
@@ -3555,13 +3529,13 @@
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="22" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -3570,7 +3544,7 @@
         <v>Skin_Eagle_1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>69</v>
@@ -3580,13 +3554,13 @@
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -3595,7 +3569,7 @@
         <v>Skin_Snake_1</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>70</v>
@@ -3605,25 +3579,25 @@
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="22" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3635,13 +3609,13 @@
       <c r="F7" s="11"/>
       <c r="G7" s="22"/>
       <c r="L7" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="M7" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N7" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3653,57 +3627,57 @@
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
       <c r="L8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="L9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="L10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M10" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="L11" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M11" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="L12" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3766,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>9</v>
@@ -3779,13 +3753,13 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>29</v>
@@ -3794,10 +3768,10 @@
         <v>30</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -3829,10 +3803,10 @@
         <v>105</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3861,7 +3835,7 @@
     <row r="8" spans="1:12">
       <c r="F8" s="9"/>
       <c r="G8" s="9" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -3924,7 +3898,7 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>29</v>
@@ -3952,7 +3926,7 @@
         <v>Projectile_Human</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>46</v>
@@ -3964,13 +3938,13 @@
         <v>104</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>105</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -4066,7 +4040,7 @@
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>0</v>
@@ -4079,10 +4053,10 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4094,7 +4068,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -4105,17 +4079,17 @@
         <v>AI_Flow_DefaultDetectionRange</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G5" s="9">
         <v>6</v>
@@ -4127,16 +4101,16 @@
         <v>AI_Flow_DefaultAttackRange</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G6" s="9">
         <v>1.5</v>
@@ -4148,16 +4122,16 @@
         <v>AI_Flow_TargetLostRangeOffset</v>
       </c>
       <c r="B7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" t="s">
         <v>169</v>
       </c>
-      <c r="C7" t="s">
-        <v>171</v>
-      </c>
-      <c r="D7" t="s">
-        <v>173</v>
-      </c>
       <c r="F7" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G7" s="9">
         <v>2</v>
@@ -4169,16 +4143,16 @@
         <v>AI_Flow_FoolowDistanceRatio</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G8" s="9">
         <v>0.9</v>
@@ -4484,10 +4458,10 @@
         <v>88</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
@@ -4501,10 +4475,10 @@
       <c r="B2" s="8"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>29</v>
@@ -4540,10 +4514,10 @@
         <v>98</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="S2" s="6"/>
       <c r="T2" s="14"/>
@@ -4595,7 +4569,7 @@
         <v>20</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="O3" s="9">
         <v>100</v>
@@ -4650,7 +4624,7 @@
         <v>21</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="O4" s="9">
         <v>100</v>
@@ -4705,7 +4679,7 @@
         <v>21</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="O5" s="9">
         <v>100</v>
@@ -4760,7 +4734,7 @@
         <v>21</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="O6" s="9">
         <v>100</v>
@@ -5054,7 +5028,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>25</v>
@@ -5105,7 +5079,7 @@
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="6" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>27</v>
@@ -5116,7 +5090,7 @@
         <v>22</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>30</v>
@@ -5152,48 +5126,48 @@
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
+      <c r="B3" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B4:F4)</f>
-        <v>Item_RHand_Bow_1</v>
+        <f t="shared" ref="A4:A11" si="0">_xlfn.TEXTJOIN("_",TRUE,B4:F4)</f>
+        <v>Item_MainWeapon_Bow_1</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -5201,19 +5175,19 @@
       <c r="F4" s="9"/>
       <c r="G4" s="2"/>
       <c r="H4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M4" t="s">
         <v>11</v>
@@ -5224,17 +5198,17 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B5:F5)</f>
-        <v>Item_RHand_Bow_2</v>
+        <f t="shared" si="0"/>
+        <v>Item_MainWeapon_Bow_2</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="D5" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -5242,19 +5216,19 @@
       <c r="F5" s="9"/>
       <c r="G5" s="2"/>
       <c r="H5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M5" t="s">
         <v>11</v>
@@ -5265,17 +5239,17 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B6:F6)</f>
-        <v>Item_RHand_Bow_3</v>
+        <f t="shared" si="0"/>
+        <v>Item_MainWeapon_Bow_3</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="D6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5283,19 +5257,19 @@
       <c r="F6" s="9"/>
       <c r="G6" s="2"/>
       <c r="H6" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I6" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M6" t="s">
         <v>11</v>
@@ -5306,36 +5280,36 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B7:F7)</f>
-        <v>Item_RHand_Bow_4</v>
+        <f t="shared" si="0"/>
+        <v>Item_MainWeapon_Bow_4</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7" s="9"/>
       <c r="H7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="I7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M7" t="s">
         <v>11</v>
@@ -5346,36 +5320,36 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B8:F8)</f>
-        <v>Item_RHand_Bow_5</v>
+        <f t="shared" si="0"/>
+        <v>Item_MainWeapon_Bow_5</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="D8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E8">
         <v>5</v>
       </c>
       <c r="F8" s="9"/>
       <c r="H8" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I8" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M8" t="s">
         <v>11</v>
@@ -5386,36 +5360,36 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B9:F9)</f>
-        <v>Item_RHand_Bow_6</v>
+        <f t="shared" si="0"/>
+        <v>Item_MainWeapon_Bow_6</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
       <c r="F9" s="9"/>
       <c r="H9" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="I9" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M9" t="s">
         <v>11</v>
@@ -5426,36 +5400,36 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B10:F10)</f>
-        <v>Item_RHand_Bow_7</v>
+        <f t="shared" si="0"/>
+        <v>Item_MainWeapon_Bow_7</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="D10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E10">
         <v>7</v>
       </c>
       <c r="F10" s="9"/>
       <c r="H10" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I10" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>103</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M10" t="s">
         <v>11</v>
@@ -5466,36 +5440,36 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="7" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,B11:F11)</f>
-        <v>Item_RHand_Bow_8</v>
+        <f t="shared" si="0"/>
+        <v>Item_MainWeapon_Bow_8</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="F11" s="9"/>
       <c r="H11" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="I11" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M11" t="s">
         <v>11</v>
@@ -5519,16 +5493,16 @@
     <row r="13" spans="1:25">
       <c r="A13" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B13:F13)</f>
-        <v>Item_RHand_Shield_1</v>
+        <v>Item_SubWeapon_Shield_1</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5536,16 +5510,16 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I13" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" t="s">
@@ -5558,16 +5532,16 @@
     <row r="14" spans="1:25">
       <c r="A14" s="7" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,B14:F14)</f>
-        <v>Item_RHand_Shield_2</v>
+        <v>Item_SubWeapon_Shield_2</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -5575,16 +5549,16 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="I14" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L14" s="11"/>
       <c r="M14" t="s">
@@ -5596,17 +5570,17 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="7" t="str">
-        <f t="shared" ref="A15:A22" si="0">_xlfn.TEXTJOIN("_",TRUE,B15:F15)</f>
-        <v>Item_RHand_Shield_3</v>
+        <f t="shared" ref="A15:A22" si="1">_xlfn.TEXTJOIN("_",TRUE,B15:F15)</f>
+        <v>Item_SubWeapon_Shield_3</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D15" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -5614,16 +5588,16 @@
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="I15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L15" s="11"/>
       <c r="M15" t="s">
@@ -5635,17 +5609,17 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Item_RHand_Shield_4</v>
+        <f t="shared" si="1"/>
+        <v>Item_SubWeapon_Shield_4</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -5653,16 +5627,16 @@
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L16" s="11"/>
       <c r="M16" t="s">
@@ -5674,17 +5648,17 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Item_RHand_Shield_5</v>
+        <f t="shared" si="1"/>
+        <v>Item_SubWeapon_Shield_5</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D17" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -5692,16 +5666,16 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I17" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L17" s="11"/>
       <c r="M17" t="s">
@@ -5713,17 +5687,17 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Item_RHand_Shield_6</v>
+        <f t="shared" si="1"/>
+        <v>Item_SubWeapon_Shield_6</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D18" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -5731,16 +5705,16 @@
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="I18" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L18" s="11"/>
       <c r="M18" t="s">
@@ -5752,17 +5726,17 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Item_RHand_Shield_7</v>
+        <f t="shared" si="1"/>
+        <v>Item_SubWeapon_Shield_7</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D19" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E19">
         <v>7</v>
@@ -5770,16 +5744,16 @@
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I19" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L19" s="11"/>
       <c r="M19" t="s">
@@ -5791,17 +5765,17 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Item_RHand_Shield_8</v>
+        <f t="shared" si="1"/>
+        <v>Item_SubWeapon_Shield_8</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D20" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -5809,16 +5783,16 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="I20" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L20" s="11"/>
       <c r="M20" t="s">
@@ -5830,17 +5804,17 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Item_RHand_Shield_9</v>
+        <f t="shared" si="1"/>
+        <v>Item_SubWeapon_Shield_9</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D21" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E21">
         <v>9</v>
@@ -5848,16 +5822,16 @@
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I21" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L21" s="11"/>
       <c r="M21" t="s">
@@ -5869,17 +5843,17 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Item_RHand_Shield_10</v>
+        <f t="shared" si="1"/>
+        <v>Item_SubWeapon_Shield_10</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>203</v>
+        <v>356</v>
       </c>
       <c r="D22" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -5887,16 +5861,16 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I22" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L22" s="11"/>
       <c r="M22" t="s">
@@ -5920,17 +5894,17 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="7" t="str">
-        <f t="shared" ref="A24" si="1">_xlfn.TEXTJOIN("_",TRUE,B24:F24)</f>
-        <v>Item_LHand_Sword_1</v>
+        <f t="shared" ref="A24" si="2">_xlfn.TEXTJOIN("_",TRUE,B24:F24)</f>
+        <v>Item_MainWeapon_Sword_1</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -5938,16 +5912,16 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L24" s="11"/>
       <c r="M24" t="s">
@@ -5959,17 +5933,17 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="7" t="str">
-        <f t="shared" ref="A25:A41" si="2">_xlfn.TEXTJOIN("_",TRUE,B25:F25)</f>
-        <v>Item_LHand_Sword_2</v>
+        <f t="shared" ref="A25:A41" si="3">_xlfn.TEXTJOIN("_",TRUE,B25:F25)</f>
+        <v>Item_MainWeapon_Sword_2</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -5977,16 +5951,16 @@
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L25" s="11"/>
       <c r="M25" t="s">
@@ -5998,17 +5972,17 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_3</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_3</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D26" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -6016,16 +5990,16 @@
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L26" s="11"/>
       <c r="M26" t="s">
@@ -6037,17 +6011,17 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_4</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_4</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D27" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -6055,16 +6029,16 @@
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L27" s="11"/>
       <c r="M27" t="s">
@@ -6076,17 +6050,17 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_5</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_5</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -6094,16 +6068,16 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L28" s="11"/>
       <c r="M28" t="s">
@@ -6115,17 +6089,17 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_6</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_6</v>
       </c>
       <c r="B29" t="s">
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D29" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -6133,16 +6107,16 @@
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L29" s="11"/>
       <c r="M29" t="s">
@@ -6154,17 +6128,17 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_7</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_7</v>
       </c>
       <c r="B30" t="s">
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D30" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E30">
         <v>7</v>
@@ -6172,16 +6146,16 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L30" s="11"/>
       <c r="M30" t="s">
@@ -6193,17 +6167,17 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_8</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_8</v>
       </c>
       <c r="B31" t="s">
         <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D31" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E31">
         <v>8</v>
@@ -6211,16 +6185,16 @@
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L31" s="11"/>
       <c r="M31" t="s">
@@ -6232,17 +6206,17 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_9</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_9</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D32" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E32">
         <v>9</v>
@@ -6250,16 +6224,16 @@
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L32" s="11"/>
       <c r="M32" t="s">
@@ -6271,17 +6245,17 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_10</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_10</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D33" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E33">
         <v>10</v>
@@ -6289,16 +6263,16 @@
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L33" s="11"/>
       <c r="M33" t="s">
@@ -6310,17 +6284,17 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_11</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_11</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D34" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E34">
         <v>11</v>
@@ -6328,16 +6302,16 @@
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L34" s="11"/>
       <c r="M34" t="s">
@@ -6349,17 +6323,17 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_12</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_12</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D35" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -6367,16 +6341,16 @@
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L35" s="11"/>
       <c r="M35" t="s">
@@ -6388,17 +6362,17 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_13</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_13</v>
       </c>
       <c r="B36" t="s">
         <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D36" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E36">
         <v>13</v>
@@ -6406,16 +6380,16 @@
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L36" s="11"/>
       <c r="M36" t="s">
@@ -6427,17 +6401,17 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_14</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_14</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D37" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E37">
         <v>14</v>
@@ -6445,16 +6419,16 @@
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L37" s="11"/>
       <c r="M37" t="s">
@@ -6466,17 +6440,17 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_15</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_15</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D38" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E38">
         <v>15</v>
@@ -6484,16 +6458,16 @@
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L38" s="11"/>
       <c r="M38" t="s">
@@ -6505,17 +6479,17 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_16</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_16</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D39" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E39">
         <v>16</v>
@@ -6523,16 +6497,16 @@
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L39" s="11"/>
       <c r="M39" t="s">
@@ -6544,17 +6518,17 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_17</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_17</v>
       </c>
       <c r="B40" t="s">
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D40" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E40">
         <v>17</v>
@@ -6562,16 +6536,16 @@
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L40" s="11"/>
       <c r="M40" t="s">
@@ -6583,17 +6557,17 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_LHand_Sword_18</v>
+        <f t="shared" si="3"/>
+        <v>Item_MainWeapon_Sword_18</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D41" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E41">
         <v>18</v>
@@ -6601,16 +6575,16 @@
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L41" s="11"/>
       <c r="M41" t="s">
@@ -6634,17 +6608,17 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="7" t="str">
-        <f t="shared" ref="A43:A47" si="3">_xlfn.TEXTJOIN("_",TRUE,B43:F43)</f>
-        <v>Item_LHand_Staff_1</v>
+        <f t="shared" ref="A43:A47" si="4">_xlfn.TEXTJOIN("_",TRUE,B43:F43)</f>
+        <v>Item_MainWeapon_Staff_1</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -6652,16 +6626,16 @@
       <c r="F43" s="9"/>
       <c r="G43" s="9"/>
       <c r="H43" s="22" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L43" s="11"/>
       <c r="M43" t="s">
@@ -6673,17 +6647,17 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Item_LHand_Staff_2</v>
+        <f t="shared" si="4"/>
+        <v>Item_MainWeapon_Staff_2</v>
       </c>
       <c r="B44" t="s">
         <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D44" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -6691,16 +6665,16 @@
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="22" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L44" s="11"/>
       <c r="M44" t="s">
@@ -6712,17 +6686,17 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Item_LHand_Staff_3</v>
+        <f t="shared" si="4"/>
+        <v>Item_MainWeapon_Staff_3</v>
       </c>
       <c r="B45" t="s">
         <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D45" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -6730,16 +6704,16 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="22" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L45" s="11"/>
       <c r="M45" t="s">
@@ -6751,17 +6725,17 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Item_LHand_Staff_4</v>
+        <f t="shared" si="4"/>
+        <v>Item_MainWeapon_Staff_4</v>
       </c>
       <c r="B46" t="s">
         <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D46" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E46">
         <v>4</v>
@@ -6769,16 +6743,16 @@
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
       <c r="H46" s="22" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L46" s="11"/>
       <c r="M46" t="s">
@@ -6790,17 +6764,17 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Item_LHand_Staff_5</v>
+        <f t="shared" si="4"/>
+        <v>Item_MainWeapon_Staff_5</v>
       </c>
       <c r="B47" t="s">
         <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="D47" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E47">
         <v>5</v>
@@ -6808,16 +6782,16 @@
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
       <c r="H47" s="22" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L47" s="11"/>
       <c r="M47" t="s">
@@ -6841,17 +6815,17 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="7" t="str">
-        <f t="shared" ref="A49:A75" si="4">_xlfn.TEXTJOIN("_",TRUE,B49:F49)</f>
+        <f t="shared" ref="A49:A75" si="5">_xlfn.TEXTJOIN("_",TRUE,B49:F49)</f>
         <v>Item_Top_Top_1</v>
       </c>
       <c r="B49" t="s">
         <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D49" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -6859,16 +6833,16 @@
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L49" s="11"/>
       <c r="M49" t="s">
@@ -6880,17 +6854,17 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_2</v>
       </c>
       <c r="B50" t="s">
         <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D50" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E50">
         <v>2</v>
@@ -6898,16 +6872,16 @@
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L50" s="11"/>
       <c r="M50" t="s">
@@ -6919,17 +6893,17 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_3</v>
       </c>
       <c r="B51" t="s">
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D51" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -6937,16 +6911,16 @@
       <c r="F51" s="9"/>
       <c r="G51" s="9"/>
       <c r="H51" s="9" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L51" s="11"/>
       <c r="M51" t="s">
@@ -6958,17 +6932,17 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_4</v>
       </c>
       <c r="B52" t="s">
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D52" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E52">
         <v>4</v>
@@ -6976,16 +6950,16 @@
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
       <c r="H52" s="9" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L52" s="11"/>
       <c r="M52" t="s">
@@ -6997,17 +6971,17 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_5</v>
       </c>
       <c r="B53" t="s">
         <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D53" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E53">
         <v>5</v>
@@ -7015,16 +6989,16 @@
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L53" s="11"/>
       <c r="M53" t="s">
@@ -7036,17 +7010,17 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_6</v>
       </c>
       <c r="B54" t="s">
         <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D54" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E54">
         <v>6</v>
@@ -7054,16 +7028,16 @@
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
       <c r="H54" s="9" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L54" s="11"/>
       <c r="M54" t="s">
@@ -7075,17 +7049,17 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_7</v>
       </c>
       <c r="B55" t="s">
         <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D55" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E55">
         <v>7</v>
@@ -7093,16 +7067,16 @@
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="9" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L55" s="11"/>
       <c r="M55" t="s">
@@ -7114,17 +7088,17 @@
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_8</v>
       </c>
       <c r="B56" t="s">
         <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D56" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E56">
         <v>8</v>
@@ -7132,16 +7106,16 @@
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L56" s="11"/>
       <c r="M56" t="s">
@@ -7153,17 +7127,17 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_9</v>
       </c>
       <c r="B57" t="s">
         <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D57" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E57">
         <v>9</v>
@@ -7171,16 +7145,16 @@
       <c r="F57" s="9"/>
       <c r="G57" s="9"/>
       <c r="H57" s="9" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L57" s="11"/>
       <c r="M57" t="s">
@@ -7192,17 +7166,17 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_10</v>
       </c>
       <c r="B58" t="s">
         <v>26</v>
       </c>
       <c r="C58" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D58" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E58">
         <v>10</v>
@@ -7210,16 +7184,16 @@
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
       <c r="H58" s="9" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L58" s="11"/>
       <c r="M58" t="s">
@@ -7231,17 +7205,17 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_11</v>
       </c>
       <c r="B59" t="s">
         <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D59" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E59">
         <v>11</v>
@@ -7249,16 +7223,16 @@
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
       <c r="H59" s="9" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L59" s="11"/>
       <c r="M59" t="s">
@@ -7270,17 +7244,17 @@
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_12</v>
       </c>
       <c r="B60" t="s">
         <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D60" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E60">
         <v>12</v>
@@ -7288,16 +7262,16 @@
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L60" s="11"/>
       <c r="M60" t="s">
@@ -7309,17 +7283,17 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_13</v>
       </c>
       <c r="B61" t="s">
         <v>26</v>
       </c>
       <c r="C61" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D61" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E61">
         <v>13</v>
@@ -7327,16 +7301,16 @@
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L61" s="11"/>
       <c r="M61" t="s">
@@ -7348,17 +7322,17 @@
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_14</v>
       </c>
       <c r="B62" t="s">
         <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D62" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E62">
         <v>14</v>
@@ -7366,16 +7340,16 @@
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
       <c r="H62" s="9" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" t="s">
@@ -7387,17 +7361,17 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_15</v>
       </c>
       <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D63" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E63">
         <v>15</v>
@@ -7405,16 +7379,16 @@
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L63" s="11"/>
       <c r="M63" t="s">
@@ -7426,17 +7400,17 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_16</v>
       </c>
       <c r="B64" t="s">
         <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D64" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E64">
         <v>16</v>
@@ -7444,16 +7418,16 @@
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
       <c r="H64" s="9" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L64" s="11"/>
       <c r="M64" t="s">
@@ -7465,17 +7439,17 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_17</v>
       </c>
       <c r="B65" t="s">
         <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D65" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E65">
         <v>17</v>
@@ -7483,16 +7457,16 @@
       <c r="F65" s="9"/>
       <c r="G65" s="9"/>
       <c r="H65" s="9" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L65" s="11"/>
       <c r="M65" t="s">
@@ -7504,17 +7478,17 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_18</v>
       </c>
       <c r="B66" t="s">
         <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D66" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E66">
         <v>18</v>
@@ -7522,16 +7496,16 @@
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="9" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L66" s="11"/>
       <c r="M66" t="s">
@@ -7543,17 +7517,17 @@
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_19</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D67" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E67">
         <v>19</v>
@@ -7561,16 +7535,16 @@
       <c r="F67" s="9"/>
       <c r="G67" s="9"/>
       <c r="H67" s="9" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L67" s="11"/>
       <c r="M67" t="s">
@@ -7582,17 +7556,17 @@
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_20</v>
       </c>
       <c r="B68" t="s">
         <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D68" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E68">
         <v>20</v>
@@ -7600,16 +7574,16 @@
       <c r="F68" s="9"/>
       <c r="G68" s="9"/>
       <c r="H68" s="9" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L68" s="11"/>
       <c r="M68" t="s">
@@ -7621,17 +7595,17 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_21</v>
       </c>
       <c r="B69" t="s">
         <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D69" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E69">
         <v>21</v>
@@ -7639,16 +7613,16 @@
       <c r="F69" s="9"/>
       <c r="G69" s="9"/>
       <c r="H69" s="9" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L69" s="11"/>
       <c r="M69" t="s">
@@ -7660,17 +7634,17 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_22</v>
       </c>
       <c r="B70" t="s">
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D70" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E70">
         <v>22</v>
@@ -7678,16 +7652,16 @@
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="9" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L70" s="11"/>
       <c r="M70" t="s">
@@ -7699,17 +7673,17 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_23</v>
       </c>
       <c r="B71" t="s">
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D71" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E71">
         <v>23</v>
@@ -7717,16 +7691,16 @@
       <c r="F71" s="9"/>
       <c r="G71" s="9"/>
       <c r="H71" s="9" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K71" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L71" s="11"/>
       <c r="M71" t="s">
@@ -7738,17 +7712,17 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_24</v>
       </c>
       <c r="B72" t="s">
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D72" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E72">
         <v>24</v>
@@ -7756,16 +7730,16 @@
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
       <c r="H72" s="9" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K72" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L72" s="11"/>
       <c r="M72" t="s">
@@ -7777,17 +7751,17 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_25</v>
       </c>
       <c r="B73" t="s">
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D73" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E73">
         <v>25</v>
@@ -7795,16 +7769,16 @@
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
       <c r="H73" s="9" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L73" s="11"/>
       <c r="M73" t="s">
@@ -7816,17 +7790,17 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_26</v>
       </c>
       <c r="B74" t="s">
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D74" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E74">
         <v>26</v>
@@ -7834,16 +7808,16 @@
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L74" s="11"/>
       <c r="M74" t="s">
@@ -7855,17 +7829,17 @@
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Item_Top_Top_27</v>
       </c>
       <c r="B75" t="s">
         <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D75" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E75">
         <v>27</v>
@@ -7873,16 +7847,16 @@
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
       <c r="H75" s="9" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K75" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L75" s="11"/>
       <c r="M75" t="s">
@@ -7901,10 +7875,10 @@
         <v>26</v>
       </c>
       <c r="C76" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D76" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E76">
         <v>28</v>
@@ -7912,16 +7886,16 @@
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="9" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L76" s="11"/>
       <c r="M76" t="s">
@@ -7940,10 +7914,10 @@
         <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D77" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E77">
         <v>29</v>
@@ -7951,16 +7925,16 @@
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L77" s="11"/>
       <c r="M77" t="s">
@@ -7979,26 +7953,26 @@
         <v>26</v>
       </c>
       <c r="C78" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D78" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E78">
         <v>30</v>
       </c>
       <c r="F78" s="9"/>
       <c r="H78" s="9" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L78" s="11"/>
       <c r="M78" t="s">
@@ -8017,10 +7991,10 @@
         <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D79" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E79">
         <v>31</v>
@@ -8028,16 +8002,16 @@
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L79" s="11"/>
       <c r="M79" t="s">
@@ -8058,32 +8032,32 @@
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="7" t="str">
-        <f t="shared" ref="A81" si="5">_xlfn.TEXTJOIN("_",TRUE,B81:F81)</f>
+        <f t="shared" ref="A81" si="6">_xlfn.TEXTJOIN("_",TRUE,B81:F81)</f>
         <v>Item_Pants_Pants_1</v>
       </c>
       <c r="B81" t="s">
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D81" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="I81" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L81" s="11"/>
       <c r="M81" t="s">
@@ -8102,25 +8076,25 @@
         <v>26</v>
       </c>
       <c r="C82" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D82" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E82">
         <v>2</v>
       </c>
       <c r="H82" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="I82" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L82" s="11"/>
       <c r="M82" t="s">
@@ -8139,25 +8113,25 @@
         <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D83" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
       <c r="H83" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I83" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L83" s="11"/>
       <c r="M83" t="s">
@@ -8176,25 +8150,25 @@
         <v>26</v>
       </c>
       <c r="C84" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D84" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E84">
         <v>4</v>
       </c>
       <c r="H84" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="I84" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L84" s="11"/>
       <c r="M84" t="s">
@@ -8213,25 +8187,25 @@
         <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D85" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E85">
         <v>5</v>
       </c>
       <c r="H85" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="I85" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L85" s="11"/>
       <c r="M85" t="s">
@@ -8243,32 +8217,32 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="7" t="str">
-        <f t="shared" ref="A86" si="6">_xlfn.TEXTJOIN("_",TRUE,B86:F86)</f>
+        <f t="shared" ref="A86" si="7">_xlfn.TEXTJOIN("_",TRUE,B86:F86)</f>
         <v>Item_Pants_Pants_6</v>
       </c>
       <c r="B86" t="s">
         <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D86" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E86">
         <v>6</v>
       </c>
       <c r="H86" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I86" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L86" s="11"/>
       <c r="M86" t="s">
@@ -8287,25 +8261,25 @@
         <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D87" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E87">
         <v>7</v>
       </c>
       <c r="H87" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="I87" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K87" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L87" s="11"/>
       <c r="M87" t="s">
@@ -8324,25 +8298,25 @@
         <v>26</v>
       </c>
       <c r="C88" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D88" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E88">
         <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="I88" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L88" s="11"/>
       <c r="M88" t="s">
@@ -8361,25 +8335,25 @@
         <v>26</v>
       </c>
       <c r="C89" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D89" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E89">
         <v>9</v>
       </c>
       <c r="H89" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="I89" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K89" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L89" s="11"/>
       <c r="M89" t="s">
@@ -8398,25 +8372,25 @@
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D90" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E90">
         <v>10</v>
       </c>
       <c r="H90" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I90" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K90" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L90" s="11"/>
       <c r="M90" t="s">
@@ -8428,32 +8402,32 @@
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="7" t="str">
-        <f t="shared" ref="A91" si="7">_xlfn.TEXTJOIN("_",TRUE,B91:F91)</f>
+        <f t="shared" ref="A91" si="8">_xlfn.TEXTJOIN("_",TRUE,B91:F91)</f>
         <v>Item_Pants_Pants_11</v>
       </c>
       <c r="B91" t="s">
         <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D91" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E91">
         <v>11</v>
       </c>
       <c r="H91" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="I91" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K91" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L91" s="11"/>
       <c r="M91" t="s">
@@ -8472,25 +8446,25 @@
         <v>26</v>
       </c>
       <c r="C92" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D92" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E92">
         <v>12</v>
       </c>
       <c r="H92" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I92" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K92" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L92" s="11"/>
       <c r="M92" t="s">
@@ -8509,25 +8483,25 @@
         <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D93" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E93">
         <v>13</v>
       </c>
       <c r="H93" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="I93" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K93" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L93" s="11"/>
       <c r="M93" t="s">
@@ -8546,25 +8520,25 @@
         <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D94" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E94">
         <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="I94" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="J94" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K94" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L94" s="11"/>
       <c r="M94" t="s">
@@ -8583,25 +8557,25 @@
         <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D95" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E95">
         <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="I95" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K95" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L95" s="11"/>
       <c r="M95" t="s">
@@ -8613,32 +8587,32 @@
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="7" t="str">
-        <f t="shared" ref="A96" si="8">_xlfn.TEXTJOIN("_",TRUE,B96:F96)</f>
+        <f t="shared" ref="A96" si="9">_xlfn.TEXTJOIN("_",TRUE,B96:F96)</f>
         <v>Item_Pants_Pants_16</v>
       </c>
       <c r="B96" t="s">
         <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D96" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E96">
         <v>16</v>
       </c>
       <c r="H96" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I96" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K96" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L96" s="11"/>
       <c r="M96" t="s">
@@ -8657,25 +8631,25 @@
         <v>26</v>
       </c>
       <c r="C97" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D97" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E97">
         <v>17</v>
       </c>
       <c r="H97" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I97" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="J97" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K97" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L97" s="11"/>
       <c r="M97" t="s">
@@ -8694,25 +8668,25 @@
         <v>26</v>
       </c>
       <c r="C98" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D98" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E98">
         <v>18</v>
       </c>
       <c r="H98" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I98" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J98" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K98" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L98" s="11"/>
       <c r="M98" t="s">
@@ -8731,25 +8705,25 @@
         <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D99" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E99">
         <v>19</v>
       </c>
       <c r="H99" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="I99" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J99" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K99" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L99" s="11"/>
       <c r="M99" t="s">
@@ -8768,25 +8742,25 @@
         <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D100" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E100">
         <v>20</v>
       </c>
       <c r="H100" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I100" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J100" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K100" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L100" s="11"/>
       <c r="M100" t="s">
@@ -8805,25 +8779,25 @@
         <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D101" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E101">
         <v>21</v>
       </c>
       <c r="H101" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="I101" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="J101" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K101" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L101" s="11"/>
       <c r="M101" t="s">
@@ -8847,25 +8821,25 @@
         <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D103" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E103">
         <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I103" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="J103" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K103" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L103" s="11"/>
       <c r="M103" t="s">
@@ -8877,32 +8851,32 @@
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="7" t="str">
-        <f t="shared" ref="A104:A108" si="9">_xlfn.TEXTJOIN("_",TRUE,B104:F104)</f>
+        <f t="shared" ref="A104:A108" si="10">_xlfn.TEXTJOIN("_",TRUE,B104:F104)</f>
         <v>Item_Cape_Cape_2</v>
       </c>
       <c r="B104" t="s">
         <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D104" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E104">
         <v>2</v>
       </c>
       <c r="H104" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="I104" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L104" s="11"/>
       <c r="M104" t="s">
@@ -8914,32 +8888,32 @@
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Item_Cape_Cape_3</v>
       </c>
       <c r="B105" t="s">
         <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D105" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E105">
         <v>3</v>
       </c>
       <c r="H105" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I105" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K105" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L105" s="11"/>
       <c r="M105" t="s">
@@ -8951,32 +8925,32 @@
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Item_Cape_Cape_4</v>
       </c>
       <c r="B106" t="s">
         <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D106" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E106">
         <v>4</v>
       </c>
       <c r="H106" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="I106" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="J106" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K106" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L106" s="11"/>
       <c r="M106" t="s">
@@ -8988,32 +8962,32 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Item_Cape_Cape_5</v>
       </c>
       <c r="B107" t="s">
         <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D107" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E107">
         <v>5</v>
       </c>
       <c r="H107" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="I107" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J107" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K107" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L107" s="11"/>
       <c r="M107" t="s">
@@ -9025,32 +8999,32 @@
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Item_Cape_Cape_6</v>
       </c>
       <c r="B108" t="s">
         <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D108" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E108">
         <v>6</v>
       </c>
       <c r="H108" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="I108" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="J108" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K108" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L108" s="11"/>
       <c r="M108" t="s">
@@ -9067,32 +9041,32 @@
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="7" t="str">
-        <f t="shared" ref="A110" si="10">_xlfn.TEXTJOIN("_",TRUE,B110:F110)</f>
+        <f t="shared" ref="A110" si="11">_xlfn.TEXTJOIN("_",TRUE,B110:F110)</f>
         <v>Item_FaceAcc_FaceAcc_1</v>
       </c>
       <c r="B110" t="s">
         <v>26</v>
       </c>
       <c r="C110" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D110" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E110">
         <v>1</v>
       </c>
       <c r="H110" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I110" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="J110" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K110" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L110" s="11"/>
       <c r="M110" t="s">
@@ -9104,32 +9078,32 @@
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="7" t="str">
-        <f t="shared" ref="A111:A116" si="11">_xlfn.TEXTJOIN("_",TRUE,B111:F111)</f>
+        <f t="shared" ref="A111:A116" si="12">_xlfn.TEXTJOIN("_",TRUE,B111:F111)</f>
         <v>Item_FaceAcc_FaceAcc_2</v>
       </c>
       <c r="B111" t="s">
         <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D111" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E111">
         <v>2</v>
       </c>
       <c r="H111" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="I111" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J111" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K111" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L111" s="11"/>
       <c r="M111" t="s">
@@ -9141,32 +9115,32 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Item_FaceAcc_FaceAcc_3</v>
       </c>
       <c r="B112" t="s">
         <v>26</v>
       </c>
       <c r="C112" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D112" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E112">
         <v>3</v>
       </c>
       <c r="H112" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="I112" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K112" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L112" s="11"/>
       <c r="M112" t="s">
@@ -9178,32 +9152,32 @@
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Item_FaceAcc_FaceAcc_4</v>
       </c>
       <c r="B113" t="s">
         <v>26</v>
       </c>
       <c r="C113" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D113" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E113">
         <v>4</v>
       </c>
       <c r="H113" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="I113" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="J113" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K113" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L113" s="11"/>
       <c r="M113" t="s">
@@ -9215,32 +9189,32 @@
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Item_FaceAcc_FaceAcc_5</v>
       </c>
       <c r="B114" t="s">
         <v>26</v>
       </c>
       <c r="C114" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D114" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E114">
         <v>5</v>
       </c>
       <c r="H114" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I114" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="J114" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K114" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L114" s="11"/>
       <c r="M114" t="s">
@@ -9252,32 +9226,32 @@
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Item_FaceAcc_FaceAcc_6</v>
       </c>
       <c r="B115" t="s">
         <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D115" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E115">
         <v>6</v>
       </c>
       <c r="H115" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="I115" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="J115" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K115" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L115" s="11"/>
       <c r="M115" t="s">
@@ -9289,32 +9263,32 @@
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Item_FaceAcc_FaceAcc_7</v>
       </c>
       <c r="B116" t="s">
         <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D116" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E116">
         <v>7</v>
       </c>
       <c r="H116" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="I116" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="J116" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K116" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L116" s="11"/>
       <c r="M116" t="s">
@@ -9331,32 +9305,32 @@
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="7" t="str">
-        <f t="shared" ref="A118:A122" si="12">_xlfn.TEXTJOIN("_",TRUE,B118:F118)</f>
+        <f t="shared" ref="A118:A122" si="13">_xlfn.TEXTJOIN("_",TRUE,B118:F118)</f>
         <v>Item_HairAcc_Hat_1</v>
       </c>
       <c r="B118" t="s">
         <v>26</v>
       </c>
       <c r="C118" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D118" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E118">
         <v>1</v>
       </c>
       <c r="H118" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="I118" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K118" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L118" s="11"/>
       <c r="M118" t="s">
@@ -9368,32 +9342,32 @@
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="7" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Item_HairAcc_Hat_2</v>
       </c>
       <c r="B119" t="s">
         <v>26</v>
       </c>
       <c r="C119" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D119" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E119">
         <v>2</v>
       </c>
       <c r="H119" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="I119" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="J119" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K119" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L119" s="11"/>
       <c r="M119" t="s">
@@ -9405,32 +9379,32 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="7" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Item_HairAcc_Hat_3</v>
       </c>
       <c r="B120" t="s">
         <v>26</v>
       </c>
       <c r="C120" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D120" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E120">
         <v>3</v>
       </c>
       <c r="H120" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="I120" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="J120" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K120" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L120" s="11"/>
       <c r="M120" t="s">
@@ -9442,32 +9416,32 @@
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="7" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Item_HairAcc_Hat_4</v>
       </c>
       <c r="B121" t="s">
         <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D121" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E121">
         <v>4</v>
       </c>
       <c r="H121" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I121" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="J121" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K121" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L121" s="11"/>
       <c r="M121" t="s">
@@ -9479,32 +9453,32 @@
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="7" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Item_HairAcc_Hat_5</v>
       </c>
       <c r="B122" t="s">
         <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D122" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E122">
         <v>5</v>
       </c>
       <c r="H122" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="I122" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K122" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L122" s="11"/>
       <c r="M122" t="s">
@@ -9516,32 +9490,32 @@
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="7" t="str">
-        <f t="shared" ref="A123:A142" si="13">_xlfn.TEXTJOIN("_",TRUE,B123:F123)</f>
+        <f t="shared" ref="A123:A142" si="14">_xlfn.TEXTJOIN("_",TRUE,B123:F123)</f>
         <v>Item_HairAcc_Hat_6</v>
       </c>
       <c r="B123" t="s">
         <v>26</v>
       </c>
       <c r="C123" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D123" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E123">
         <v>6</v>
       </c>
       <c r="H123" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I123" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="J123" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K123" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L123" s="11"/>
       <c r="M123" t="s">
@@ -9553,32 +9527,32 @@
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_7</v>
       </c>
       <c r="B124" t="s">
         <v>26</v>
       </c>
       <c r="C124" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D124" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E124">
         <v>7</v>
       </c>
       <c r="H124" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="I124" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="J124" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K124" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L124" s="11"/>
       <c r="M124" t="s">
@@ -9590,32 +9564,32 @@
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_8</v>
       </c>
       <c r="B125" t="s">
         <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D125" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="I125" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="J125" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K125" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L125" s="11"/>
       <c r="M125" t="s">
@@ -9627,32 +9601,32 @@
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_9</v>
       </c>
       <c r="B126" t="s">
         <v>26</v>
       </c>
       <c r="C126" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D126" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E126">
         <v>9</v>
       </c>
       <c r="H126" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="I126" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="J126" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K126" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L126" s="11"/>
       <c r="M126" t="s">
@@ -9664,32 +9638,32 @@
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_10</v>
       </c>
       <c r="B127" t="s">
         <v>26</v>
       </c>
       <c r="C127" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D127" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E127">
         <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="I127" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="J127" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K127" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L127" s="11"/>
       <c r="M127" t="s">
@@ -9701,32 +9675,32 @@
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_11</v>
       </c>
       <c r="B128" t="s">
         <v>26</v>
       </c>
       <c r="C128" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D128" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E128">
         <v>11</v>
       </c>
       <c r="H128" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="I128" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="J128" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K128" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L128" s="11"/>
       <c r="M128" t="s">
@@ -9738,32 +9712,32 @@
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_12</v>
       </c>
       <c r="B129" t="s">
         <v>26</v>
       </c>
       <c r="C129" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D129" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E129">
         <v>12</v>
       </c>
       <c r="H129" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="I129" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="J129" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K129" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L129" s="11"/>
       <c r="M129" t="s">
@@ -9775,32 +9749,32 @@
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_13</v>
       </c>
       <c r="B130" t="s">
         <v>26</v>
       </c>
       <c r="C130" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D130" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E130">
         <v>13</v>
       </c>
       <c r="H130" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I130" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K130" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L130" s="11"/>
       <c r="M130" t="s">
@@ -9812,32 +9786,32 @@
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_14</v>
       </c>
       <c r="B131" t="s">
         <v>26</v>
       </c>
       <c r="C131" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D131" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E131">
         <v>14</v>
       </c>
       <c r="H131" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="I131" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="J131" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K131" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L131" s="11"/>
       <c r="M131" t="s">
@@ -9849,32 +9823,32 @@
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_15</v>
       </c>
       <c r="B132" t="s">
         <v>26</v>
       </c>
       <c r="C132" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D132" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E132">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I132" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K132" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L132" s="11"/>
       <c r="M132" t="s">
@@ -9886,32 +9860,32 @@
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_16</v>
       </c>
       <c r="B133" t="s">
         <v>26</v>
       </c>
       <c r="C133" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D133" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E133">
         <v>16</v>
       </c>
       <c r="H133" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I133" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="J133" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K133" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L133" s="11"/>
       <c r="M133" t="s">
@@ -9923,32 +9897,32 @@
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_17</v>
       </c>
       <c r="B134" t="s">
         <v>26</v>
       </c>
       <c r="C134" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D134" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E134">
         <v>17</v>
       </c>
       <c r="H134" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I134" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="J134" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K134" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L134" s="11"/>
       <c r="M134" t="s">
@@ -9960,32 +9934,32 @@
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_18</v>
       </c>
       <c r="B135" t="s">
         <v>26</v>
       </c>
       <c r="C135" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D135" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E135">
         <v>18</v>
       </c>
       <c r="H135" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I135" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="J135" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K135" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L135" s="11"/>
       <c r="M135" t="s">
@@ -9997,32 +9971,32 @@
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_19</v>
       </c>
       <c r="B136" t="s">
         <v>26</v>
       </c>
       <c r="C136" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D136" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E136">
         <v>19</v>
       </c>
       <c r="H136" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="I136" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="J136" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K136" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L136" s="11"/>
       <c r="M136" t="s">
@@ -10034,32 +10008,32 @@
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_HairAcc_Hat_20</v>
       </c>
       <c r="B137" t="s">
         <v>26</v>
       </c>
       <c r="C137" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D137" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E137">
         <v>20</v>
       </c>
       <c r="H137" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I137" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="J137" s="11" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K137" s="11" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L137" s="11"/>
       <c r="M137" t="s">
@@ -10085,7 +10059,7 @@
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_Player_Player_Human</v>
       </c>
       <c r="B139" t="s">
@@ -10108,7 +10082,7 @@
         <v>59</v>
       </c>
       <c r="I139" t="s">
-        <v>109</v>
+        <v>332</v>
       </c>
       <c r="J139" s="11" t="s">
         <v>103</v>
@@ -10117,7 +10091,7 @@
         <v>102</v>
       </c>
       <c r="L139" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M139" t="s">
         <v>11</v>
@@ -10128,7 +10102,7 @@
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_Player_Player_Dog</v>
       </c>
       <c r="B140" t="s">
@@ -10151,7 +10125,7 @@
         <v>59</v>
       </c>
       <c r="I140" t="s">
-        <v>110</v>
+        <v>332</v>
       </c>
       <c r="J140" s="11" t="s">
         <v>103</v>
@@ -10160,7 +10134,7 @@
         <v>102</v>
       </c>
       <c r="L140" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M140" t="s">
         <v>11</v>
@@ -10171,7 +10145,7 @@
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_Player_Player_Eagle</v>
       </c>
       <c r="B141" t="s">
@@ -10194,7 +10168,7 @@
         <v>59</v>
       </c>
       <c r="I141" t="s">
-        <v>111</v>
+        <v>332</v>
       </c>
       <c r="J141" s="11" t="s">
         <v>103</v>
@@ -10203,7 +10177,7 @@
         <v>102</v>
       </c>
       <c r="L141" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M141" t="s">
         <v>11</v>
@@ -10214,7 +10188,7 @@
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Item_Player_Player_Snake</v>
       </c>
       <c r="B142" t="s">
@@ -10237,7 +10211,7 @@
         <v>59</v>
       </c>
       <c r="I142" t="s">
-        <v>112</v>
+        <v>332</v>
       </c>
       <c r="J142" s="11" t="s">
         <v>103</v>
@@ -10246,7 +10220,7 @@
         <v>102</v>
       </c>
       <c r="L142" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M142" t="s">
         <v>11</v>
@@ -10763,7 +10737,7 @@
         <v>52</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:6">

--- a/Generated/GameData.xlsx
+++ b/Generated/GameData.xlsx
@@ -1848,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG24"/>
+  <dimension ref="A1:AH24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.140625" defaultRowHeight="18"/>
   <cols>
     <col width="23.28515625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1944,22 +1944,27 @@
           <t>List&lt;string&gt;</t>
         </is>
       </c>
-      <c r="R1" s="8" t="n"/>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="S1" s="8" t="n"/>
       <c r="T1" s="8" t="n"/>
       <c r="U1" s="8" t="n"/>
-      <c r="V1" s="5" t="n"/>
+      <c r="V1" s="8" t="n"/>
       <c r="W1" s="5" t="n"/>
-      <c r="X1" s="8" t="n"/>
+      <c r="X1" s="5" t="n"/>
       <c r="Y1" s="8" t="n"/>
-      <c r="Z1" s="5" t="n"/>
-      <c r="AA1" s="8" t="n"/>
+      <c r="Z1" s="8" t="n"/>
+      <c r="AA1" s="5" t="n"/>
       <c r="AB1" s="8" t="n"/>
       <c r="AC1" s="8" t="n"/>
       <c r="AD1" s="8" t="n"/>
       <c r="AE1" s="8" t="n"/>
-      <c r="AF1" s="5" t="n"/>
+      <c r="AF1" s="8" t="n"/>
       <c r="AG1" s="5" t="n"/>
+      <c r="AH1" s="5" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="n"/>
@@ -2023,22 +2028,27 @@
           <t>skillActionParam</t>
         </is>
       </c>
-      <c r="R2" s="8" t="n"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>skillEffectKey</t>
+        </is>
+      </c>
       <c r="S2" s="8" t="n"/>
       <c r="T2" s="8" t="n"/>
       <c r="U2" s="8" t="n"/>
-      <c r="V2" s="6" t="n"/>
+      <c r="V2" s="8" t="n"/>
       <c r="W2" s="6" t="n"/>
-      <c r="X2" s="8" t="n"/>
+      <c r="X2" s="6" t="n"/>
       <c r="Y2" s="8" t="n"/>
-      <c r="Z2" s="6" t="n"/>
-      <c r="AA2" s="8" t="n"/>
+      <c r="Z2" s="8" t="n"/>
+      <c r="AA2" s="6" t="n"/>
       <c r="AB2" s="8" t="n"/>
       <c r="AC2" s="8" t="n"/>
       <c r="AD2" s="8" t="n"/>
       <c r="AE2" s="8" t="n"/>
-      <c r="AF2" s="6" t="n"/>
+      <c r="AF2" s="8" t="n"/>
       <c r="AG2" s="6" t="n"/>
+      <c r="AH2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -2073,8 +2083,13 @@
           <t>타입별 읽기</t>
         </is>
       </c>
-      <c r="R3" s="9" t="n"/>
-      <c r="T3" s="9" t="n"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>연출 Scriptable Addressable Key</t>
+        </is>
+      </c>
+      <c r="S3" s="9" t="n"/>
+      <c r="U3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -2082,7 +2097,7 @@
           <t>//</t>
         </is>
       </c>
-      <c r="T4" s="13" t="n"/>
+      <c r="U4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2090,7 +2105,7 @@
           <t>//</t>
         </is>
       </c>
-      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2098,7 +2113,7 @@
           <t>// Projectile Example</t>
         </is>
       </c>
-      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2167,7 +2182,7 @@
           <t>3,5,Projectile_Human</t>
         </is>
       </c>
-      <c r="T7" s="13" t="n"/>
+      <c r="U7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2236,7 +2251,7 @@
           <t>3,5,Projectile_Human</t>
         </is>
       </c>
-      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2244,7 +2259,7 @@
           <t>//</t>
         </is>
       </c>
-      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2252,7 +2267,7 @@
           <t>//</t>
         </is>
       </c>
-      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2671,6 +2686,11 @@
       <c r="Q24" s="0" t="inlineStr">
         <is>
           <t>: Int * 100</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>SkillNew/Heal/SkillEffect_Heal_1</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3277,6 @@
       <c r="I4" s="9" t="n"/>
       <c r="J4" s="9" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -12289,40 +12308,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
     <row r="177">
       <c r="C177" s="9" t="n"/>
       <c r="D177" s="9" t="n"/>
